--- a/docs/確認事項リスト.xlsx
+++ b/docs/確認事項リスト.xlsx
@@ -2,20 +2,18 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yu/mock-training/bookshelf-app/docs/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B12DEAE-5535-5B49-A532-0638C6E92B73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookPr filterPrivacy="1" defaultThemeVersion="202300"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A581A4D-724D-0044-829A-003ECFD84904}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{E987AAC5-D7CB-4143-BFFD-E0642F54BEB6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$2:$H$342</definedName>
+  </definedNames>
+  <calcPr calcId="181029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1014" uniqueCount="599">
   <si>
     <t>質問</t>
     <rPh sb="0" eb="2">
@@ -416,9 +414,6 @@
     <t>Q-64</t>
   </si>
   <si>
-    <t>Q-65</t>
-  </si>
-  <si>
     <t>Q-66</t>
   </si>
   <si>
@@ -720,11 +715,6 @@
   </si>
   <si>
     <t>★ 読書計画編集画面</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> 読書計画作成画面の表示の際、未認証の場合のリダイレクト先が機能要件に存在しません。
-リダイレクト先はログイン画面でよろしいですか？</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -1599,12 +1589,1718 @@
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>PG01</t>
+  </si>
+  <si>
+    <t>API</t>
+  </si>
+  <si>
+    <t>書籍一覧API</t>
+  </si>
+  <si>
+    <t>APIでの一覧取得は、ソート機能は不要ですか？</t>
+    <rPh sb="5" eb="7">
+      <t>イチラn</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>シュトク</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>キノウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Q-101</t>
+  </si>
+  <si>
+    <t>Q-102</t>
+  </si>
+  <si>
+    <t>Q-103</t>
+  </si>
+  <si>
+    <t>Q-104</t>
+  </si>
+  <si>
+    <t>Q-105</t>
+  </si>
+  <si>
+    <t>Q-106</t>
+  </si>
+  <si>
+    <t>Q-107</t>
+  </si>
+  <si>
+    <t>Q-108</t>
+  </si>
+  <si>
+    <t>Q-109</t>
+  </si>
+  <si>
+    <t>Q-110</t>
+  </si>
+  <si>
+    <t>Q-111</t>
+  </si>
+  <si>
+    <t>Q-112</t>
+  </si>
+  <si>
+    <t>Q-113</t>
+  </si>
+  <si>
+    <t>Q-114</t>
+  </si>
+  <si>
+    <t>Q-115</t>
+  </si>
+  <si>
+    <t>Q-116</t>
+  </si>
+  <si>
+    <t>Q-117</t>
+  </si>
+  <si>
+    <t>Q-118</t>
+  </si>
+  <si>
+    <t>Q-119</t>
+  </si>
+  <si>
+    <t>Q-120</t>
+  </si>
+  <si>
+    <t>Q-121</t>
+  </si>
+  <si>
+    <t>Q-122</t>
+  </si>
+  <si>
+    <t>Q-123</t>
+  </si>
+  <si>
+    <t>Q-124</t>
+  </si>
+  <si>
+    <t>Q-125</t>
+  </si>
+  <si>
+    <t>Q-126</t>
+  </si>
+  <si>
+    <t>Q-127</t>
+  </si>
+  <si>
+    <t>Q-128</t>
+  </si>
+  <si>
+    <t>Q-129</t>
+  </si>
+  <si>
+    <t>Q-130</t>
+  </si>
+  <si>
+    <t>Q-131</t>
+  </si>
+  <si>
+    <t>Q-132</t>
+  </si>
+  <si>
+    <t>Q-133</t>
+  </si>
+  <si>
+    <t>Q-134</t>
+  </si>
+  <si>
+    <t>Q-135</t>
+  </si>
+  <si>
+    <t>Q-136</t>
+  </si>
+  <si>
+    <t>Q-137</t>
+  </si>
+  <si>
+    <t>Q-138</t>
+  </si>
+  <si>
+    <t>Q-139</t>
+  </si>
+  <si>
+    <t>Q-140</t>
+  </si>
+  <si>
+    <t>Q-141</t>
+  </si>
+  <si>
+    <t>Q-142</t>
+  </si>
+  <si>
+    <t>Q-143</t>
+  </si>
+  <si>
+    <t>Q-144</t>
+  </si>
+  <si>
+    <t>Q-145</t>
+  </si>
+  <si>
+    <t>Q-146</t>
+  </si>
+  <si>
+    <t>Q-147</t>
+  </si>
+  <si>
+    <t>Q-148</t>
+  </si>
+  <si>
+    <t>Q-149</t>
+  </si>
+  <si>
+    <t>Q-150</t>
+  </si>
+  <si>
+    <t>Q-151</t>
+  </si>
+  <si>
+    <t>Q-152</t>
+  </si>
+  <si>
+    <t>Q-153</t>
+  </si>
+  <si>
+    <t>Q-154</t>
+  </si>
+  <si>
+    <t>Q-155</t>
+  </si>
+  <si>
+    <t>Q-156</t>
+  </si>
+  <si>
+    <t>Q-157</t>
+  </si>
+  <si>
+    <t>Q-158</t>
+  </si>
+  <si>
+    <t>Q-159</t>
+  </si>
+  <si>
+    <t>Q-160</t>
+  </si>
+  <si>
+    <t>Q-161</t>
+  </si>
+  <si>
+    <t>Q-162</t>
+  </si>
+  <si>
+    <t>Q-163</t>
+  </si>
+  <si>
+    <t>Q-164</t>
+  </si>
+  <si>
+    <t>Q-165</t>
+  </si>
+  <si>
+    <t>Q-166</t>
+  </si>
+  <si>
+    <t>Q-167</t>
+  </si>
+  <si>
+    <t>Q-168</t>
+  </si>
+  <si>
+    <t>Q-169</t>
+  </si>
+  <si>
+    <t>Q-170</t>
+  </si>
+  <si>
+    <t>Q-171</t>
+  </si>
+  <si>
+    <t>Q-172</t>
+  </si>
+  <si>
+    <t>Q-173</t>
+  </si>
+  <si>
+    <t>Q-174</t>
+  </si>
+  <si>
+    <t>Q-175</t>
+  </si>
+  <si>
+    <t>Q-176</t>
+  </si>
+  <si>
+    <t>Q-177</t>
+  </si>
+  <si>
+    <t>Q-178</t>
+  </si>
+  <si>
+    <t>Q-179</t>
+  </si>
+  <si>
+    <t>Q-180</t>
+  </si>
+  <si>
+    <t>Q-181</t>
+  </si>
+  <si>
+    <t>Q-182</t>
+  </si>
+  <si>
+    <t>Q-183</t>
+  </si>
+  <si>
+    <t>Q-184</t>
+  </si>
+  <si>
+    <t>Q-185</t>
+  </si>
+  <si>
+    <t>Q-186</t>
+  </si>
+  <si>
+    <t>Q-187</t>
+  </si>
+  <si>
+    <t>Q-188</t>
+  </si>
+  <si>
+    <t>Q-189</t>
+  </si>
+  <si>
+    <t>Q-190</t>
+  </si>
+  <si>
+    <t>Q-191</t>
+  </si>
+  <si>
+    <t>Q-192</t>
+  </si>
+  <si>
+    <t>Q-193</t>
+  </si>
+  <si>
+    <t>Q-194</t>
+  </si>
+  <si>
+    <t>Q-195</t>
+  </si>
+  <si>
+    <t>Q-196</t>
+  </si>
+  <si>
+    <t>Q-197</t>
+  </si>
+  <si>
+    <t>Q-198</t>
+  </si>
+  <si>
+    <t>Q-199</t>
+  </si>
+  <si>
+    <t>Q-200</t>
+  </si>
+  <si>
+    <t>Q-201</t>
+  </si>
+  <si>
+    <t>Q-202</t>
+  </si>
+  <si>
+    <t>Q-203</t>
+  </si>
+  <si>
+    <t>Q-204</t>
+  </si>
+  <si>
+    <t>Q-205</t>
+  </si>
+  <si>
+    <t>Q-206</t>
+  </si>
+  <si>
+    <t>Q-207</t>
+  </si>
+  <si>
+    <t>Q-208</t>
+  </si>
+  <si>
+    <t>Q-209</t>
+  </si>
+  <si>
+    <t>Q-210</t>
+  </si>
+  <si>
+    <t>Q-211</t>
+  </si>
+  <si>
+    <t>Q-212</t>
+  </si>
+  <si>
+    <t>Q-213</t>
+  </si>
+  <si>
+    <t>Q-214</t>
+  </si>
+  <si>
+    <t>Q-215</t>
+  </si>
+  <si>
+    <t>Q-216</t>
+  </si>
+  <si>
+    <t>Q-217</t>
+  </si>
+  <si>
+    <t>Q-218</t>
+  </si>
+  <si>
+    <t>Q-219</t>
+  </si>
+  <si>
+    <t>Q-220</t>
+  </si>
+  <si>
+    <t>Q-221</t>
+  </si>
+  <si>
+    <t>Q-222</t>
+  </si>
+  <si>
+    <t>Q-223</t>
+  </si>
+  <si>
+    <t>Q-224</t>
+  </si>
+  <si>
+    <t>Q-225</t>
+  </si>
+  <si>
+    <t>Q-226</t>
+  </si>
+  <si>
+    <t>Q-227</t>
+  </si>
+  <si>
+    <t>Q-228</t>
+  </si>
+  <si>
+    <t>Q-229</t>
+  </si>
+  <si>
+    <t>Q-230</t>
+  </si>
+  <si>
+    <t>Q-231</t>
+  </si>
+  <si>
+    <t>Q-232</t>
+  </si>
+  <si>
+    <t>Q-233</t>
+  </si>
+  <si>
+    <t>Q-234</t>
+  </si>
+  <si>
+    <t>Q-235</t>
+  </si>
+  <si>
+    <t>Q-236</t>
+  </si>
+  <si>
+    <t>Q-237</t>
+  </si>
+  <si>
+    <t>Q-238</t>
+  </si>
+  <si>
+    <t>Q-239</t>
+  </si>
+  <si>
+    <t>Q-240</t>
+  </si>
+  <si>
+    <t>Q-241</t>
+  </si>
+  <si>
+    <t>Q-242</t>
+  </si>
+  <si>
+    <t>Q-243</t>
+  </si>
+  <si>
+    <t>Q-244</t>
+  </si>
+  <si>
+    <t>Q-245</t>
+  </si>
+  <si>
+    <t>Q-246</t>
+  </si>
+  <si>
+    <t>Q-247</t>
+  </si>
+  <si>
+    <t>Q-248</t>
+  </si>
+  <si>
+    <t>Q-249</t>
+  </si>
+  <si>
+    <t>Q-250</t>
+  </si>
+  <si>
+    <t>Q-251</t>
+  </si>
+  <si>
+    <t>Q-252</t>
+  </si>
+  <si>
+    <t>Q-253</t>
+  </si>
+  <si>
+    <t>Q-254</t>
+  </si>
+  <si>
+    <t>Q-255</t>
+  </si>
+  <si>
+    <t>Q-256</t>
+  </si>
+  <si>
+    <t>Q-257</t>
+  </si>
+  <si>
+    <t>Q-258</t>
+  </si>
+  <si>
+    <t>Q-259</t>
+  </si>
+  <si>
+    <t>Q-260</t>
+  </si>
+  <si>
+    <t>Q-261</t>
+  </si>
+  <si>
+    <t>Q-262</t>
+  </si>
+  <si>
+    <t>Q-263</t>
+  </si>
+  <si>
+    <t>Q-264</t>
+  </si>
+  <si>
+    <t>Q-265</t>
+  </si>
+  <si>
+    <t>Q-266</t>
+  </si>
+  <si>
+    <t>Q-267</t>
+  </si>
+  <si>
+    <t>Q-268</t>
+  </si>
+  <si>
+    <t>Q-269</t>
+  </si>
+  <si>
+    <t>Q-270</t>
+  </si>
+  <si>
+    <t>Q-271</t>
+  </si>
+  <si>
+    <t>Q-272</t>
+  </si>
+  <si>
+    <t>Q-273</t>
+  </si>
+  <si>
+    <t>Q-274</t>
+  </si>
+  <si>
+    <t>Q-275</t>
+  </si>
+  <si>
+    <t>Q-276</t>
+  </si>
+  <si>
+    <t>Q-277</t>
+  </si>
+  <si>
+    <t>Q-278</t>
+  </si>
+  <si>
+    <t>Q-279</t>
+  </si>
+  <si>
+    <t>Q-280</t>
+  </si>
+  <si>
+    <t>Q-281</t>
+  </si>
+  <si>
+    <t>Q-282</t>
+  </si>
+  <si>
+    <t>Q-283</t>
+  </si>
+  <si>
+    <t>Q-284</t>
+  </si>
+  <si>
+    <t>Q-285</t>
+  </si>
+  <si>
+    <t>Q-286</t>
+  </si>
+  <si>
+    <t>Q-287</t>
+  </si>
+  <si>
+    <t>Q-288</t>
+  </si>
+  <si>
+    <t>Q-289</t>
+  </si>
+  <si>
+    <t>Q-290</t>
+  </si>
+  <si>
+    <t>Q-291</t>
+  </si>
+  <si>
+    <t>Q-292</t>
+  </si>
+  <si>
+    <t>Q-293</t>
+  </si>
+  <si>
+    <t>Q-294</t>
+  </si>
+  <si>
+    <t>Q-295</t>
+  </si>
+  <si>
+    <t>Q-296</t>
+  </si>
+  <si>
+    <t>Q-297</t>
+  </si>
+  <si>
+    <t>Q-298</t>
+  </si>
+  <si>
+    <t>Q-299</t>
+  </si>
+  <si>
+    <t>Q-300</t>
+  </si>
+  <si>
+    <t>Q-301</t>
+  </si>
+  <si>
+    <t>Q-302</t>
+  </si>
+  <si>
+    <t>Q-303</t>
+  </si>
+  <si>
+    <t>Q-304</t>
+  </si>
+  <si>
+    <t>Q-305</t>
+  </si>
+  <si>
+    <t>Q-306</t>
+  </si>
+  <si>
+    <t>Q-307</t>
+  </si>
+  <si>
+    <t>Q-308</t>
+  </si>
+  <si>
+    <t>Q-309</t>
+  </si>
+  <si>
+    <t>Q-310</t>
+  </si>
+  <si>
+    <t>Q-311</t>
+  </si>
+  <si>
+    <t>Q-312</t>
+  </si>
+  <si>
+    <t>Q-313</t>
+  </si>
+  <si>
+    <t>Q-314</t>
+  </si>
+  <si>
+    <t>Q-315</t>
+  </si>
+  <si>
+    <t>Q-316</t>
+  </si>
+  <si>
+    <t>Q-317</t>
+  </si>
+  <si>
+    <t>Q-318</t>
+  </si>
+  <si>
+    <t>Q-319</t>
+  </si>
+  <si>
+    <t>Q-320</t>
+  </si>
+  <si>
+    <t>Q-321</t>
+  </si>
+  <si>
+    <t>Q-322</t>
+  </si>
+  <si>
+    <t>Q-323</t>
+  </si>
+  <si>
+    <t>Q-324</t>
+  </si>
+  <si>
+    <t>Q-325</t>
+  </si>
+  <si>
+    <t>Q-326</t>
+  </si>
+  <si>
+    <t>Q-327</t>
+  </si>
+  <si>
+    <t>Q-328</t>
+  </si>
+  <si>
+    <t>Q-329</t>
+  </si>
+  <si>
+    <t>Q-330</t>
+  </si>
+  <si>
+    <t>Q-331</t>
+  </si>
+  <si>
+    <t>Q-332</t>
+  </si>
+  <si>
+    <t>ページネーションリンクの最大表示数はデフォルトで何件としますか？</t>
+    <rPh sb="12" eb="14">
+      <t>サイダイ</t>
+    </rPh>
+    <rPh sb="14" eb="17">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>ナンケn</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>書籍登録画面/書籍編集画面</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>PG03/PG04</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>書籍詳細画面/レビュー編集画面</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>PG02/PG09</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>状態は任意・「in_progress」または「completed」のみ選択可能で設計しましたが、この制約で合っていますか？</t>
+    <rPh sb="3" eb="5">
+      <t>ニンイ</t>
+    </rPh>
+    <rPh sb="35" eb="39">
+      <t>センタク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AP03</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>書籍登録API</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AP03/AP04</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>書籍登録API/書籍更新API</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AP04</t>
+  </si>
+  <si>
+    <t>はい、問題ありません。会員登録成功後は書籍一覧画面（/）へリダイレクトしてください。</t>
+  </si>
+  <si>
+    <t>はい、問題ありません。ログイン成功後は書籍一覧画面（/）へリダイレクトしてください。</t>
+  </si>
+  <si>
+    <t>はい、問題ありません。バリデーションエラー時は入力内容（old値）とエラーメッセージを保持して元のフォームに戻してください。</t>
+  </si>
+  <si>
+    <t>はい、問題ありません。パスワード等を除き、入力内容を保持して元のフォームに戻してください。</t>
+  </si>
+  <si>
+    <t>書籍一覧画面（トップ）は公開ページのためゲストのまま閲覧可能です。「書籍を登録」ボタン等の認証必須操作を行った場合のみログイン画面（/login）へリダイレクトしてください。</t>
+  </si>
+  <si>
+    <t>はい、問題ありません。入力内容（old値）とエラーメッセージを保持して元の書籍詳細画面に戻してください。</t>
+  </si>
+  <si>
+    <t>はい、問題ありません。入力内容（old値）を保持して登録フォームに戻してください。</t>
+  </si>
+  <si>
+    <t>はい、問題ありません。入力内容（old値）を保持して編集フォームに戻してください。</t>
+  </si>
+  <si>
+    <t>はい、ご認識の通りです。レビュー投稿フォームは書籍詳細画面（PG02）内に埋め込まれているため、独立した投稿画面は使用しません。</t>
+  </si>
+  <si>
+    <t>はい、ご認識の通りです。お気に入り操作はボタン押下によるトグル処理（または非同期/リダイレクト）で行うため、独立した登録画面は使用しません。</t>
+  </si>
+  <si>
+    <t>はい、問題ありません。入力内容（old値）を保持して作成フォームに戻してください。</t>
+  </si>
+  <si>
+    <t>はい、未認証アクセス時はログイン画面（/login）へリダイレクトしてください。</t>
+  </si>
+  <si>
+    <t>お気に入り操作は画面リダイレクト/トグル処理を行います。成功時のメッセージ表示は不要（または画面上の表示切替のみ）で問題ありません。</t>
+  </si>
+  <si>
+    <t>いいね操作はトグル処理のため、成功メッセージは不要（いいね数の即時反映/トグル表示のみ）で問題ありません。</t>
+  </si>
+  <si>
+    <t>はい、ご認識の通り全認証ユーザーがジャンル編集可能です。</t>
+  </si>
+  <si>
+    <t>はい、ご認識の通りです。UI画面は存在せず、Console Command / Schedule 経由でバックグラウンド実行されます。</t>
+  </si>
+  <si>
+    <t>はい、公開APIとして認証認可なしで取得可能です。</t>
+  </si>
+  <si>
+    <t>はい、BookPolicy により他ユーザーの書籍編集アクセスは 403 Forbidden を返してください。</t>
+  </si>
+  <si>
+    <t>はい、ReviewPolicy により他ユーザーのレビュー編集アクセスは 403 Forbidden を返してください。</t>
+  </si>
+  <si>
+    <t>はい、403 Forbidden とともに { "error": "この操作を実行する権限がありません。" } のJSONを返してください。</t>
+  </si>
+  <si>
+    <t>はい、ReadingPlanPolicy により他ユーザーの計画編集アクセスは 403 Forbidden を返してください。（なお、完了済み completed 計画の編集も 403 となります）</t>
+  </si>
+  <si>
+    <t>はい、size:13 による13桁チェックおよび unique:books,isbn による一意性チェックが必要です。エラーメッセージは「ISBNは13桁で入力してください。」「そのISBNは既に使用されています。」としてください。</t>
+  </si>
+  <si>
+    <t>はい、Rule::unique('books')-&gt;ignore($this-&gt;book) により自身のレコードを除外する設計で問題ありません。</t>
+  </si>
+  <si>
+    <t>仕様上、同一ユーザーが同一書籍に対して複数回レビューを投稿することは可能です。</t>
+  </si>
+  <si>
+    <t>はい、いいね機能はトグル処理（review_likesテーブルの追加/解除）として動作します。</t>
+  </si>
+  <si>
+    <t>同一ユーザー×同一書籍で in_progress 状態の計画が既に存在する場合は新規作成不可（バリデーションエラー「この書籍は既に進行中の読書計画が存在します。」）とし、completed 後の再計画は許可します。</t>
+  </si>
+  <si>
+    <t>回答済み</t>
+    <rPh sb="0" eb="2">
+      <t xml:space="preserve">ミカン </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>バリデーション/バリデーションメッエラーセージ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>キーワードは任意・最大255文字で設計しましたが、この制約で合っていますか？
+また、エラーメッセージは「キーワードは255文字以内で入力してください。」としましたがよろしいですか？</t>
+    <rPh sb="6" eb="8">
+      <t>ニn</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>サイダイ</t>
+    </rPh>
+    <rPh sb="61" eb="63">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="63" eb="65">
+      <t>イナイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Q-65</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Q-65にて回答済み</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ISBNは13桁固定で一意性チェック(自信を除外)も入れる想定ですが、桁数チェックは必要ですか？
+→Q-65と同様のエラーメッセージでよろしいですか？</t>
+    <rPh sb="19" eb="21">
+      <t>ジシn</t>
+    </rPh>
+    <rPh sb="55" eb="57">
+      <t>ドウヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ISBNは13桁固定で一意性チェックも入れる想定ですが、桁数チェックは必要ですか？
+エラーメッセージは「422 ValidationException」にて、Q-65と同様のエラーメッセージでよろしいですか？</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ISBNは13桁固定で一意性チェック(自信を除外)も入れる想定ですが、桁数チェックは必要ですか？
+エラーメッセージは「422 ValidationException」にて、Q-65と同様のエラーメッセージでよろしいですか？</t>
+    <rPh sb="19" eb="21">
+      <t>ジシn</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>画像URLは任意・最大255文字で設計しましたが、この制約で合っていますか？
+また、エラーメッセージは「画像URLは255文字以内で入力してください。」としましたがよろしいですか？</t>
+    <rPh sb="1" eb="3">
+      <t>ニn</t>
+    </rPh>
+    <rPh sb="3" eb="10">
+      <t>ヒッス</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ニn</t>
+    </rPh>
+    <rPh sb="11" eb="15">
+      <t>サイダイ</t>
+    </rPh>
+    <rPh sb="52" eb="54">
+      <t>_x0000__x0001__x0002_</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>説明は任意・最大255文字で設計しましたが、この制約で合っていますか？
+また、エラーメッセージは「説明は255文字以内で入力してください。」としましたがよろしいですか？</t>
+    <rPh sb="3" eb="5">
+      <t>ニn</t>
+    </rPh>
+    <rPh sb="5" eb="12">
+      <t>ヒッス</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ニn</t>
+    </rPh>
+    <rPh sb="13" eb="17">
+      <t>サイダイ</t>
+    </rPh>
+    <rPh sb="49" eb="51">
+      <t>セツメイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ジャンル名は必須・最大255文字・一意性チェックを入れる想定ですが、この制約で合っていますか？
+また、エラーメッセージは「ジャンル名は入力必須です。」「ジャンル名は255文字以内で入力してください。」「既に使用されているジャンル名です。」としましたがよろしいですか？</t>
+    <rPh sb="6" eb="8">
+      <t>ヒッス</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>サイダイ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="17" eb="20">
+      <t>１イ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>イレ</t>
+    </rPh>
+    <rPh sb="101" eb="102">
+      <t xml:space="preserve">スデニ </t>
+    </rPh>
+    <rPh sb="103" eb="105">
+      <t>シヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>著者は必須・最大255文字で設計しましたが、この制約で合っていますか？
+また、エラーメッセージは「著者は入力必須です。」「著者は255文字以内で入力してください。」としましたがよろしいですか？</t>
+    <rPh sb="5" eb="12">
+      <t>ヒッス</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ニn</t>
+    </rPh>
+    <rPh sb="13" eb="17">
+      <t>サイダイ</t>
+    </rPh>
+    <rPh sb="49" eb="51">
+      <t>チョ_x0000__x0005__x0007_</t>
+    </rPh>
+    <rPh sb="61" eb="63">
+      <t/>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>タイトルは必須・最大255文字で設計しましたが、この制約で合っていますか？
+また、エラーメッセージは「タイトルは入力必須です。」「タイトルは255文字以内で入力してください。」としましたがよろしいですか？</t>
+    <rPh sb="5" eb="12">
+      <t>ヒッス</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ニn</t>
+    </rPh>
+    <rPh sb="13" eb="17">
+      <t>サイダイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ジャンル名は必須・最大255文字・一意性チェック(自信を除外)を入れる想定ですが、この制約で合っていますか？
+また、エラーメッセージは「ジャンル名は入力必須です。」「ジャンル名は255文字以内で入力してください。」「既に使用されているジャンル名です。」としましたがよろしいですか？</t>
+    <rPh sb="6" eb="8">
+      <t>ヒッス</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>サイダイ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="17" eb="20">
+      <t>１イ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>ジシn</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>イレ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>APIでの一覧取得のページネーションの最大表示数は100件としましたが、この制約で合っていますか？
+エラーメッセージは「422 ValidationException」にて、「ページネーションの最大表示件数は100件です。」としましたがよろしいですか？
+また、デフォルトのページネーションは何件としますか？</t>
+    <rPh sb="5" eb="7">
+      <t>イチラn</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>シュトク</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>キノウ</t>
+    </rPh>
+    <rPh sb="97" eb="103">
+      <t>サイダイ</t>
+    </rPh>
+    <rPh sb="107" eb="108">
+      <t>ケn</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>キーワードは任意・最大255文字で設計しましたが、この制約で合っていますか？
+エラーメッセージは「422 ValidationException」にて、「キーワードは255文字以内で入力してください。」としましたがよろしいですか？</t>
+    <rPh sb="6" eb="8">
+      <t>ニn</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>サイダイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>タイトルは必須・最大255文字で設計しましたが、この制約で合っていますか？
+エラーメッセージは「422 ValidationException」にて、「タイトルは入力必須です。」「タイトルは255文字以内で入力してください。」としましたがよろしいですか？</t>
+    <rPh sb="5" eb="12">
+      <t>ヒッス</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ニn</t>
+    </rPh>
+    <rPh sb="13" eb="17">
+      <t>サイダイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ISBNは入力は必須ですか？
+エラーメッセージは「422 ValidationException」にて、「ISBNは入力必須です。」としましたがよろしいですか？</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>著者は必須・最大255文字で設計しましたが、この制約で合っていますか？
+エラーメッセージは「422 ValidationException」にて、「筆者は入力必須です。」「筆者は255文字以内で入力してください。」としましたがよろしいですか？</t>
+    <rPh sb="5" eb="12">
+      <t>ヒッス</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ニ_x0000_</t>
+    </rPh>
+    <rPh sb="13" eb="17">
+      <t>_x0005__x0007__x0003__x000C_</t>
+    </rPh>
+    <rPh sb="74" eb="76">
+      <t xml:space="preserve">_x0001__x0005__x000D__x0004_	</t>
+    </rPh>
+    <rPh sb="76" eb="77">
+      <t/>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ISBNは入力は必須ですか？
+エラーメッセージは「ISBNは入力必須です。」としましたがよろしいですか？</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ジャンルは任意・登録されたジャンルのみ検索可能で設計しましたが、この制約で合っていますか？
+エラーメッセージは「422 ValidationException」にて、「登録されたジャンルのみ検索可能です。」としましたがよろしいですか？</t>
+    <rPh sb="6" eb="8">
+      <t>ニn</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="19" eb="23">
+      <t>ケンサク</t>
+    </rPh>
+    <rPh sb="84" eb="86">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="95" eb="97">
+      <t>ケンサク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ジャンルは任意・登録されたジャンルのみ選択可能で設計しましたが、この制約で合っていますか？
+エラーメッセージは「422 ValidationException」にて、「登録されたジャンルのみ選択可能です。」としましたがよろしいですか？</t>
+    <rPh sb="0" eb="6">
+      <t>ヒッス</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ニn</t>
+    </rPh>
+    <rPh sb="7" eb="11">
+      <t>サイダイ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>🧺</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>カノウ</t>
+    </rPh>
+    <rPh sb="84" eb="86">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ジャンルは任意・登録されたジャンルのみ選択可能で設計しましたが、この制約で合っていますか？
+また、エラーメッセージは「登録されたジャンルのみ選択可能です。」としましたがよろしいですか？</t>
+    <rPh sb="0" eb="6">
+      <t>ヒッス</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ニn</t>
+    </rPh>
+    <rPh sb="7" eb="11">
+      <t>サイダイ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>🧺</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>カノウ</t>
+    </rPh>
+    <rPh sb="59" eb="61">
+      <t>トウロクサレテ</t>
+    </rPh>
+    <rPh sb="70" eb="72">
+      <t>センタク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ジャンルは任意・登録されたジャンルのみ検索可能で設計しましたが、この制約で合っていますか？
+また、エラーメッセージは「登録されたジャンルのみ検索可能です。」としましたがよろしいですか？</t>
+    <rPh sb="6" eb="8">
+      <t>ニn</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="19" eb="23">
+      <t>ケンサク</t>
+    </rPh>
+    <rPh sb="59" eb="61">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="70" eb="74">
+      <t>ケンサク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ソート順は任意・「newest,oldest,rating,title」のみ選択可能で設計しましたが、この制約で合っていますか？
+また、エラーメッセージは「新しい順、古い順、評価順、タイトル順のいずれかを選択してください。」としましたがよろしいですか？</t>
+    <rPh sb="38" eb="40">
+      <t>センタク</t>
+    </rPh>
+    <rPh sb="110" eb="112">
+      <t>センタク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>評価は必須・「1,2,3,4,5」のみ選択可能で設計しましたが、この制約で合っていますか？
+また、エラーメッセージは「評価は入力必須です。」「評価は1、2、3、4、5のいずれかを選択してください。」としましたがよろしいですか？</t>
+    <rPh sb="0" eb="2">
+      <t>ヒョウ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ヒッス</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ニn</t>
+    </rPh>
+    <rPh sb="4" eb="7">
+      <t>サイダイ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>カノウ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>セッケイ</t>
+    </rPh>
+    <rPh sb="44" eb="46">
+      <t>トウコウ</t>
+    </rPh>
+    <rPh sb="47" eb="51">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="59" eb="61">
+      <t>ヒョウカ</t>
+    </rPh>
+    <rPh sb="71" eb="73">
+      <t>ヒョウカ</t>
+    </rPh>
+    <rPh sb="89" eb="91">
+      <t>センタク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>レビュー投稿は必須・最大255文字で設計しましたが、この制約で合っていますか？
+また、エラーメッセージは「レビュー投稿は入力必須です。」「レビュー投稿は255文字以内で入力してください。」としましたがよろしいですか？</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>出版日は任意・日付形式必須(YYYY-mm-dd)で設計しましたが、この制約で合っていますか？
+また、エラーメッセージは「日付はYYYY-mm-ddで入力してください。」としましたがよろしいですか？</t>
+    <rPh sb="1" eb="3">
+      <t>ニn</t>
+    </rPh>
+    <rPh sb="3" eb="7">
+      <t>ヒッス</t>
+    </rPh>
+    <rPh sb="7" eb="11">
+      <t>ヒヅケ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ヒッス</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>サイダイ</t>
+    </rPh>
+    <rPh sb="58" eb="60">
+      <t>セツメイ</t>
+    </rPh>
+    <rPh sb="61" eb="63">
+      <t>ヒヅケ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>対象書籍は必須・登録された書籍のみ選択可能で設計しましたが、この制約で合っていますか？
+また、エラーメッセージは「書籍は選択必須です。」「登録された書籍のみ選択可能です。」としましたがよろしいですか？</t>
+    <rPh sb="0" eb="2">
+      <t>タイショウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ショセキ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ヒッス</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>sy</t>
+    </rPh>
+    <rPh sb="17" eb="21">
+      <t>センタク</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>セッケイ</t>
+    </rPh>
+    <rPh sb="57" eb="59">
+      <t>sy</t>
+    </rPh>
+    <rPh sb="60" eb="62">
+      <t>センタク</t>
+    </rPh>
+    <rPh sb="74" eb="76">
+      <t>sy</t>
+    </rPh>
+    <rPh sb="92" eb="93">
+      <t xml:space="preserve">スデニ </t>
+    </rPh>
+    <rPh sb="94" eb="96">
+      <t>シヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>★ PG16/★ PG17</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>★ 読書計画作成画面/★ 読書計画編集画面</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ページ番号は任意・最小値1で設計しましたが、この制約で合っていますか？
+エラーメッセージは「422 ValidationException」にて、「ページ番号は1以上で入力してください。」としましたがよろしいですか？</t>
+    <rPh sb="3" eb="5">
+      <t>バンゴウ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>サイセィオ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>🩸</t>
+    </rPh>
+    <rPh sb="81" eb="83">
+      <t>イジョウ</t>
+    </rPh>
+    <rPh sb="84" eb="86">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Q-333</t>
+  </si>
+  <si>
+    <t>Q-334</t>
+  </si>
+  <si>
+    <t>Q-335</t>
+  </si>
+  <si>
+    <t>Q-336</t>
+  </si>
+  <si>
+    <t>Q-337</t>
+  </si>
+  <si>
+    <t>Q-338</t>
+  </si>
+  <si>
+    <t>Q-339</t>
+  </si>
+  <si>
+    <t>Q-340</t>
+  </si>
+  <si>
+    <t>ログイン画面</t>
+    <rPh sb="4" eb="6">
+      <t>ガメn</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>メールアドレスは必須・文字列の想定(Fortify標準)ですが、この制約で合っていますか？
+また、エラーメッセージは「メールアドレスは入力必須です。」「文字列で入力してください。」としましたがよろしいですか？</t>
+    <rPh sb="8" eb="10">
+      <t>ヒッス</t>
+    </rPh>
+    <rPh sb="11" eb="14">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>ヒョウジュn</t>
+    </rPh>
+    <rPh sb="76" eb="79">
+      <t>モジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>パスワードは必須の想定(Fortify標準)ですが、この制約で合っていますか？
+また、エラーメッセージは「パスワードは入力必須です。」としましたがよろしいですか？</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>会員登録画面</t>
+    <rPh sb="4" eb="6">
+      <t>ガメnガメn</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>お名前は必須・最大255文字の想定(Fortify標準)ですが、この制約で合っていますか？
+また、エラーメッセージは「お名前は入力必須です。」「お名前は255文字以内で入力してください。」としましたがよろしいですか？</t>
+    <rPh sb="1" eb="3">
+      <t>ヒッス</t>
+    </rPh>
+    <rPh sb="4" eb="7">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ヒョウジュn</t>
+    </rPh>
+    <rPh sb="65" eb="68">
+      <t>モジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>メールアドレスは必須・メール形式・最大255文字・一意性チェックの想定(Fortify標準)ですが、この制約で合っていますか？
+また、エラーメッセージは「メールアドレスは入力必須です。」「メールアドレスはメール形式で入力してください。」「メールアドレスは255文字以内で入力してください。」「既に使用されているメールアドレスです。」としましたがよろしいですか？</t>
+    <rPh sb="8" eb="11">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="25" eb="28">
+      <t>１イ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>ヒョウジュn</t>
+    </rPh>
+    <rPh sb="87" eb="90">
+      <t>モジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>パスワード/パスワード確認は必須・8文字以上・確認一致の想定(Fortify標準)ですが、この制約で合っていますか？
+また、エラーメッセージは「パスワードは入力必須です。」「パスワードは8文字以上で入力してください」「パスワードと一致しません」としましたがよろしいですか？</t>
+    <rPh sb="14" eb="17">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="18" eb="22">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>カクニ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>イッティ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>ヒョウジュn</t>
+    </rPh>
+    <rPh sb="80" eb="83">
+      <t>モジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>画像URLは任意・最大255文字で設計しましたが、この制約で合っていますか？
+エラーメッセージは「422 ValidationException」にて、「画像URLは255文字以内で入力してください。」としましたがよろしいですか？</t>
+    <rPh sb="1" eb="3">
+      <t>ニn</t>
+    </rPh>
+    <rPh sb="3" eb="10">
+      <t>ヒッス</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ニn</t>
+    </rPh>
+    <rPh sb="11" eb="15">
+      <t>サイダイ</t>
+    </rPh>
+    <rPh sb="77" eb="79">
+      <t>ガゾウ</t>
+    </rPh>
+    <rPh sb="82" eb="84">
+      <t/>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>説明は任意・最大255文字で設計しましたが、この制約で合っていますか？
+エラーメッセージは「422 ValidationException」にて、「説明は255文字以内で入力してください。」としましたがよろしいですか？</t>
+    <rPh sb="3" eb="5">
+      <t>ニn</t>
+    </rPh>
+    <rPh sb="5" eb="12">
+      <t>ヒッス</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ニn</t>
+    </rPh>
+    <rPh sb="13" eb="17">
+      <t>サイダイ</t>
+    </rPh>
+    <rPh sb="74" eb="76">
+      <t>セツメイ</t>
+    </rPh>
+    <rPh sb="76" eb="78">
+      <t/>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>期日は必須・日付形式必須(YYYY-mm-dd)で設計しましたが、この制約で合っていますか？
+また、エラーメッセージは「期日は入力必須です。」「期日はYYYY-mm-ddで入力してください。」としましたがよろしいですか？</t>
+    <rPh sb="0" eb="2">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="2" eb="6">
+      <t>ヒッス</t>
+    </rPh>
+    <rPh sb="6" eb="10">
+      <t>ヒヅケ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ヒッス</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>サイダイ</t>
+    </rPh>
+    <rPh sb="57" eb="59">
+      <t>セツメイ</t>
+    </rPh>
+    <rPh sb="60" eb="62">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="63" eb="65">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> 読書計画編集画面の表示の際、未認証の場合のリダイレクト先が機能要件に存在しません。
+リダイレクト先はログイン画面でよろしいですか？</t>
+    <rPh sb="5" eb="7">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>OK</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>削除処理完了後は、「レビューを削除しました。」のフラッシュメッセージとともに書籍詳細画面（/books/{book}）へリダイレクト（再読み込み）してください。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>はい、「書籍を削除しました。」のフラッシュメッセージとともに書籍一覧画面（/）へリダイレクトしてください。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>いいえ。書籍登録成功後は、「書籍を登録しました。」のフラッシュメッセージとともに登録した【書籍詳細画面（/books/{book}）】へリダイレクトしてください。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>はい、問題ありません。入力内容（old値）を保持して登録フォームに戻してください。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>はい、「書籍情報を更新しました。」のフラッシュメッセージとともに書籍詳細画面（/books/{book}）へリダイレクトしてください。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>はい、問題ありません。入力内容（old値）を保持して編集フォームに戻してください。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>はい、「レビューを更新しました。」のフラッシュメッセージとともに該当書籍の詳細画面（/books/{book}）へリダイレクトしてください。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>はい、「ジャンルを削除しました。」のフラッシュメッセージとともにジャンル一覧画面（/genres）へリダイレクトしてください。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>はい、「ジャンルを作成しました。」のフラッシュメッセージとともにジャンル一覧画面（/genres）へリダイレクトしてください。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>はい、「ジャンルを更新しました。」のフラッシュメッセージとともにジャンル一覧画面（/genres）へリダイレクトしてください。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>はい、問題ありません。エラー時はパラメータをクリアまたは保持して一覧画面に戻してください。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>はい、「読書計画を完了しました。」のフラッシュメッセージとともに読書計画一覧画面（/reading-plans）へリダイレクトしてください。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>はい、「読書計画を削除しました。」のフラッシュメッセージとともに読書計画一覧画面（/reading-plans）へリダイレクトしてください。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>はい、「読書計画を作成しました。」のフラッシュメッセージとともに読書計画一覧画面（/reading-plans）へリダイレクトしてください。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>はい、「読書計画を更新しました。」のフラッシュメッセージとともに読書計画一覧画面（/reading-plans）へリダイレクトしてください。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>はい、「通知を既読にしました。」のフラッシュメッセージとともに通知一覧画面（/notifications）へリダイレクトしてください。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>はい、クエリパラメータの不正時はデフォルト検索条件（または全件表示）で一覧画面を表示してください。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ランキング画面は公開ページのためリダイレクトは行わず、未認証のまま閲覧可能としてください。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>成功時は「レビューを投稿しました。」と表示してください。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>成功時は「レビューを削除しました。」と表示してください。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>成功時は「書籍を削除しました。」と表示してください。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>成功時は「書籍を登録しました。」と表示してください。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>はい。13桁でない場合は400「ISBNは13桁で入力してください。」、見つからない場合は404「書籍が見つかりませんでした。」、クォータ超過は429、通信エラーは500メッセージを返してください。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>成功時は「書籍情報を更新しました。」と表示してください。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>成功時は「レビューを更新しました。」と表示してください。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>成功時は「ジャンルを削除しました。」と表示してください。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>書籍が紐付いている場合は削除を拒否し、「このジャンルには書籍が紐付いているため削除できません。」と表示してください。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>成功時は「ジャンルを作成しました。」と表示してください。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>成功時は「ジャンルを更新しました。」と表示してください。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>成功時は「読書計画を完了しました。」と表示してください。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>成功時は「読書計画を削除しました。」と表示してください。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>成功時は「読書計画を作成しました。」と表示してください。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>成功時は「読書計画を更新しました。」と表示してください。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>成功時は「通知を既読にしました。」と表示してください。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>設計への反映</t>
+    <rPh sb="0" eb="1">
+      <t>セッケイヘノヘ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>はい、ご認識の通り全認証ユーザーがジャンル操作可能です（特定所有者チェックは不要です）。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ランキングはレビュー平均評価TOP10を表示し、レビューのない書籍は非表示とします。なお、ゲストユーザーも閲覧可能です。</t>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1643,8 +3339,17 @@
       <family val="2"/>
       <charset val="128"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1663,8 +3368,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -1687,13 +3398,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1720,6 +3442,21 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2083,7 +3820,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{833B9C12-88F9-F440-902B-BDAD178A24F6}">
-  <dimension ref="A2:G102"/>
+  <dimension ref="A1:H342"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
     <col min="2" max="2" width="28.85546875" customWidth="1"/>
@@ -2092,15 +3829,18 @@
     <col min="5" max="6" width="60.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:7">
+    <row r="1" spans="1:8">
+      <c r="H1" s="13"/>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D2" s="5" t="s">
         <v>13</v>
@@ -2114,16 +3854,19 @@
       <c r="G2" s="2" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" ht="42">
+      <c r="H2" s="12" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="42">
       <c r="A3" s="3" t="s">
         <v>15</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>3</v>
@@ -2131,20 +3874,25 @@
       <c r="E3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="4"/>
-      <c r="G3" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="42">
+      <c r="F3" s="4" t="s">
+        <v>484</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>510</v>
+      </c>
+      <c r="H3" s="11" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="42">
       <c r="A4" s="3" t="s">
         <v>22</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>4</v>
@@ -2152,20 +3900,25 @@
       <c r="E4" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="4"/>
-      <c r="G4" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="42">
+      <c r="F4" s="4" t="s">
+        <v>485</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>510</v>
+      </c>
+      <c r="H4" s="11" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="42">
       <c r="A5" s="3" t="s">
         <v>23</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>3</v>
@@ -2173,20 +3926,25 @@
       <c r="E5" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="F5" s="4"/>
-      <c r="G5" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="42">
+      <c r="F5" s="4" t="s">
+        <v>486</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>510</v>
+      </c>
+      <c r="H5" s="11" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="42">
       <c r="A6" s="3" t="s">
         <v>24</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>4</v>
@@ -2194,41 +3952,51 @@
       <c r="E6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F6" s="4"/>
-      <c r="G6" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="42">
+      <c r="F6" s="4" t="s">
+        <v>487</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>510</v>
+      </c>
+      <c r="H6" s="11" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="63">
       <c r="A7" s="3" t="s">
         <v>25</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="E7" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F7" s="4"/>
-      <c r="G7" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="63">
+      <c r="F7" s="4" t="s">
+        <v>488</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>510</v>
+      </c>
+      <c r="H7" s="11" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="63">
       <c r="A8" s="3" t="s">
         <v>26</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>10</v>
@@ -2236,20 +4004,25 @@
       <c r="E8" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F8" s="4"/>
-      <c r="G8" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="42">
+      <c r="F8" s="4" t="s">
+        <v>489</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>510</v>
+      </c>
+      <c r="H8" s="11" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="63">
       <c r="A9" s="3" t="s">
         <v>27</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>10</v>
@@ -2257,62 +4030,77 @@
       <c r="E9" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F9" s="4"/>
-      <c r="G9" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="42">
+      <c r="F9" s="4" t="s">
+        <v>562</v>
+      </c>
+      <c r="G9" s="9" t="s">
+        <v>510</v>
+      </c>
+      <c r="H9" s="11" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="42">
       <c r="A10" s="3" t="s">
         <v>28</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>10</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="F10" s="4"/>
-      <c r="G10" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="63">
+        <v>184</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>563</v>
+      </c>
+      <c r="G10" s="9" t="s">
+        <v>510</v>
+      </c>
+      <c r="H10" s="11" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="63">
       <c r="A11" s="3" t="s">
         <v>29</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>17</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="F11" s="4"/>
-      <c r="G11" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="42">
+        <v>183</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>564</v>
+      </c>
+      <c r="G11" s="9" t="s">
+        <v>510</v>
+      </c>
+      <c r="H11" s="11" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="42">
       <c r="A12" s="3" t="s">
         <v>30</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>17</v>
@@ -2320,20 +4108,25 @@
       <c r="E12" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="F12" s="4"/>
-      <c r="G12" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="63">
+      <c r="F12" s="4" t="s">
+        <v>565</v>
+      </c>
+      <c r="G12" s="9" t="s">
+        <v>510</v>
+      </c>
+      <c r="H12" s="11" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="63">
       <c r="A13" s="3" t="s">
         <v>31</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>20</v>
@@ -2341,20 +4134,25 @@
       <c r="E13" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="F13" s="4"/>
-      <c r="G13" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="42">
+      <c r="F13" s="4" t="s">
+        <v>566</v>
+      </c>
+      <c r="G13" s="9" t="s">
+        <v>510</v>
+      </c>
+      <c r="H13" s="11" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="42">
       <c r="A14" s="3" t="s">
         <v>32</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>20</v>
@@ -2362,1533 +4160,4845 @@
       <c r="E14" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F14" s="4"/>
-      <c r="G14" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="63">
+      <c r="F14" s="4" t="s">
+        <v>567</v>
+      </c>
+      <c r="G14" s="9" t="s">
+        <v>510</v>
+      </c>
+      <c r="H14" s="11" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="63">
       <c r="A15" s="3" t="s">
         <v>33</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D15" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="E15" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="E15" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="F15" s="4"/>
-      <c r="G15" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="42">
+      <c r="F15" s="4" t="s">
+        <v>568</v>
+      </c>
+      <c r="G15" s="9" t="s">
+        <v>510</v>
+      </c>
+      <c r="H15" s="11" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="42">
       <c r="A16" s="3" t="s">
         <v>34</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="F16" s="4"/>
-      <c r="G16" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="42">
+        <v>122</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>491</v>
+      </c>
+      <c r="G16" s="9" t="s">
+        <v>510</v>
+      </c>
+      <c r="H16" s="11" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="42">
       <c r="A17" s="3" t="s">
         <v>35</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D17" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="E17" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="E17" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="F17" s="4"/>
-      <c r="G17" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="42">
+      <c r="F17" s="4" t="s">
+        <v>492</v>
+      </c>
+      <c r="G17" s="9" t="s">
+        <v>510</v>
+      </c>
+      <c r="H17" s="11" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="63">
       <c r="A18" s="3" t="s">
         <v>36</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D18" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="E18" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="E18" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="F18" s="4"/>
-      <c r="G18" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="63">
+      <c r="F18" s="4" t="s">
+        <v>493</v>
+      </c>
+      <c r="G18" s="9" t="s">
+        <v>510</v>
+      </c>
+      <c r="H18" s="11" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="63">
       <c r="A19" s="3" t="s">
         <v>37</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D19" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="E19" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="E19" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="F19" s="4"/>
-      <c r="G19" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="42">
+      <c r="F19" s="4" t="s">
+        <v>569</v>
+      </c>
+      <c r="G19" s="9" t="s">
+        <v>510</v>
+      </c>
+      <c r="H19" s="11" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="42">
       <c r="A20" s="3" t="s">
         <v>38</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D20" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="E20" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="E20" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="F20" s="4"/>
-      <c r="G20" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="63">
+      <c r="F20" s="4" t="s">
+        <v>490</v>
+      </c>
+      <c r="G20" s="9" t="s">
+        <v>510</v>
+      </c>
+      <c r="H20" s="11" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="63">
       <c r="A21" s="3" t="s">
         <v>39</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="F21" s="4"/>
-      <c r="G21" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="42">
+        <v>181</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>570</v>
+      </c>
+      <c r="G21" s="9" t="s">
+        <v>510</v>
+      </c>
+      <c r="H21" s="11" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="42">
       <c r="A22" s="3" t="s">
         <v>40</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D22" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="E22" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="E22" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="F22" s="4"/>
-      <c r="G22" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="63">
+      <c r="F22" s="4" t="s">
+        <v>491</v>
+      </c>
+      <c r="G22" s="9" t="s">
+        <v>510</v>
+      </c>
+      <c r="H22" s="11" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="63">
       <c r="A23" s="3" t="s">
         <v>41</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="F23" s="4"/>
-      <c r="G23" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="42">
+        <v>182</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>571</v>
+      </c>
+      <c r="G23" s="9" t="s">
+        <v>510</v>
+      </c>
+      <c r="H23" s="11" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="42">
       <c r="A24" s="3" t="s">
         <v>42</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D24" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="E24" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="E24" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="F24" s="4"/>
-      <c r="G24" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="63">
+      <c r="F24" s="4" t="s">
+        <v>572</v>
+      </c>
+      <c r="G24" s="9" t="s">
+        <v>510</v>
+      </c>
+      <c r="H24" s="11" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="63">
       <c r="A25" s="3" t="s">
         <v>43</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="F25" s="4"/>
-      <c r="G25" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="63">
+        <v>135</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>573</v>
+      </c>
+      <c r="G25" s="9" t="s">
+        <v>510</v>
+      </c>
+      <c r="H25" s="11" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="63">
       <c r="A26" s="3" t="s">
         <v>44</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="F26" s="4"/>
-      <c r="G26" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="42">
+        <v>136</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="G26" s="9" t="s">
+        <v>510</v>
+      </c>
+      <c r="H26" s="11" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="42">
       <c r="A27" s="3" t="s">
         <v>45</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D27" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="E27" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="E27" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="F27" s="4"/>
-      <c r="G27" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="63">
+      <c r="F27" s="4" t="s">
+        <v>494</v>
+      </c>
+      <c r="G27" s="9" t="s">
+        <v>510</v>
+      </c>
+      <c r="H27" s="11" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="63">
       <c r="A28" s="3" t="s">
         <v>46</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="F28" s="4"/>
-      <c r="G28" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="63">
+        <v>139</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>575</v>
+      </c>
+      <c r="G28" s="9" t="s">
+        <v>510</v>
+      </c>
+      <c r="H28" s="11" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="63">
       <c r="A29" s="3" t="s">
         <v>47</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="F29" s="4"/>
-      <c r="G29" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" ht="42">
+        <v>560</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>495</v>
+      </c>
+      <c r="G29" s="9" t="s">
+        <v>510</v>
+      </c>
+      <c r="H29" s="11" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="42">
       <c r="A30" s="3" t="s">
         <v>48</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D30" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="E30" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="E30" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="F30" s="4"/>
-      <c r="G30" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" ht="63">
+      <c r="F30" s="4" t="s">
+        <v>491</v>
+      </c>
+      <c r="G30" s="9" t="s">
+        <v>510</v>
+      </c>
+      <c r="H30" s="11" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="63">
       <c r="A31" s="3" t="s">
         <v>49</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="F31" s="4"/>
-      <c r="G31" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" ht="63">
+        <v>142</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>576</v>
+      </c>
+      <c r="G31" s="9" t="s">
+        <v>510</v>
+      </c>
+      <c r="H31" s="11" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="63">
       <c r="A32" s="3" t="s">
         <v>50</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="F32" s="4"/>
-      <c r="G32" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" ht="63">
+        <v>144</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>495</v>
+      </c>
+      <c r="G32" s="9" t="s">
+        <v>510</v>
+      </c>
+      <c r="H32" s="11" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="63">
       <c r="A33" s="3" t="s">
         <v>51</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D33" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="E33" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="E33" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="F33" s="4"/>
-      <c r="G33" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" ht="42">
+      <c r="F33" s="4" t="s">
+        <v>577</v>
+      </c>
+      <c r="G33" s="9" t="s">
+        <v>510</v>
+      </c>
+      <c r="H33" s="11" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="42">
       <c r="A34" s="3" t="s">
         <v>52</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="F34" s="4"/>
-      <c r="G34" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" ht="84">
+        <v>164</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>578</v>
+      </c>
+      <c r="G34" s="9" t="s">
+        <v>510</v>
+      </c>
+      <c r="H34" s="11" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" ht="84">
       <c r="A35" s="3" t="s">
         <v>53</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D35" s="4" t="s">
         <v>10</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="F35" s="4"/>
-      <c r="G35" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" ht="63">
+        <v>169</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>496</v>
+      </c>
+      <c r="G35" s="9" t="s">
+        <v>510</v>
+      </c>
+      <c r="H35" s="11" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="63">
       <c r="A36" s="3" t="s">
         <v>54</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D36" s="4" t="s">
         <v>10</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="F36" s="4"/>
-      <c r="G36" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" ht="63">
+        <v>170</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>580</v>
+      </c>
+      <c r="G36" s="9" t="s">
+        <v>510</v>
+      </c>
+      <c r="H36" s="11" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="63">
       <c r="A37" s="3" t="s">
         <v>55</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D37" s="4" t="s">
         <v>10</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="F37" s="4"/>
-      <c r="G37" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" ht="63">
+        <v>171</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>497</v>
+      </c>
+      <c r="G37" s="9" t="s">
+        <v>510</v>
+      </c>
+      <c r="H37" s="11" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="63">
       <c r="A38" s="3" t="s">
         <v>56</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D38" s="4" t="s">
         <v>10</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="F38" s="4"/>
-      <c r="G38" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" ht="63">
+        <v>172</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>581</v>
+      </c>
+      <c r="G38" s="9" t="s">
+        <v>510</v>
+      </c>
+      <c r="H38" s="11" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="63">
       <c r="A39" s="3" t="s">
         <v>57</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D39" s="4" t="s">
         <v>10</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="F39" s="4"/>
-      <c r="G39" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" ht="63">
+        <v>173</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>582</v>
+      </c>
+      <c r="G39" s="9" t="s">
+        <v>510</v>
+      </c>
+      <c r="H39" s="11" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" ht="63">
       <c r="A40" s="3" t="s">
         <v>58</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D40" s="4" t="s">
         <v>17</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="F40" s="4"/>
-      <c r="G40" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" ht="63">
+        <v>174</v>
+      </c>
+      <c r="F40" s="4" t="s">
+        <v>583</v>
+      </c>
+      <c r="G40" s="9" t="s">
+        <v>510</v>
+      </c>
+      <c r="H40" s="11" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" ht="63">
       <c r="A41" s="3" t="s">
         <v>59</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D41" s="4" t="s">
         <v>17</v>
       </c>
       <c r="E41" s="8" t="s">
-        <v>177</v>
-      </c>
-      <c r="F41" s="4"/>
-      <c r="G41" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" ht="63">
+        <v>175</v>
+      </c>
+      <c r="F41" s="4" t="s">
+        <v>584</v>
+      </c>
+      <c r="G41" s="9" t="s">
+        <v>510</v>
+      </c>
+      <c r="H41" s="11" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" ht="63">
       <c r="A42" s="3" t="s">
         <v>60</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D42" s="4" t="s">
         <v>20</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="F42" s="4"/>
-      <c r="G42" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" ht="63">
+        <v>177</v>
+      </c>
+      <c r="F42" s="4" t="s">
+        <v>585</v>
+      </c>
+      <c r="G42" s="9" t="s">
+        <v>510</v>
+      </c>
+      <c r="H42" s="11" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" ht="63">
       <c r="A43" s="3" t="s">
         <v>61</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="F43" s="4"/>
-      <c r="G43" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" ht="63">
+        <v>178</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>586</v>
+      </c>
+      <c r="G43" s="9" t="s">
+        <v>510</v>
+      </c>
+      <c r="H43" s="11" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" ht="63">
       <c r="A44" s="3" t="s">
         <v>62</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="F44" s="4"/>
-      <c r="G44" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" ht="42">
+        <v>179</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>587</v>
+      </c>
+      <c r="G44" s="9" t="s">
+        <v>510</v>
+      </c>
+      <c r="H44" s="11" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" ht="42">
       <c r="A45" s="3" t="s">
         <v>63</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>224</v>
-      </c>
-      <c r="F45" s="4"/>
-      <c r="G45" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" ht="63">
+        <v>222</v>
+      </c>
+      <c r="F45" s="4" t="s">
+        <v>588</v>
+      </c>
+      <c r="G45" s="9" t="s">
+        <v>510</v>
+      </c>
+      <c r="H45" s="11" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" ht="63">
       <c r="A46" s="3" t="s">
         <v>64</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="F46" s="4"/>
-      <c r="G46" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" ht="63">
+        <v>180</v>
+      </c>
+      <c r="F46" s="4" t="s">
+        <v>589</v>
+      </c>
+      <c r="G46" s="9" t="s">
+        <v>510</v>
+      </c>
+      <c r="H46" s="11" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" ht="63">
       <c r="A47" s="3" t="s">
         <v>65</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="F47" s="4"/>
-      <c r="G47" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" ht="63">
+        <v>185</v>
+      </c>
+      <c r="F47" s="4" t="s">
+        <v>590</v>
+      </c>
+      <c r="G47" s="9" t="s">
+        <v>510</v>
+      </c>
+      <c r="H47" s="11" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" ht="63">
       <c r="A48" s="3" t="s">
         <v>66</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="F48" s="4"/>
-      <c r="G48" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" ht="63">
+        <v>186</v>
+      </c>
+      <c r="F48" s="4" t="s">
+        <v>591</v>
+      </c>
+      <c r="G48" s="9" t="s">
+        <v>510</v>
+      </c>
+      <c r="H48" s="11" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" ht="63">
       <c r="A49" s="3" t="s">
         <v>67</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>189</v>
-      </c>
-      <c r="F49" s="4"/>
-      <c r="G49" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" ht="63">
+        <v>187</v>
+      </c>
+      <c r="F49" s="4" t="s">
+        <v>592</v>
+      </c>
+      <c r="G49" s="9" t="s">
+        <v>510</v>
+      </c>
+      <c r="H49" s="11" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" ht="63">
       <c r="A50" s="3" t="s">
         <v>68</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="F50" s="4"/>
-      <c r="G50" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" ht="63">
+        <v>188</v>
+      </c>
+      <c r="F50" s="4" t="s">
+        <v>593</v>
+      </c>
+      <c r="G50" s="9" t="s">
+        <v>510</v>
+      </c>
+      <c r="H50" s="11" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" ht="63">
       <c r="A51" s="3" t="s">
         <v>69</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="F51" s="4"/>
-      <c r="G51" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" ht="63">
+        <v>189</v>
+      </c>
+      <c r="F51" s="4" t="s">
+        <v>594</v>
+      </c>
+      <c r="G51" s="9" t="s">
+        <v>510</v>
+      </c>
+      <c r="H51" s="11" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" ht="63">
       <c r="A52" s="3" t="s">
         <v>70</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="F52" s="4"/>
-      <c r="G52" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" ht="63">
+        <v>190</v>
+      </c>
+      <c r="F52" s="4" t="s">
+        <v>595</v>
+      </c>
+      <c r="G52" s="9" t="s">
+        <v>510</v>
+      </c>
+      <c r="H52" s="11" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" ht="63">
       <c r="A53" s="3" t="s">
         <v>71</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D53" s="4" t="s">
         <v>20</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="F53" s="4"/>
-      <c r="G53" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" ht="63">
+        <v>192</v>
+      </c>
+      <c r="F53" s="4" t="s">
+        <v>495</v>
+      </c>
+      <c r="G53" s="9" t="s">
+        <v>510</v>
+      </c>
+      <c r="H53" s="11" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" ht="63">
       <c r="A54" s="3" t="s">
         <v>72</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>196</v>
-      </c>
-      <c r="F54" s="4"/>
-      <c r="G54" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" ht="42">
+        <v>194</v>
+      </c>
+      <c r="F54" s="4" t="s">
+        <v>495</v>
+      </c>
+      <c r="G54" s="9" t="s">
+        <v>510</v>
+      </c>
+      <c r="H54" s="11" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" ht="42">
       <c r="A55" s="3" t="s">
         <v>73</v>
       </c>
       <c r="B55" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="D55" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="E55" s="4" t="s">
         <v>195</v>
       </c>
-      <c r="C55" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="D55" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="E55" s="4" t="s">
-        <v>197</v>
-      </c>
-      <c r="F55" s="4"/>
-      <c r="G55" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" ht="42">
+      <c r="F55" s="4" t="s">
+        <v>597</v>
+      </c>
+      <c r="G55" s="9" t="s">
+        <v>510</v>
+      </c>
+      <c r="H55" s="11" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" ht="42">
       <c r="A56" s="3" t="s">
         <v>74</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>198</v>
-      </c>
-      <c r="F56" s="4"/>
-      <c r="G56" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" ht="63">
+        <v>196</v>
+      </c>
+      <c r="F56" s="4" t="s">
+        <v>498</v>
+      </c>
+      <c r="G56" s="9" t="s">
+        <v>510</v>
+      </c>
+      <c r="H56" s="11" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" ht="63">
       <c r="A57" s="3" t="s">
         <v>75</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="F57" s="4"/>
-      <c r="G57" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" ht="63">
+        <v>197</v>
+      </c>
+      <c r="F57" s="4" t="s">
+        <v>598</v>
+      </c>
+      <c r="G57" s="9" t="s">
+        <v>510</v>
+      </c>
+      <c r="H57" s="10" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" ht="63">
       <c r="A58" s="3" t="s">
         <v>76</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C58" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="D58" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="E58" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="D58" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="E58" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="F58" s="4"/>
-      <c r="G58" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" ht="63">
+      <c r="F58" s="4" t="s">
+        <v>579</v>
+      </c>
+      <c r="G58" s="9" t="s">
+        <v>510</v>
+      </c>
+      <c r="H58" s="10" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" ht="63">
       <c r="A59" s="3" t="s">
         <v>77</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="F59" s="4"/>
-      <c r="G59" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" ht="21">
+        <v>207</v>
+      </c>
+      <c r="F59" s="4" t="s">
+        <v>499</v>
+      </c>
+      <c r="G59" s="9" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" ht="21">
       <c r="A60" s="3" t="s">
         <v>78</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="D60" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="E60" s="4" t="s">
         <v>208</v>
       </c>
-      <c r="E60" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="F60" s="4"/>
-      <c r="G60" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" ht="21">
+      <c r="F60" s="4" t="s">
+        <v>500</v>
+      </c>
+      <c r="G60" s="9" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" ht="21">
       <c r="A61" s="3" t="s">
         <v>79</v>
       </c>
       <c r="B61" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="D61" s="4" t="s">
         <v>211</v>
       </c>
-      <c r="C61" s="4" t="s">
+      <c r="E61" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="D61" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="E61" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="F61" s="4"/>
-      <c r="G61" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" ht="42">
+      <c r="F61" s="4" t="s">
+        <v>500</v>
+      </c>
+      <c r="G61" s="9" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" ht="42">
       <c r="A62" s="3" t="s">
         <v>80</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D62" s="4" t="s">
         <v>20</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>216</v>
-      </c>
-      <c r="F62" s="4"/>
-      <c r="G62" s="3"/>
-    </row>
-    <row r="63" spans="1:7" ht="42">
+        <v>214</v>
+      </c>
+      <c r="F62" s="4" t="s">
+        <v>501</v>
+      </c>
+      <c r="G62" s="9" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" ht="42">
       <c r="A63" s="3" t="s">
         <v>81</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="F63" s="4"/>
-      <c r="G63" s="3"/>
-    </row>
-    <row r="64" spans="1:7" ht="84">
+        <v>213</v>
+      </c>
+      <c r="F63" s="4" t="s">
+        <v>502</v>
+      </c>
+      <c r="G63" s="9" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" ht="84">
       <c r="A64" s="3" t="s">
         <v>82</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>221</v>
-      </c>
-      <c r="F64" s="4"/>
-      <c r="G64" s="3"/>
-    </row>
-    <row r="65" spans="1:7" ht="84">
+        <v>219</v>
+      </c>
+      <c r="F64" s="4" t="s">
+        <v>503</v>
+      </c>
+      <c r="G64" s="9" t="s">
+        <v>510</v>
+      </c>
+      <c r="H64" s="10"/>
+    </row>
+    <row r="65" spans="1:8" ht="84">
       <c r="A65" s="3" t="s">
         <v>83</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C65" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="D65" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="E65" s="4" t="s">
         <v>220</v>
       </c>
-      <c r="D65" s="4" t="s">
-        <v>219</v>
-      </c>
-      <c r="E65" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="F65" s="4"/>
-      <c r="G65" s="3"/>
-    </row>
-    <row r="66" spans="1:7" ht="42">
+      <c r="F65" s="4" t="s">
+        <v>503</v>
+      </c>
+      <c r="G65" s="9" t="s">
+        <v>510</v>
+      </c>
+      <c r="H65" s="10"/>
+    </row>
+    <row r="66" spans="1:8" ht="63">
       <c r="A66" s="3" t="s">
         <v>84</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E66" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="F66" s="4" t="s">
+        <v>504</v>
+      </c>
+      <c r="G66" s="9" t="s">
+        <v>510</v>
+      </c>
+      <c r="H66" s="10"/>
+    </row>
+    <row r="67" spans="1:8" ht="63">
+      <c r="A67" s="3" t="s">
+        <v>513</v>
+      </c>
+      <c r="B67" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="F66" s="4"/>
-      <c r="G66" s="3"/>
-    </row>
-    <row r="67" spans="1:7" ht="42">
-      <c r="A67" s="3" t="s">
+      <c r="C67" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="D67" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="E67" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="F67" s="4" t="s">
+        <v>505</v>
+      </c>
+      <c r="G67" s="9" t="s">
+        <v>510</v>
+      </c>
+      <c r="H67" s="10"/>
+    </row>
+    <row r="68" spans="1:8" ht="42">
+      <c r="A68" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="B67" s="4" t="s">
-        <v>225</v>
-      </c>
-      <c r="C67" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="D67" s="4" t="s">
-        <v>227</v>
-      </c>
-      <c r="E67" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="F67" s="4"/>
-      <c r="G67" s="3"/>
-    </row>
-    <row r="68" spans="1:7" ht="42">
-      <c r="A68" s="3" t="s">
-        <v>86</v>
-      </c>
       <c r="B68" s="4" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D68" s="4" t="s">
         <v>20</v>
       </c>
       <c r="E68" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="F68" s="4" t="s">
+        <v>506</v>
+      </c>
+      <c r="G68" s="9" t="s">
+        <v>510</v>
+      </c>
+      <c r="H68" s="10"/>
+    </row>
+    <row r="69" spans="1:8" ht="42">
+      <c r="A69" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="C69" s="4" t="s">
         <v>229</v>
       </c>
-      <c r="F68" s="4"/>
-      <c r="G68" s="3"/>
-    </row>
-    <row r="69" spans="1:7" ht="21">
-      <c r="A69" s="3" t="s">
+      <c r="D69" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="E69" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="F69" s="4" t="s">
+        <v>507</v>
+      </c>
+      <c r="G69" s="9" t="s">
+        <v>510</v>
+      </c>
+      <c r="H69" s="10"/>
+    </row>
+    <row r="70" spans="1:8" ht="42">
+      <c r="A70" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="B69" s="4" t="s">
-        <v>225</v>
-      </c>
-      <c r="C69" s="4" t="s">
+      <c r="B70" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="C70" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="D70" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="D69" s="4" t="s">
-        <v>230</v>
-      </c>
-      <c r="E69" s="4" t="s">
-        <v>232</v>
-      </c>
-      <c r="F69" s="4"/>
-      <c r="G69" s="3"/>
-    </row>
-    <row r="70" spans="1:7" ht="21">
-      <c r="A70" s="3" t="s">
+      <c r="E70" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="F70" s="4" t="s">
+        <v>508</v>
+      </c>
+      <c r="G70" s="9" t="s">
+        <v>510</v>
+      </c>
+      <c r="H70" s="10"/>
+    </row>
+    <row r="71" spans="1:8" ht="63">
+      <c r="A71" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="B70" s="4" t="s">
-        <v>225</v>
-      </c>
-      <c r="C70" s="4" t="s">
+      <c r="B71" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="C71" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="D71" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="E71" s="4" t="s">
         <v>234</v>
       </c>
-      <c r="D70" s="4" t="s">
-        <v>233</v>
-      </c>
-      <c r="E70" s="4" t="s">
-        <v>235</v>
-      </c>
-      <c r="F70" s="4"/>
-      <c r="G70" s="3"/>
-    </row>
-    <row r="71" spans="1:7" ht="21">
-      <c r="A71" s="3" t="s">
+      <c r="F71" s="4" t="s">
+        <v>509</v>
+      </c>
+      <c r="G71" s="9" t="s">
+        <v>510</v>
+      </c>
+      <c r="H71" s="10"/>
+    </row>
+    <row r="72" spans="1:8" ht="84">
+      <c r="A72" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="B71" s="4" t="s">
-        <v>225</v>
-      </c>
-      <c r="C71" s="4" t="s">
+      <c r="B72" s="4" t="s">
+        <v>511</v>
+      </c>
+      <c r="C72" s="4" t="s">
         <v>237</v>
       </c>
-      <c r="D71" s="4" t="s">
+      <c r="D72" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="E72" s="4" t="s">
+        <v>512</v>
+      </c>
+      <c r="F72" s="4"/>
+      <c r="G72" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" ht="84">
+      <c r="A73" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>511</v>
+      </c>
+      <c r="C73" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="D73" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="E73" s="4" t="s">
+        <v>533</v>
+      </c>
+      <c r="F73" s="4"/>
+      <c r="G73" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" ht="42">
+      <c r="A74" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="C74" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="D74" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="E74" s="4" t="s">
+        <v>473</v>
+      </c>
+      <c r="F74" s="4"/>
+      <c r="G74" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" ht="84">
+      <c r="A75" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>511</v>
+      </c>
+      <c r="C75" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="D75" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="E75" s="4" t="s">
+        <v>534</v>
+      </c>
+      <c r="F75" s="4"/>
+      <c r="G75" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" ht="84">
+      <c r="A76" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B76" s="4" t="s">
+        <v>511</v>
+      </c>
+      <c r="C76" s="4" t="s">
+        <v>477</v>
+      </c>
+      <c r="D76" s="4" t="s">
+        <v>476</v>
+      </c>
+      <c r="E76" s="4" t="s">
+        <v>535</v>
+      </c>
+      <c r="F76" s="4"/>
+      <c r="G76" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" ht="84">
+      <c r="A77" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>511</v>
+      </c>
+      <c r="C77" s="4" t="s">
+        <v>477</v>
+      </c>
+      <c r="D77" s="4" t="s">
+        <v>476</v>
+      </c>
+      <c r="E77" s="4" t="s">
+        <v>536</v>
+      </c>
+      <c r="F77" s="4"/>
+      <c r="G77" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" ht="84">
+      <c r="A78" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B78" s="4" t="s">
+        <v>511</v>
+      </c>
+      <c r="C78" s="4" t="s">
+        <v>475</v>
+      </c>
+      <c r="D78" s="4" t="s">
+        <v>474</v>
+      </c>
+      <c r="E78" s="4" t="s">
+        <v>522</v>
+      </c>
+      <c r="F78" s="4"/>
+      <c r="G78" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" ht="63">
+      <c r="A79" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>511</v>
+      </c>
+      <c r="C79" s="4" t="s">
+        <v>475</v>
+      </c>
+      <c r="D79" s="4" t="s">
+        <v>474</v>
+      </c>
+      <c r="E79" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="F79" s="4"/>
+      <c r="G79" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" ht="63">
+      <c r="A80" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B80" s="4" t="s">
+        <v>511</v>
+      </c>
+      <c r="C80" s="4" t="s">
+        <v>475</v>
+      </c>
+      <c r="D80" s="4" t="s">
+        <v>474</v>
+      </c>
+      <c r="E80" s="4" t="s">
+        <v>529</v>
+      </c>
+      <c r="F80" s="4"/>
+      <c r="G80" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" ht="42">
+      <c r="A81" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B81" s="4" t="s">
+        <v>511</v>
+      </c>
+      <c r="C81" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="D81" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E81" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="F81" s="4" t="s">
+        <v>514</v>
+      </c>
+      <c r="G81" s="9" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" ht="63">
+      <c r="A82" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B82" s="4" t="s">
+        <v>511</v>
+      </c>
+      <c r="C82" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="D82" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E82" s="4" t="s">
+        <v>515</v>
+      </c>
+      <c r="F82" s="4"/>
+      <c r="G82" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" ht="84">
+      <c r="A83" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="B83" s="4" t="s">
+        <v>511</v>
+      </c>
+      <c r="C83" s="4" t="s">
+        <v>475</v>
+      </c>
+      <c r="D83" s="4" t="s">
+        <v>474</v>
+      </c>
+      <c r="E83" s="4" t="s">
+        <v>537</v>
+      </c>
+      <c r="F83" s="4"/>
+      <c r="G83" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" ht="63">
+      <c r="A84" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B84" s="4" t="s">
+        <v>511</v>
+      </c>
+      <c r="C84" s="4" t="s">
+        <v>475</v>
+      </c>
+      <c r="D84" s="4" t="s">
+        <v>474</v>
+      </c>
+      <c r="E84" s="4" t="s">
+        <v>519</v>
+      </c>
+      <c r="F84" s="4"/>
+      <c r="G84" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" ht="84">
+      <c r="A85" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B85" s="4" t="s">
+        <v>511</v>
+      </c>
+      <c r="C85" s="4" t="s">
+        <v>475</v>
+      </c>
+      <c r="D85" s="4" t="s">
+        <v>474</v>
+      </c>
+      <c r="E85" s="4" t="s">
+        <v>518</v>
+      </c>
+      <c r="F85" s="4"/>
+      <c r="G85" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" ht="84">
+      <c r="A86" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B86" s="4" t="s">
+        <v>511</v>
+      </c>
+      <c r="C86" s="4" t="s">
+        <v>475</v>
+      </c>
+      <c r="D86" s="4" t="s">
+        <v>474</v>
+      </c>
+      <c r="E86" s="4" t="s">
+        <v>532</v>
+      </c>
+      <c r="F86" s="4"/>
+      <c r="G86" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" ht="105">
+      <c r="A87" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B87" s="4" t="s">
+        <v>511</v>
+      </c>
+      <c r="C87" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="D87" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="E87" s="4" t="s">
+        <v>520</v>
+      </c>
+      <c r="F87" s="4"/>
+      <c r="G87" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" ht="105">
+      <c r="A88" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B88" s="4" t="s">
+        <v>511</v>
+      </c>
+      <c r="C88" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="D88" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="E88" s="4" t="s">
+        <v>523</v>
+      </c>
+      <c r="F88" s="4"/>
+      <c r="G88" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" ht="42">
+      <c r="A89" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B89" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="C89" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="D89" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="E89" s="4" t="s">
+        <v>478</v>
+      </c>
+      <c r="F89" s="4"/>
+      <c r="G89" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" ht="84">
+      <c r="A90" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="B90" s="4" t="s">
+        <v>511</v>
+      </c>
+      <c r="C90" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="D90" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="E90" s="4" t="s">
+        <v>538</v>
+      </c>
+      <c r="F90" s="4"/>
+      <c r="G90" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" ht="84">
+      <c r="A91" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B91" s="4" t="s">
+        <v>511</v>
+      </c>
+      <c r="C91" s="4" t="s">
+        <v>539</v>
+      </c>
+      <c r="D91" s="4" t="s">
+        <v>540</v>
+      </c>
+      <c r="E91" s="4" t="s">
+        <v>559</v>
+      </c>
+      <c r="F91" s="4"/>
+      <c r="G91" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" ht="21">
+      <c r="A92" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B92" s="4" t="s">
         <v>238</v>
       </c>
-      <c r="E71" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="F71" s="4"/>
-      <c r="G71" s="3"/>
-    </row>
-    <row r="72" spans="1:7">
-      <c r="A72" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="B72" s="4"/>
-      <c r="C72" s="4"/>
-      <c r="D72" s="4"/>
-      <c r="E72" s="4"/>
-      <c r="F72" s="4"/>
-      <c r="G72" s="3"/>
-    </row>
-    <row r="73" spans="1:7">
-      <c r="A73" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="B73" s="4"/>
-      <c r="C73" s="4"/>
-      <c r="D73" s="4"/>
-      <c r="E73" s="4"/>
-      <c r="F73" s="4"/>
-      <c r="G73" s="3"/>
-    </row>
-    <row r="74" spans="1:7">
-      <c r="A74" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="B74" s="4"/>
-      <c r="C74" s="4"/>
-      <c r="D74" s="4"/>
-      <c r="E74" s="4"/>
-      <c r="F74" s="4"/>
-      <c r="G74" s="3"/>
-    </row>
-    <row r="75" spans="1:7">
-      <c r="A75" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="B75" s="4"/>
-      <c r="C75" s="4"/>
-      <c r="D75" s="4"/>
-      <c r="E75" s="4"/>
-      <c r="F75" s="4"/>
-      <c r="G75" s="3"/>
-    </row>
-    <row r="76" spans="1:7">
-      <c r="A76" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="B76" s="4"/>
-      <c r="C76" s="4"/>
-      <c r="D76" s="4"/>
-      <c r="E76" s="4"/>
-      <c r="F76" s="4"/>
-      <c r="G76" s="3"/>
-    </row>
-    <row r="77" spans="1:7">
-      <c r="A77" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="B77" s="4"/>
-      <c r="C77" s="4"/>
-      <c r="D77" s="4"/>
-      <c r="E77" s="4"/>
-      <c r="F77" s="4"/>
-      <c r="G77" s="3"/>
-    </row>
-    <row r="78" spans="1:7">
-      <c r="A78" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="B78" s="4"/>
-      <c r="C78" s="4"/>
-      <c r="D78" s="4"/>
-      <c r="E78" s="4"/>
-      <c r="F78" s="4"/>
-      <c r="G78" s="3"/>
-    </row>
-    <row r="79" spans="1:7">
-      <c r="A79" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="B79" s="4"/>
-      <c r="C79" s="4"/>
-      <c r="D79" s="4"/>
-      <c r="E79" s="4"/>
-      <c r="F79" s="4"/>
-      <c r="G79" s="3"/>
-    </row>
-    <row r="80" spans="1:7">
-      <c r="A80" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="B80" s="4"/>
-      <c r="C80" s="4"/>
-      <c r="D80" s="4"/>
-      <c r="E80" s="4"/>
-      <c r="F80" s="4"/>
-      <c r="G80" s="3"/>
-    </row>
-    <row r="81" spans="1:7">
-      <c r="A81" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="B81" s="4"/>
-      <c r="C81" s="4"/>
-      <c r="D81" s="4"/>
-      <c r="E81" s="4"/>
-      <c r="F81" s="4"/>
-      <c r="G81" s="3"/>
-    </row>
-    <row r="82" spans="1:7">
-      <c r="A82" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="B82" s="4"/>
-      <c r="C82" s="4"/>
-      <c r="D82" s="4"/>
-      <c r="E82" s="4"/>
-      <c r="F82" s="4"/>
-      <c r="G82" s="3"/>
-    </row>
-    <row r="83" spans="1:7">
-      <c r="A83" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="B83" s="4"/>
-      <c r="C83" s="4"/>
-      <c r="D83" s="4"/>
-      <c r="E83" s="4"/>
-      <c r="F83" s="4"/>
-      <c r="G83" s="3"/>
-    </row>
-    <row r="84" spans="1:7">
-      <c r="A84" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="B84" s="4"/>
-      <c r="C84" s="4"/>
-      <c r="D84" s="4"/>
-      <c r="E84" s="4"/>
-      <c r="F84" s="4"/>
-      <c r="G84" s="3"/>
-    </row>
-    <row r="85" spans="1:7">
-      <c r="A85" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="B85" s="4"/>
-      <c r="C85" s="4"/>
-      <c r="D85" s="4"/>
-      <c r="E85" s="4"/>
-      <c r="F85" s="4"/>
-      <c r="G85" s="3"/>
-    </row>
-    <row r="86" spans="1:7">
-      <c r="A86" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="B86" s="4"/>
-      <c r="C86" s="4"/>
-      <c r="D86" s="4"/>
-      <c r="E86" s="4"/>
-      <c r="F86" s="4"/>
-      <c r="G86" s="3"/>
-    </row>
-    <row r="87" spans="1:7">
-      <c r="A87" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="B87" s="4"/>
-      <c r="C87" s="4"/>
-      <c r="D87" s="4"/>
-      <c r="E87" s="4"/>
-      <c r="F87" s="4"/>
-      <c r="G87" s="3"/>
-    </row>
-    <row r="88" spans="1:7">
-      <c r="A88" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="B88" s="4"/>
-      <c r="C88" s="4"/>
-      <c r="D88" s="4"/>
-      <c r="E88" s="4"/>
-      <c r="F88" s="4"/>
-      <c r="G88" s="3"/>
-    </row>
-    <row r="89" spans="1:7">
-      <c r="A89" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="B89" s="4"/>
-      <c r="C89" s="4"/>
-      <c r="D89" s="4"/>
-      <c r="E89" s="4"/>
-      <c r="F89" s="4"/>
-      <c r="G89" s="3"/>
-    </row>
-    <row r="90" spans="1:7">
-      <c r="A90" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="B90" s="4"/>
-      <c r="C90" s="4"/>
-      <c r="D90" s="4"/>
-      <c r="E90" s="4"/>
-      <c r="F90" s="4"/>
-      <c r="G90" s="3"/>
-    </row>
-    <row r="91" spans="1:7">
-      <c r="A91" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="B91" s="4"/>
-      <c r="C91" s="4"/>
-      <c r="D91" s="4"/>
-      <c r="E91" s="4"/>
-      <c r="F91" s="4"/>
-      <c r="G91" s="3"/>
-    </row>
-    <row r="92" spans="1:7">
-      <c r="A92" s="3" t="s">
+      <c r="C92" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="D92" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="E92" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="F92" s="4"/>
+      <c r="G92" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" ht="105">
+      <c r="A93" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="B92" s="4"/>
-      <c r="C92" s="4"/>
-      <c r="D92" s="4"/>
-      <c r="E92" s="4"/>
-      <c r="F92" s="4"/>
-      <c r="G92" s="3"/>
-    </row>
-    <row r="93" spans="1:7">
-      <c r="A93" s="3" t="s">
+      <c r="B93" s="4" t="s">
+        <v>511</v>
+      </c>
+      <c r="C93" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="D93" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="E93" s="4" t="s">
+        <v>524</v>
+      </c>
+      <c r="F93" s="4"/>
+      <c r="G93" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" ht="84">
+      <c r="A94" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="B93" s="4"/>
-      <c r="C93" s="4"/>
-      <c r="D93" s="4"/>
-      <c r="E93" s="4"/>
-      <c r="F93" s="4"/>
-      <c r="G93" s="3"/>
-    </row>
-    <row r="94" spans="1:7">
-      <c r="A94" s="3" t="s">
+      <c r="B94" s="4" t="s">
+        <v>511</v>
+      </c>
+      <c r="C94" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="D94" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="E94" s="4" t="s">
+        <v>525</v>
+      </c>
+      <c r="F94" s="4"/>
+      <c r="G94" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" ht="84">
+      <c r="A95" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="B94" s="4"/>
-      <c r="C94" s="4"/>
-      <c r="D94" s="4"/>
-      <c r="E94" s="4"/>
-      <c r="F94" s="4"/>
-      <c r="G94" s="3"/>
-    </row>
-    <row r="95" spans="1:7">
-      <c r="A95" s="3" t="s">
+      <c r="B95" s="4" t="s">
+        <v>511</v>
+      </c>
+      <c r="C95" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="D95" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="E95" s="4" t="s">
+        <v>530</v>
+      </c>
+      <c r="F95" s="4"/>
+      <c r="G95" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" ht="63">
+      <c r="A96" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="B95" s="4"/>
-      <c r="C95" s="4"/>
-      <c r="D95" s="4"/>
-      <c r="E95" s="4"/>
-      <c r="F95" s="4"/>
-      <c r="G95" s="3"/>
-    </row>
-    <row r="96" spans="1:7">
-      <c r="A96" s="3" t="s">
+      <c r="B96" s="4" t="s">
+        <v>511</v>
+      </c>
+      <c r="C96" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="D96" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="E96" s="4" t="s">
+        <v>541</v>
+      </c>
+      <c r="F96" s="4"/>
+      <c r="G96" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" ht="105">
+      <c r="A97" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="B96" s="4"/>
-      <c r="C96" s="4"/>
-      <c r="D96" s="4"/>
-      <c r="E96" s="4"/>
-      <c r="F96" s="4"/>
-      <c r="G96" s="3"/>
-    </row>
-    <row r="97" spans="1:7">
-      <c r="A97" s="3" t="s">
+      <c r="B97" s="4" t="s">
+        <v>511</v>
+      </c>
+      <c r="C97" s="4" t="s">
+        <v>481</v>
+      </c>
+      <c r="D97" s="4" t="s">
+        <v>482</v>
+      </c>
+      <c r="E97" s="4" t="s">
+        <v>526</v>
+      </c>
+      <c r="F97" s="4"/>
+      <c r="G97" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" ht="84">
+      <c r="A98" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="B97" s="4"/>
-      <c r="C97" s="4"/>
-      <c r="D97" s="4"/>
-      <c r="E97" s="4"/>
-      <c r="F97" s="4"/>
-      <c r="G97" s="3"/>
-    </row>
-    <row r="98" spans="1:7">
-      <c r="A98" s="3" t="s">
+      <c r="B98" s="4" t="s">
+        <v>511</v>
+      </c>
+      <c r="C98" s="4" t="s">
+        <v>481</v>
+      </c>
+      <c r="D98" s="4" t="s">
+        <v>482</v>
+      </c>
+      <c r="E98" s="4" t="s">
+        <v>528</v>
+      </c>
+      <c r="F98" s="4"/>
+      <c r="G98" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" ht="63">
+      <c r="A99" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="B98" s="4"/>
-      <c r="C98" s="4"/>
-      <c r="D98" s="4"/>
-      <c r="E98" s="4"/>
-      <c r="F98" s="4"/>
-      <c r="G98" s="3"/>
-    </row>
-    <row r="99" spans="1:7">
-      <c r="A99" s="3" t="s">
+      <c r="B99" s="4" t="s">
+        <v>511</v>
+      </c>
+      <c r="C99" s="4" t="s">
+        <v>481</v>
+      </c>
+      <c r="D99" s="4" t="s">
+        <v>482</v>
+      </c>
+      <c r="E99" s="4" t="s">
+        <v>527</v>
+      </c>
+      <c r="F99" s="4"/>
+      <c r="G99" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" ht="84">
+      <c r="A100" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="B99" s="4"/>
-      <c r="C99" s="4"/>
-      <c r="D99" s="4"/>
-      <c r="E99" s="4"/>
-      <c r="F99" s="4"/>
-      <c r="G99" s="3"/>
-    </row>
-    <row r="100" spans="1:7">
-      <c r="A100" s="3" t="s">
+      <c r="B100" s="4" t="s">
+        <v>511</v>
+      </c>
+      <c r="C100" s="4" t="s">
+        <v>479</v>
+      </c>
+      <c r="D100" s="4" t="s">
+        <v>480</v>
+      </c>
+      <c r="E100" s="4" t="s">
+        <v>516</v>
+      </c>
+      <c r="F100" s="4"/>
+      <c r="G100" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" ht="84">
+      <c r="A101" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="B100" s="4"/>
-      <c r="C100" s="4"/>
-      <c r="D100" s="4"/>
-      <c r="E100" s="4"/>
-      <c r="F100" s="4"/>
-      <c r="G100" s="3"/>
-    </row>
-    <row r="101" spans="1:7">
-      <c r="A101" s="3" t="s">
+      <c r="B101" s="4" t="s">
+        <v>511</v>
+      </c>
+      <c r="C101" s="4" t="s">
+        <v>483</v>
+      </c>
+      <c r="D101" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="E101" s="4" t="s">
+        <v>517</v>
+      </c>
+      <c r="F101" s="4"/>
+      <c r="G101" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" ht="84">
+      <c r="A102" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="B101" s="4"/>
-      <c r="C101" s="4"/>
-      <c r="D101" s="4"/>
-      <c r="E101" s="4"/>
-      <c r="F101" s="4"/>
-      <c r="G101" s="3"/>
-    </row>
-    <row r="102" spans="1:7">
-      <c r="A102" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="B102" s="4"/>
-      <c r="C102" s="4"/>
-      <c r="D102" s="4"/>
-      <c r="E102" s="4"/>
+      <c r="B102" s="4" t="s">
+        <v>511</v>
+      </c>
+      <c r="C102" s="4" t="s">
+        <v>481</v>
+      </c>
+      <c r="D102" s="4" t="s">
+        <v>482</v>
+      </c>
+      <c r="E102" s="4" t="s">
+        <v>537</v>
+      </c>
       <c r="F102" s="4"/>
-      <c r="G102" s="3"/>
+      <c r="G102" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" ht="63">
+      <c r="A103" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="B103" s="4" t="s">
+        <v>511</v>
+      </c>
+      <c r="C103" s="4" t="s">
+        <v>481</v>
+      </c>
+      <c r="D103" s="4" t="s">
+        <v>482</v>
+      </c>
+      <c r="E103" s="4" t="s">
+        <v>558</v>
+      </c>
+      <c r="F103" s="4"/>
+      <c r="G103" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" ht="84">
+      <c r="A104" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="B104" s="4" t="s">
+        <v>511</v>
+      </c>
+      <c r="C104" s="4" t="s">
+        <v>481</v>
+      </c>
+      <c r="D104" s="4" t="s">
+        <v>482</v>
+      </c>
+      <c r="E104" s="4" t="s">
+        <v>557</v>
+      </c>
+      <c r="F104" s="4"/>
+      <c r="G104" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" ht="84">
+      <c r="A105" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="B105" s="4" t="s">
+        <v>511</v>
+      </c>
+      <c r="C105" s="4" t="s">
+        <v>481</v>
+      </c>
+      <c r="D105" s="4" t="s">
+        <v>482</v>
+      </c>
+      <c r="E105" s="4" t="s">
+        <v>531</v>
+      </c>
+      <c r="F105" s="4"/>
+      <c r="G105" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" ht="84">
+      <c r="A106" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="B106" s="4" t="s">
+        <v>511</v>
+      </c>
+      <c r="C106" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="D106" s="4" t="s">
+        <v>550</v>
+      </c>
+      <c r="E106" s="4" t="s">
+        <v>551</v>
+      </c>
+      <c r="F106" s="4"/>
+      <c r="G106" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" ht="63">
+      <c r="A107" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="B107" s="4" t="s">
+        <v>511</v>
+      </c>
+      <c r="C107" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="D107" s="4" t="s">
+        <v>550</v>
+      </c>
+      <c r="E107" s="4" t="s">
+        <v>552</v>
+      </c>
+      <c r="F107" s="4"/>
+      <c r="G107" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" ht="84">
+      <c r="A108" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="B108" s="4" t="s">
+        <v>511</v>
+      </c>
+      <c r="C108" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="D108" s="4" t="s">
+        <v>553</v>
+      </c>
+      <c r="E108" s="4" t="s">
+        <v>554</v>
+      </c>
+      <c r="F108" s="4"/>
+      <c r="G108" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" ht="126">
+      <c r="A109" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="B109" s="4" t="s">
+        <v>511</v>
+      </c>
+      <c r="C109" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="D109" s="4" t="s">
+        <v>553</v>
+      </c>
+      <c r="E109" s="4" t="s">
+        <v>555</v>
+      </c>
+      <c r="F109" s="4"/>
+      <c r="G109" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" ht="105">
+      <c r="A110" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="B110" s="4" t="s">
+        <v>511</v>
+      </c>
+      <c r="C110" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="D110" s="4" t="s">
+        <v>553</v>
+      </c>
+      <c r="E110" s="4" t="s">
+        <v>556</v>
+      </c>
+      <c r="F110" s="4"/>
+      <c r="G110" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7">
+      <c r="A111" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="B111" s="4"/>
+      <c r="C111" s="4"/>
+      <c r="D111" s="4"/>
+      <c r="E111" s="4"/>
+      <c r="F111" s="4"/>
+      <c r="G111" s="3"/>
+    </row>
+    <row r="112" spans="1:7">
+      <c r="A112" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="B112" s="4"/>
+      <c r="C112" s="4"/>
+      <c r="D112" s="4"/>
+      <c r="E112" s="4"/>
+      <c r="F112" s="4"/>
+      <c r="G112" s="3"/>
+    </row>
+    <row r="113" spans="1:7">
+      <c r="A113" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="B113" s="4"/>
+      <c r="C113" s="4"/>
+      <c r="D113" s="4"/>
+      <c r="E113" s="4"/>
+      <c r="F113" s="4"/>
+      <c r="G113" s="3"/>
+    </row>
+    <row r="114" spans="1:7">
+      <c r="A114" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="B114" s="4"/>
+      <c r="C114" s="4"/>
+      <c r="D114" s="4"/>
+      <c r="E114" s="4"/>
+      <c r="F114" s="4"/>
+      <c r="G114" s="3"/>
+    </row>
+    <row r="115" spans="1:7">
+      <c r="A115" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="B115" s="4"/>
+      <c r="C115" s="4"/>
+      <c r="D115" s="4"/>
+      <c r="E115" s="4"/>
+      <c r="F115" s="4"/>
+      <c r="G115" s="3"/>
+    </row>
+    <row r="116" spans="1:7">
+      <c r="A116" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="B116" s="4"/>
+      <c r="C116" s="4"/>
+      <c r="D116" s="4"/>
+      <c r="E116" s="4"/>
+      <c r="F116" s="4"/>
+      <c r="G116" s="3"/>
+    </row>
+    <row r="117" spans="1:7">
+      <c r="A117" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="B117" s="4"/>
+      <c r="C117" s="4"/>
+      <c r="D117" s="4"/>
+      <c r="E117" s="4"/>
+      <c r="F117" s="4"/>
+      <c r="G117" s="3"/>
+    </row>
+    <row r="118" spans="1:7">
+      <c r="A118" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="B118" s="4"/>
+      <c r="C118" s="4"/>
+      <c r="D118" s="4"/>
+      <c r="E118" s="4"/>
+      <c r="F118" s="4"/>
+      <c r="G118" s="3"/>
+    </row>
+    <row r="119" spans="1:7">
+      <c r="A119" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="B119" s="4"/>
+      <c r="C119" s="4"/>
+      <c r="D119" s="4"/>
+      <c r="E119" s="4"/>
+      <c r="F119" s="4"/>
+      <c r="G119" s="3"/>
+    </row>
+    <row r="120" spans="1:7">
+      <c r="A120" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="B120" s="4"/>
+      <c r="C120" s="4"/>
+      <c r="D120" s="4"/>
+      <c r="E120" s="4"/>
+      <c r="F120" s="4"/>
+      <c r="G120" s="3"/>
+    </row>
+    <row r="121" spans="1:7">
+      <c r="A121" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="B121" s="4"/>
+      <c r="C121" s="4"/>
+      <c r="D121" s="4"/>
+      <c r="E121" s="4"/>
+      <c r="F121" s="4"/>
+      <c r="G121" s="3"/>
+    </row>
+    <row r="122" spans="1:7">
+      <c r="A122" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="B122" s="4"/>
+      <c r="C122" s="4"/>
+      <c r="D122" s="4"/>
+      <c r="E122" s="4"/>
+      <c r="F122" s="4"/>
+      <c r="G122" s="3"/>
+    </row>
+    <row r="123" spans="1:7">
+      <c r="A123" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="B123" s="4"/>
+      <c r="C123" s="4"/>
+      <c r="D123" s="4"/>
+      <c r="E123" s="4"/>
+      <c r="F123" s="4"/>
+      <c r="G123" s="3"/>
+    </row>
+    <row r="124" spans="1:7">
+      <c r="A124" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="B124" s="4"/>
+      <c r="C124" s="4"/>
+      <c r="D124" s="4"/>
+      <c r="E124" s="4"/>
+      <c r="F124" s="4"/>
+      <c r="G124" s="3"/>
+    </row>
+    <row r="125" spans="1:7">
+      <c r="A125" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="B125" s="4"/>
+      <c r="C125" s="4"/>
+      <c r="D125" s="4"/>
+      <c r="E125" s="4"/>
+      <c r="F125" s="4"/>
+      <c r="G125" s="3"/>
+    </row>
+    <row r="126" spans="1:7">
+      <c r="A126" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="B126" s="4"/>
+      <c r="C126" s="4"/>
+      <c r="D126" s="4"/>
+      <c r="E126" s="4"/>
+      <c r="F126" s="4"/>
+      <c r="G126" s="3"/>
+    </row>
+    <row r="127" spans="1:7">
+      <c r="A127" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="B127" s="4"/>
+      <c r="C127" s="4"/>
+      <c r="D127" s="4"/>
+      <c r="E127" s="4"/>
+      <c r="F127" s="4"/>
+      <c r="G127" s="3"/>
+    </row>
+    <row r="128" spans="1:7">
+      <c r="A128" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="B128" s="4"/>
+      <c r="C128" s="4"/>
+      <c r="D128" s="4"/>
+      <c r="E128" s="4"/>
+      <c r="F128" s="4"/>
+      <c r="G128" s="3"/>
+    </row>
+    <row r="129" spans="1:7">
+      <c r="A129" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="B129" s="4"/>
+      <c r="C129" s="4"/>
+      <c r="D129" s="4"/>
+      <c r="E129" s="4"/>
+      <c r="F129" s="4"/>
+      <c r="G129" s="3"/>
+    </row>
+    <row r="130" spans="1:7">
+      <c r="A130" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="B130" s="4"/>
+      <c r="C130" s="4"/>
+      <c r="D130" s="4"/>
+      <c r="E130" s="4"/>
+      <c r="F130" s="4"/>
+      <c r="G130" s="3"/>
+    </row>
+    <row r="131" spans="1:7">
+      <c r="A131" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="B131" s="4"/>
+      <c r="C131" s="4"/>
+      <c r="D131" s="4"/>
+      <c r="E131" s="4"/>
+      <c r="F131" s="4"/>
+      <c r="G131" s="3"/>
+    </row>
+    <row r="132" spans="1:7">
+      <c r="A132" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="B132" s="4"/>
+      <c r="C132" s="4"/>
+      <c r="D132" s="4"/>
+      <c r="E132" s="4"/>
+      <c r="F132" s="4"/>
+      <c r="G132" s="3"/>
+    </row>
+    <row r="133" spans="1:7">
+      <c r="A133" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="B133" s="4"/>
+      <c r="C133" s="4"/>
+      <c r="D133" s="4"/>
+      <c r="E133" s="4"/>
+      <c r="F133" s="4"/>
+      <c r="G133" s="3"/>
+    </row>
+    <row r="134" spans="1:7">
+      <c r="A134" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="B134" s="4"/>
+      <c r="C134" s="4"/>
+      <c r="D134" s="4"/>
+      <c r="E134" s="4"/>
+      <c r="F134" s="4"/>
+      <c r="G134" s="3"/>
+    </row>
+    <row r="135" spans="1:7">
+      <c r="A135" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="B135" s="4"/>
+      <c r="C135" s="4"/>
+      <c r="D135" s="4"/>
+      <c r="E135" s="4"/>
+      <c r="F135" s="4"/>
+      <c r="G135" s="3"/>
+    </row>
+    <row r="136" spans="1:7">
+      <c r="A136" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="B136" s="4"/>
+      <c r="C136" s="4"/>
+      <c r="D136" s="4"/>
+      <c r="E136" s="4"/>
+      <c r="F136" s="4"/>
+      <c r="G136" s="3"/>
+    </row>
+    <row r="137" spans="1:7">
+      <c r="A137" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="B137" s="4"/>
+      <c r="C137" s="4"/>
+      <c r="D137" s="4"/>
+      <c r="E137" s="4"/>
+      <c r="F137" s="4"/>
+      <c r="G137" s="3"/>
+    </row>
+    <row r="138" spans="1:7">
+      <c r="A138" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="B138" s="4"/>
+      <c r="C138" s="4"/>
+      <c r="D138" s="4"/>
+      <c r="E138" s="4"/>
+      <c r="F138" s="4"/>
+      <c r="G138" s="3"/>
+    </row>
+    <row r="139" spans="1:7">
+      <c r="A139" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="B139" s="4"/>
+      <c r="C139" s="4"/>
+      <c r="D139" s="4"/>
+      <c r="E139" s="4"/>
+      <c r="F139" s="4"/>
+      <c r="G139" s="3"/>
+    </row>
+    <row r="140" spans="1:7">
+      <c r="A140" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="B140" s="4"/>
+      <c r="C140" s="4"/>
+      <c r="D140" s="4"/>
+      <c r="E140" s="4"/>
+      <c r="F140" s="4"/>
+      <c r="G140" s="3"/>
+    </row>
+    <row r="141" spans="1:7">
+      <c r="A141" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="B141" s="4"/>
+      <c r="C141" s="4"/>
+      <c r="D141" s="4"/>
+      <c r="E141" s="4"/>
+      <c r="F141" s="4"/>
+      <c r="G141" s="3"/>
+    </row>
+    <row r="142" spans="1:7">
+      <c r="A142" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="B142" s="4"/>
+      <c r="C142" s="4"/>
+      <c r="D142" s="4"/>
+      <c r="E142" s="4"/>
+      <c r="F142" s="4"/>
+      <c r="G142" s="3"/>
+    </row>
+    <row r="143" spans="1:7">
+      <c r="A143" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="B143" s="4"/>
+      <c r="C143" s="4"/>
+      <c r="D143" s="4"/>
+      <c r="E143" s="4"/>
+      <c r="F143" s="4"/>
+      <c r="G143" s="3"/>
+    </row>
+    <row r="144" spans="1:7">
+      <c r="A144" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="B144" s="4"/>
+      <c r="C144" s="4"/>
+      <c r="D144" s="4"/>
+      <c r="E144" s="4"/>
+      <c r="F144" s="4"/>
+      <c r="G144" s="3"/>
+    </row>
+    <row r="145" spans="1:7">
+      <c r="A145" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="B145" s="4"/>
+      <c r="C145" s="4"/>
+      <c r="D145" s="4"/>
+      <c r="E145" s="4"/>
+      <c r="F145" s="4"/>
+      <c r="G145" s="3"/>
+    </row>
+    <row r="146" spans="1:7">
+      <c r="A146" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="B146" s="4"/>
+      <c r="C146" s="4"/>
+      <c r="D146" s="4"/>
+      <c r="E146" s="4"/>
+      <c r="F146" s="4"/>
+      <c r="G146" s="3"/>
+    </row>
+    <row r="147" spans="1:7">
+      <c r="A147" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="B147" s="4"/>
+      <c r="C147" s="4"/>
+      <c r="D147" s="4"/>
+      <c r="E147" s="4"/>
+      <c r="F147" s="4"/>
+      <c r="G147" s="3"/>
+    </row>
+    <row r="148" spans="1:7">
+      <c r="A148" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="B148" s="4"/>
+      <c r="C148" s="4"/>
+      <c r="D148" s="4"/>
+      <c r="E148" s="4"/>
+      <c r="F148" s="4"/>
+      <c r="G148" s="3"/>
+    </row>
+    <row r="149" spans="1:7">
+      <c r="A149" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="B149" s="4"/>
+      <c r="C149" s="4"/>
+      <c r="D149" s="4"/>
+      <c r="E149" s="4"/>
+      <c r="F149" s="4"/>
+      <c r="G149" s="3"/>
+    </row>
+    <row r="150" spans="1:7">
+      <c r="A150" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="B150" s="4"/>
+      <c r="C150" s="4"/>
+      <c r="D150" s="4"/>
+      <c r="E150" s="4"/>
+      <c r="F150" s="4"/>
+      <c r="G150" s="3"/>
+    </row>
+    <row r="151" spans="1:7">
+      <c r="A151" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="B151" s="4"/>
+      <c r="C151" s="4"/>
+      <c r="D151" s="4"/>
+      <c r="E151" s="4"/>
+      <c r="F151" s="4"/>
+      <c r="G151" s="3"/>
+    </row>
+    <row r="152" spans="1:7">
+      <c r="A152" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="B152" s="4"/>
+      <c r="C152" s="4"/>
+      <c r="D152" s="4"/>
+      <c r="E152" s="4"/>
+      <c r="F152" s="4"/>
+      <c r="G152" s="3"/>
+    </row>
+    <row r="153" spans="1:7">
+      <c r="A153" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="B153" s="4"/>
+      <c r="C153" s="4"/>
+      <c r="D153" s="4"/>
+      <c r="E153" s="4"/>
+      <c r="F153" s="4"/>
+      <c r="G153" s="3"/>
+    </row>
+    <row r="154" spans="1:7">
+      <c r="A154" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="B154" s="4"/>
+      <c r="C154" s="4"/>
+      <c r="D154" s="4"/>
+      <c r="E154" s="4"/>
+      <c r="F154" s="4"/>
+      <c r="G154" s="3"/>
+    </row>
+    <row r="155" spans="1:7">
+      <c r="A155" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="B155" s="4"/>
+      <c r="C155" s="4"/>
+      <c r="D155" s="4"/>
+      <c r="E155" s="4"/>
+      <c r="F155" s="4"/>
+      <c r="G155" s="3"/>
+    </row>
+    <row r="156" spans="1:7">
+      <c r="A156" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="B156" s="4"/>
+      <c r="C156" s="4"/>
+      <c r="D156" s="4"/>
+      <c r="E156" s="4"/>
+      <c r="F156" s="4"/>
+      <c r="G156" s="3"/>
+    </row>
+    <row r="157" spans="1:7">
+      <c r="A157" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="B157" s="4"/>
+      <c r="C157" s="4"/>
+      <c r="D157" s="4"/>
+      <c r="E157" s="4"/>
+      <c r="F157" s="4"/>
+      <c r="G157" s="3"/>
+    </row>
+    <row r="158" spans="1:7">
+      <c r="A158" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="B158" s="4"/>
+      <c r="C158" s="4"/>
+      <c r="D158" s="4"/>
+      <c r="E158" s="4"/>
+      <c r="F158" s="4"/>
+      <c r="G158" s="3"/>
+    </row>
+    <row r="159" spans="1:7">
+      <c r="A159" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="B159" s="4"/>
+      <c r="C159" s="4"/>
+      <c r="D159" s="4"/>
+      <c r="E159" s="4"/>
+      <c r="F159" s="4"/>
+      <c r="G159" s="3"/>
+    </row>
+    <row r="160" spans="1:7">
+      <c r="A160" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="B160" s="4"/>
+      <c r="C160" s="4"/>
+      <c r="D160" s="4"/>
+      <c r="E160" s="4"/>
+      <c r="F160" s="4"/>
+      <c r="G160" s="3"/>
+    </row>
+    <row r="161" spans="1:7">
+      <c r="A161" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="B161" s="4"/>
+      <c r="C161" s="4"/>
+      <c r="D161" s="4"/>
+      <c r="E161" s="4"/>
+      <c r="F161" s="4"/>
+      <c r="G161" s="3"/>
+    </row>
+    <row r="162" spans="1:7">
+      <c r="A162" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="B162" s="4"/>
+      <c r="C162" s="4"/>
+      <c r="D162" s="4"/>
+      <c r="E162" s="4"/>
+      <c r="F162" s="4"/>
+      <c r="G162" s="3"/>
+    </row>
+    <row r="163" spans="1:7">
+      <c r="A163" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="B163" s="4"/>
+      <c r="C163" s="4"/>
+      <c r="D163" s="4"/>
+      <c r="E163" s="4"/>
+      <c r="F163" s="4"/>
+      <c r="G163" s="3"/>
+    </row>
+    <row r="164" spans="1:7">
+      <c r="A164" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="B164" s="4"/>
+      <c r="C164" s="4"/>
+      <c r="D164" s="4"/>
+      <c r="E164" s="4"/>
+      <c r="F164" s="4"/>
+      <c r="G164" s="3"/>
+    </row>
+    <row r="165" spans="1:7">
+      <c r="A165" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="B165" s="4"/>
+      <c r="C165" s="4"/>
+      <c r="D165" s="4"/>
+      <c r="E165" s="4"/>
+      <c r="F165" s="4"/>
+      <c r="G165" s="3"/>
+    </row>
+    <row r="166" spans="1:7">
+      <c r="A166" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="B166" s="4"/>
+      <c r="C166" s="4"/>
+      <c r="D166" s="4"/>
+      <c r="E166" s="4"/>
+      <c r="F166" s="4"/>
+      <c r="G166" s="3"/>
+    </row>
+    <row r="167" spans="1:7">
+      <c r="A167" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="B167" s="4"/>
+      <c r="C167" s="4"/>
+      <c r="D167" s="4"/>
+      <c r="E167" s="4"/>
+      <c r="F167" s="4"/>
+      <c r="G167" s="3"/>
+    </row>
+    <row r="168" spans="1:7">
+      <c r="A168" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="B168" s="4"/>
+      <c r="C168" s="4"/>
+      <c r="D168" s="4"/>
+      <c r="E168" s="4"/>
+      <c r="F168" s="4"/>
+      <c r="G168" s="3"/>
+    </row>
+    <row r="169" spans="1:7">
+      <c r="A169" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="B169" s="4"/>
+      <c r="C169" s="4"/>
+      <c r="D169" s="4"/>
+      <c r="E169" s="4"/>
+      <c r="F169" s="4"/>
+      <c r="G169" s="3"/>
+    </row>
+    <row r="170" spans="1:7">
+      <c r="A170" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="B170" s="4"/>
+      <c r="C170" s="4"/>
+      <c r="D170" s="4"/>
+      <c r="E170" s="4"/>
+      <c r="F170" s="4"/>
+      <c r="G170" s="3"/>
+    </row>
+    <row r="171" spans="1:7">
+      <c r="A171" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="B171" s="4"/>
+      <c r="C171" s="4"/>
+      <c r="D171" s="4"/>
+      <c r="E171" s="4"/>
+      <c r="F171" s="4"/>
+      <c r="G171" s="3"/>
+    </row>
+    <row r="172" spans="1:7">
+      <c r="A172" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="B172" s="4"/>
+      <c r="C172" s="4"/>
+      <c r="D172" s="4"/>
+      <c r="E172" s="4"/>
+      <c r="F172" s="4"/>
+      <c r="G172" s="3"/>
+    </row>
+    <row r="173" spans="1:7">
+      <c r="A173" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="B173" s="4"/>
+      <c r="C173" s="4"/>
+      <c r="D173" s="4"/>
+      <c r="E173" s="4"/>
+      <c r="F173" s="4"/>
+      <c r="G173" s="3"/>
+    </row>
+    <row r="174" spans="1:7">
+      <c r="A174" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="B174" s="4"/>
+      <c r="C174" s="4"/>
+      <c r="D174" s="4"/>
+      <c r="E174" s="4"/>
+      <c r="F174" s="4"/>
+      <c r="G174" s="3"/>
+    </row>
+    <row r="175" spans="1:7">
+      <c r="A175" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="B175" s="4"/>
+      <c r="C175" s="4"/>
+      <c r="D175" s="4"/>
+      <c r="E175" s="4"/>
+      <c r="F175" s="4"/>
+      <c r="G175" s="3"/>
+    </row>
+    <row r="176" spans="1:7">
+      <c r="A176" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="B176" s="4"/>
+      <c r="C176" s="4"/>
+      <c r="D176" s="4"/>
+      <c r="E176" s="4"/>
+      <c r="F176" s="4"/>
+      <c r="G176" s="3"/>
+    </row>
+    <row r="177" spans="1:7">
+      <c r="A177" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="B177" s="4"/>
+      <c r="C177" s="4"/>
+      <c r="D177" s="4"/>
+      <c r="E177" s="4"/>
+      <c r="F177" s="4"/>
+      <c r="G177" s="3"/>
+    </row>
+    <row r="178" spans="1:7">
+      <c r="A178" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="B178" s="4"/>
+      <c r="C178" s="4"/>
+      <c r="D178" s="4"/>
+      <c r="E178" s="4"/>
+      <c r="F178" s="4"/>
+      <c r="G178" s="3"/>
+    </row>
+    <row r="179" spans="1:7">
+      <c r="A179" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="B179" s="4"/>
+      <c r="C179" s="4"/>
+      <c r="D179" s="4"/>
+      <c r="E179" s="4"/>
+      <c r="F179" s="4"/>
+      <c r="G179" s="3"/>
+    </row>
+    <row r="180" spans="1:7">
+      <c r="A180" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="B180" s="4"/>
+      <c r="C180" s="4"/>
+      <c r="D180" s="4"/>
+      <c r="E180" s="4"/>
+      <c r="F180" s="4"/>
+      <c r="G180" s="3"/>
+    </row>
+    <row r="181" spans="1:7">
+      <c r="A181" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="B181" s="4"/>
+      <c r="C181" s="4"/>
+      <c r="D181" s="4"/>
+      <c r="E181" s="4"/>
+      <c r="F181" s="4"/>
+      <c r="G181" s="3"/>
+    </row>
+    <row r="182" spans="1:7">
+      <c r="A182" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="B182" s="4"/>
+      <c r="C182" s="4"/>
+      <c r="D182" s="4"/>
+      <c r="E182" s="4"/>
+      <c r="F182" s="4"/>
+      <c r="G182" s="3"/>
+    </row>
+    <row r="183" spans="1:7">
+      <c r="A183" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="B183" s="4"/>
+      <c r="C183" s="4"/>
+      <c r="D183" s="4"/>
+      <c r="E183" s="4"/>
+      <c r="F183" s="4"/>
+      <c r="G183" s="3"/>
+    </row>
+    <row r="184" spans="1:7">
+      <c r="A184" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="B184" s="4"/>
+      <c r="C184" s="4"/>
+      <c r="D184" s="4"/>
+      <c r="E184" s="4"/>
+      <c r="F184" s="4"/>
+      <c r="G184" s="3"/>
+    </row>
+    <row r="185" spans="1:7">
+      <c r="A185" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="B185" s="4"/>
+      <c r="C185" s="4"/>
+      <c r="D185" s="4"/>
+      <c r="E185" s="4"/>
+      <c r="F185" s="4"/>
+      <c r="G185" s="3"/>
+    </row>
+    <row r="186" spans="1:7">
+      <c r="A186" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="B186" s="4"/>
+      <c r="C186" s="4"/>
+      <c r="D186" s="4"/>
+      <c r="E186" s="4"/>
+      <c r="F186" s="4"/>
+      <c r="G186" s="3"/>
+    </row>
+    <row r="187" spans="1:7">
+      <c r="A187" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="B187" s="4"/>
+      <c r="C187" s="4"/>
+      <c r="D187" s="4"/>
+      <c r="E187" s="4"/>
+      <c r="F187" s="4"/>
+      <c r="G187" s="3"/>
+    </row>
+    <row r="188" spans="1:7">
+      <c r="A188" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="B188" s="4"/>
+      <c r="C188" s="4"/>
+      <c r="D188" s="4"/>
+      <c r="E188" s="4"/>
+      <c r="F188" s="4"/>
+      <c r="G188" s="3"/>
+    </row>
+    <row r="189" spans="1:7">
+      <c r="A189" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="B189" s="4"/>
+      <c r="C189" s="4"/>
+      <c r="D189" s="4"/>
+      <c r="E189" s="4"/>
+      <c r="F189" s="4"/>
+      <c r="G189" s="3"/>
+    </row>
+    <row r="190" spans="1:7">
+      <c r="A190" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="B190" s="4"/>
+      <c r="C190" s="4"/>
+      <c r="D190" s="4"/>
+      <c r="E190" s="4"/>
+      <c r="F190" s="4"/>
+      <c r="G190" s="3"/>
+    </row>
+    <row r="191" spans="1:7">
+      <c r="A191" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="B191" s="4"/>
+      <c r="C191" s="4"/>
+      <c r="D191" s="4"/>
+      <c r="E191" s="4"/>
+      <c r="F191" s="4"/>
+      <c r="G191" s="3"/>
+    </row>
+    <row r="192" spans="1:7">
+      <c r="A192" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="B192" s="4"/>
+      <c r="C192" s="4"/>
+      <c r="D192" s="4"/>
+      <c r="E192" s="4"/>
+      <c r="F192" s="4"/>
+      <c r="G192" s="3"/>
+    </row>
+    <row r="193" spans="1:7">
+      <c r="A193" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="B193" s="4"/>
+      <c r="C193" s="4"/>
+      <c r="D193" s="4"/>
+      <c r="E193" s="4"/>
+      <c r="F193" s="4"/>
+      <c r="G193" s="3"/>
+    </row>
+    <row r="194" spans="1:7">
+      <c r="A194" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="B194" s="4"/>
+      <c r="C194" s="4"/>
+      <c r="D194" s="4"/>
+      <c r="E194" s="4"/>
+      <c r="F194" s="4"/>
+      <c r="G194" s="3"/>
+    </row>
+    <row r="195" spans="1:7">
+      <c r="A195" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="B195" s="4"/>
+      <c r="C195" s="4"/>
+      <c r="D195" s="4"/>
+      <c r="E195" s="4"/>
+      <c r="F195" s="4"/>
+      <c r="G195" s="3"/>
+    </row>
+    <row r="196" spans="1:7">
+      <c r="A196" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="B196" s="4"/>
+      <c r="C196" s="4"/>
+      <c r="D196" s="4"/>
+      <c r="E196" s="4"/>
+      <c r="F196" s="4"/>
+      <c r="G196" s="3"/>
+    </row>
+    <row r="197" spans="1:7">
+      <c r="A197" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="B197" s="4"/>
+      <c r="C197" s="4"/>
+      <c r="D197" s="4"/>
+      <c r="E197" s="4"/>
+      <c r="F197" s="4"/>
+      <c r="G197" s="3"/>
+    </row>
+    <row r="198" spans="1:7">
+      <c r="A198" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="B198" s="4"/>
+      <c r="C198" s="4"/>
+      <c r="D198" s="4"/>
+      <c r="E198" s="4"/>
+      <c r="F198" s="4"/>
+      <c r="G198" s="3"/>
+    </row>
+    <row r="199" spans="1:7">
+      <c r="A199" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="B199" s="4"/>
+      <c r="C199" s="4"/>
+      <c r="D199" s="4"/>
+      <c r="E199" s="4"/>
+      <c r="F199" s="4"/>
+      <c r="G199" s="3"/>
+    </row>
+    <row r="200" spans="1:7">
+      <c r="A200" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="B200" s="4"/>
+      <c r="C200" s="4"/>
+      <c r="D200" s="4"/>
+      <c r="E200" s="4"/>
+      <c r="F200" s="4"/>
+      <c r="G200" s="3"/>
+    </row>
+    <row r="201" spans="1:7">
+      <c r="A201" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="B201" s="4"/>
+      <c r="C201" s="4"/>
+      <c r="D201" s="4"/>
+      <c r="E201" s="4"/>
+      <c r="F201" s="4"/>
+      <c r="G201" s="3"/>
+    </row>
+    <row r="202" spans="1:7">
+      <c r="A202" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="B202" s="4"/>
+      <c r="C202" s="4"/>
+      <c r="D202" s="4"/>
+      <c r="E202" s="4"/>
+      <c r="F202" s="4"/>
+      <c r="G202" s="3"/>
+    </row>
+    <row r="203" spans="1:7">
+      <c r="A203" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="B203" s="4"/>
+      <c r="C203" s="4"/>
+      <c r="D203" s="4"/>
+      <c r="E203" s="4"/>
+      <c r="F203" s="4"/>
+      <c r="G203" s="3"/>
+    </row>
+    <row r="204" spans="1:7">
+      <c r="A204" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="B204" s="4"/>
+      <c r="C204" s="4"/>
+      <c r="D204" s="4"/>
+      <c r="E204" s="4"/>
+      <c r="F204" s="4"/>
+      <c r="G204" s="3"/>
+    </row>
+    <row r="205" spans="1:7">
+      <c r="A205" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="B205" s="4"/>
+      <c r="C205" s="4"/>
+      <c r="D205" s="4"/>
+      <c r="E205" s="4"/>
+      <c r="F205" s="4"/>
+      <c r="G205" s="3"/>
+    </row>
+    <row r="206" spans="1:7">
+      <c r="A206" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="B206" s="4"/>
+      <c r="C206" s="4"/>
+      <c r="D206" s="4"/>
+      <c r="E206" s="4"/>
+      <c r="F206" s="4"/>
+      <c r="G206" s="3"/>
+    </row>
+    <row r="207" spans="1:7">
+      <c r="A207" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="B207" s="4"/>
+      <c r="C207" s="4"/>
+      <c r="D207" s="4"/>
+      <c r="E207" s="4"/>
+      <c r="F207" s="4"/>
+      <c r="G207" s="3"/>
+    </row>
+    <row r="208" spans="1:7">
+      <c r="A208" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="B208" s="4"/>
+      <c r="C208" s="4"/>
+      <c r="D208" s="4"/>
+      <c r="E208" s="4"/>
+      <c r="F208" s="4"/>
+      <c r="G208" s="3"/>
+    </row>
+    <row r="209" spans="1:7">
+      <c r="A209" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="B209" s="4"/>
+      <c r="C209" s="4"/>
+      <c r="D209" s="4"/>
+      <c r="E209" s="4"/>
+      <c r="F209" s="4"/>
+      <c r="G209" s="3"/>
+    </row>
+    <row r="210" spans="1:7">
+      <c r="A210" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="B210" s="4"/>
+      <c r="C210" s="4"/>
+      <c r="D210" s="4"/>
+      <c r="E210" s="4"/>
+      <c r="F210" s="4"/>
+      <c r="G210" s="3"/>
+    </row>
+    <row r="211" spans="1:7">
+      <c r="A211" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="B211" s="4"/>
+      <c r="C211" s="4"/>
+      <c r="D211" s="4"/>
+      <c r="E211" s="4"/>
+      <c r="F211" s="4"/>
+      <c r="G211" s="3"/>
+    </row>
+    <row r="212" spans="1:7">
+      <c r="A212" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="B212" s="4"/>
+      <c r="C212" s="4"/>
+      <c r="D212" s="4"/>
+      <c r="E212" s="4"/>
+      <c r="F212" s="4"/>
+      <c r="G212" s="3"/>
+    </row>
+    <row r="213" spans="1:7">
+      <c r="A213" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="B213" s="4"/>
+      <c r="C213" s="4"/>
+      <c r="D213" s="4"/>
+      <c r="E213" s="4"/>
+      <c r="F213" s="4"/>
+      <c r="G213" s="3"/>
+    </row>
+    <row r="214" spans="1:7">
+      <c r="A214" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="B214" s="4"/>
+      <c r="C214" s="4"/>
+      <c r="D214" s="4"/>
+      <c r="E214" s="4"/>
+      <c r="F214" s="4"/>
+      <c r="G214" s="3"/>
+    </row>
+    <row r="215" spans="1:7">
+      <c r="A215" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="B215" s="4"/>
+      <c r="C215" s="4"/>
+      <c r="D215" s="4"/>
+      <c r="E215" s="4"/>
+      <c r="F215" s="4"/>
+      <c r="G215" s="3"/>
+    </row>
+    <row r="216" spans="1:7">
+      <c r="A216" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="B216" s="4"/>
+      <c r="C216" s="4"/>
+      <c r="D216" s="4"/>
+      <c r="E216" s="4"/>
+      <c r="F216" s="4"/>
+      <c r="G216" s="3"/>
+    </row>
+    <row r="217" spans="1:7">
+      <c r="A217" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="B217" s="4"/>
+      <c r="C217" s="4"/>
+      <c r="D217" s="4"/>
+      <c r="E217" s="4"/>
+      <c r="F217" s="4"/>
+      <c r="G217" s="3"/>
+    </row>
+    <row r="218" spans="1:7">
+      <c r="A218" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="B218" s="4"/>
+      <c r="C218" s="4"/>
+      <c r="D218" s="4"/>
+      <c r="E218" s="4"/>
+      <c r="F218" s="4"/>
+      <c r="G218" s="3"/>
+    </row>
+    <row r="219" spans="1:7">
+      <c r="A219" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="B219" s="4"/>
+      <c r="C219" s="4"/>
+      <c r="D219" s="4"/>
+      <c r="E219" s="4"/>
+      <c r="F219" s="4"/>
+      <c r="G219" s="3"/>
+    </row>
+    <row r="220" spans="1:7">
+      <c r="A220" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="B220" s="4"/>
+      <c r="C220" s="4"/>
+      <c r="D220" s="4"/>
+      <c r="E220" s="4"/>
+      <c r="F220" s="4"/>
+      <c r="G220" s="3"/>
+    </row>
+    <row r="221" spans="1:7">
+      <c r="A221" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="B221" s="4"/>
+      <c r="C221" s="4"/>
+      <c r="D221" s="4"/>
+      <c r="E221" s="4"/>
+      <c r="F221" s="4"/>
+      <c r="G221" s="3"/>
+    </row>
+    <row r="222" spans="1:7">
+      <c r="A222" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="B222" s="4"/>
+      <c r="C222" s="4"/>
+      <c r="D222" s="4"/>
+      <c r="E222" s="4"/>
+      <c r="F222" s="4"/>
+      <c r="G222" s="3"/>
+    </row>
+    <row r="223" spans="1:7">
+      <c r="A223" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="B223" s="4"/>
+      <c r="C223" s="4"/>
+      <c r="D223" s="4"/>
+      <c r="E223" s="4"/>
+      <c r="F223" s="4"/>
+      <c r="G223" s="3"/>
+    </row>
+    <row r="224" spans="1:7">
+      <c r="A224" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="B224" s="4"/>
+      <c r="C224" s="4"/>
+      <c r="D224" s="4"/>
+      <c r="E224" s="4"/>
+      <c r="F224" s="4"/>
+      <c r="G224" s="3"/>
+    </row>
+    <row r="225" spans="1:7">
+      <c r="A225" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="B225" s="4"/>
+      <c r="C225" s="4"/>
+      <c r="D225" s="4"/>
+      <c r="E225" s="4"/>
+      <c r="F225" s="4"/>
+      <c r="G225" s="3"/>
+    </row>
+    <row r="226" spans="1:7">
+      <c r="A226" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="B226" s="4"/>
+      <c r="C226" s="4"/>
+      <c r="D226" s="4"/>
+      <c r="E226" s="4"/>
+      <c r="F226" s="4"/>
+      <c r="G226" s="3"/>
+    </row>
+    <row r="227" spans="1:7">
+      <c r="A227" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="B227" s="4"/>
+      <c r="C227" s="4"/>
+      <c r="D227" s="4"/>
+      <c r="E227" s="4"/>
+      <c r="F227" s="4"/>
+      <c r="G227" s="3"/>
+    </row>
+    <row r="228" spans="1:7">
+      <c r="A228" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="B228" s="4"/>
+      <c r="C228" s="4"/>
+      <c r="D228" s="4"/>
+      <c r="E228" s="4"/>
+      <c r="F228" s="4"/>
+      <c r="G228" s="3"/>
+    </row>
+    <row r="229" spans="1:7">
+      <c r="A229" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="B229" s="4"/>
+      <c r="C229" s="4"/>
+      <c r="D229" s="4"/>
+      <c r="E229" s="4"/>
+      <c r="F229" s="4"/>
+      <c r="G229" s="3"/>
+    </row>
+    <row r="230" spans="1:7">
+      <c r="A230" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="B230" s="4"/>
+      <c r="C230" s="4"/>
+      <c r="D230" s="4"/>
+      <c r="E230" s="4"/>
+      <c r="F230" s="4"/>
+      <c r="G230" s="3"/>
+    </row>
+    <row r="231" spans="1:7">
+      <c r="A231" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="B231" s="4"/>
+      <c r="C231" s="4"/>
+      <c r="D231" s="4"/>
+      <c r="E231" s="4"/>
+      <c r="F231" s="4"/>
+      <c r="G231" s="3"/>
+    </row>
+    <row r="232" spans="1:7">
+      <c r="A232" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="B232" s="4"/>
+      <c r="C232" s="4"/>
+      <c r="D232" s="4"/>
+      <c r="E232" s="4"/>
+      <c r="F232" s="4"/>
+      <c r="G232" s="3"/>
+    </row>
+    <row r="233" spans="1:7">
+      <c r="A233" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="B233" s="4"/>
+      <c r="C233" s="4"/>
+      <c r="D233" s="4"/>
+      <c r="E233" s="4"/>
+      <c r="F233" s="4"/>
+      <c r="G233" s="3"/>
+    </row>
+    <row r="234" spans="1:7">
+      <c r="A234" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="B234" s="4"/>
+      <c r="C234" s="4"/>
+      <c r="D234" s="4"/>
+      <c r="E234" s="4"/>
+      <c r="F234" s="4"/>
+      <c r="G234" s="3"/>
+    </row>
+    <row r="235" spans="1:7">
+      <c r="A235" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="B235" s="4"/>
+      <c r="C235" s="4"/>
+      <c r="D235" s="4"/>
+      <c r="E235" s="4"/>
+      <c r="F235" s="4"/>
+      <c r="G235" s="3"/>
+    </row>
+    <row r="236" spans="1:7">
+      <c r="A236" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="B236" s="4"/>
+      <c r="C236" s="4"/>
+      <c r="D236" s="4"/>
+      <c r="E236" s="4"/>
+      <c r="F236" s="4"/>
+      <c r="G236" s="3"/>
+    </row>
+    <row r="237" spans="1:7">
+      <c r="A237" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="B237" s="4"/>
+      <c r="C237" s="4"/>
+      <c r="D237" s="4"/>
+      <c r="E237" s="4"/>
+      <c r="F237" s="4"/>
+      <c r="G237" s="3"/>
+    </row>
+    <row r="238" spans="1:7">
+      <c r="A238" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="B238" s="4"/>
+      <c r="C238" s="4"/>
+      <c r="D238" s="4"/>
+      <c r="E238" s="4"/>
+      <c r="F238" s="4"/>
+      <c r="G238" s="3"/>
+    </row>
+    <row r="239" spans="1:7">
+      <c r="A239" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="B239" s="4"/>
+      <c r="C239" s="4"/>
+      <c r="D239" s="4"/>
+      <c r="E239" s="4"/>
+      <c r="F239" s="4"/>
+      <c r="G239" s="3"/>
+    </row>
+    <row r="240" spans="1:7">
+      <c r="A240" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="B240" s="4"/>
+      <c r="C240" s="4"/>
+      <c r="D240" s="4"/>
+      <c r="E240" s="4"/>
+      <c r="F240" s="4"/>
+      <c r="G240" s="3"/>
+    </row>
+    <row r="241" spans="1:7">
+      <c r="A241" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="B241" s="4"/>
+      <c r="C241" s="4"/>
+      <c r="D241" s="4"/>
+      <c r="E241" s="4"/>
+      <c r="F241" s="4"/>
+      <c r="G241" s="3"/>
+    </row>
+    <row r="242" spans="1:7">
+      <c r="A242" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="B242" s="4"/>
+      <c r="C242" s="4"/>
+      <c r="D242" s="4"/>
+      <c r="E242" s="4"/>
+      <c r="F242" s="4"/>
+      <c r="G242" s="3"/>
+    </row>
+    <row r="243" spans="1:7">
+      <c r="A243" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="B243" s="4"/>
+      <c r="C243" s="4"/>
+      <c r="D243" s="4"/>
+      <c r="E243" s="4"/>
+      <c r="F243" s="4"/>
+      <c r="G243" s="3"/>
+    </row>
+    <row r="244" spans="1:7">
+      <c r="A244" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="B244" s="4"/>
+      <c r="C244" s="4"/>
+      <c r="D244" s="4"/>
+      <c r="E244" s="4"/>
+      <c r="F244" s="4"/>
+      <c r="G244" s="3"/>
+    </row>
+    <row r="245" spans="1:7">
+      <c r="A245" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="B245" s="4"/>
+      <c r="C245" s="4"/>
+      <c r="D245" s="4"/>
+      <c r="E245" s="4"/>
+      <c r="F245" s="4"/>
+      <c r="G245" s="3"/>
+    </row>
+    <row r="246" spans="1:7">
+      <c r="A246" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="B246" s="4"/>
+      <c r="C246" s="4"/>
+      <c r="D246" s="4"/>
+      <c r="E246" s="4"/>
+      <c r="F246" s="4"/>
+      <c r="G246" s="3"/>
+    </row>
+    <row r="247" spans="1:7">
+      <c r="A247" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="B247" s="4"/>
+      <c r="C247" s="4"/>
+      <c r="D247" s="4"/>
+      <c r="E247" s="4"/>
+      <c r="F247" s="4"/>
+      <c r="G247" s="3"/>
+    </row>
+    <row r="248" spans="1:7">
+      <c r="A248" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="B248" s="4"/>
+      <c r="C248" s="4"/>
+      <c r="D248" s="4"/>
+      <c r="E248" s="4"/>
+      <c r="F248" s="4"/>
+      <c r="G248" s="3"/>
+    </row>
+    <row r="249" spans="1:7">
+      <c r="A249" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="B249" s="4"/>
+      <c r="C249" s="4"/>
+      <c r="D249" s="4"/>
+      <c r="E249" s="4"/>
+      <c r="F249" s="4"/>
+      <c r="G249" s="3"/>
+    </row>
+    <row r="250" spans="1:7">
+      <c r="A250" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="B250" s="4"/>
+      <c r="C250" s="4"/>
+      <c r="D250" s="4"/>
+      <c r="E250" s="4"/>
+      <c r="F250" s="4"/>
+      <c r="G250" s="3"/>
+    </row>
+    <row r="251" spans="1:7">
+      <c r="A251" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="B251" s="4"/>
+      <c r="C251" s="4"/>
+      <c r="D251" s="4"/>
+      <c r="E251" s="4"/>
+      <c r="F251" s="4"/>
+      <c r="G251" s="3"/>
+    </row>
+    <row r="252" spans="1:7">
+      <c r="A252" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="B252" s="4"/>
+      <c r="C252" s="4"/>
+      <c r="D252" s="4"/>
+      <c r="E252" s="4"/>
+      <c r="F252" s="4"/>
+      <c r="G252" s="3"/>
+    </row>
+    <row r="253" spans="1:7">
+      <c r="A253" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="B253" s="4"/>
+      <c r="C253" s="4"/>
+      <c r="D253" s="4"/>
+      <c r="E253" s="4"/>
+      <c r="F253" s="4"/>
+      <c r="G253" s="3"/>
+    </row>
+    <row r="254" spans="1:7">
+      <c r="A254" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="B254" s="4"/>
+      <c r="C254" s="4"/>
+      <c r="D254" s="4"/>
+      <c r="E254" s="4"/>
+      <c r="F254" s="4"/>
+      <c r="G254" s="3"/>
+    </row>
+    <row r="255" spans="1:7">
+      <c r="A255" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="B255" s="4"/>
+      <c r="C255" s="4"/>
+      <c r="D255" s="4"/>
+      <c r="E255" s="4"/>
+      <c r="F255" s="4"/>
+      <c r="G255" s="3"/>
+    </row>
+    <row r="256" spans="1:7">
+      <c r="A256" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="B256" s="4"/>
+      <c r="C256" s="4"/>
+      <c r="D256" s="4"/>
+      <c r="E256" s="4"/>
+      <c r="F256" s="4"/>
+      <c r="G256" s="3"/>
+    </row>
+    <row r="257" spans="1:7">
+      <c r="A257" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="B257" s="4"/>
+      <c r="C257" s="4"/>
+      <c r="D257" s="4"/>
+      <c r="E257" s="4"/>
+      <c r="F257" s="4"/>
+      <c r="G257" s="3"/>
+    </row>
+    <row r="258" spans="1:7">
+      <c r="A258" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="B258" s="4"/>
+      <c r="C258" s="4"/>
+      <c r="D258" s="4"/>
+      <c r="E258" s="4"/>
+      <c r="F258" s="4"/>
+      <c r="G258" s="3"/>
+    </row>
+    <row r="259" spans="1:7">
+      <c r="A259" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="B259" s="4"/>
+      <c r="C259" s="4"/>
+      <c r="D259" s="4"/>
+      <c r="E259" s="4"/>
+      <c r="F259" s="4"/>
+      <c r="G259" s="3"/>
+    </row>
+    <row r="260" spans="1:7">
+      <c r="A260" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="B260" s="4"/>
+      <c r="C260" s="4"/>
+      <c r="D260" s="4"/>
+      <c r="E260" s="4"/>
+      <c r="F260" s="4"/>
+      <c r="G260" s="3"/>
+    </row>
+    <row r="261" spans="1:7">
+      <c r="A261" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="B261" s="4"/>
+      <c r="C261" s="4"/>
+      <c r="D261" s="4"/>
+      <c r="E261" s="4"/>
+      <c r="F261" s="4"/>
+      <c r="G261" s="3"/>
+    </row>
+    <row r="262" spans="1:7">
+      <c r="A262" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="B262" s="4"/>
+      <c r="C262" s="4"/>
+      <c r="D262" s="4"/>
+      <c r="E262" s="4"/>
+      <c r="F262" s="4"/>
+      <c r="G262" s="3"/>
+    </row>
+    <row r="263" spans="1:7">
+      <c r="A263" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="B263" s="4"/>
+      <c r="C263" s="4"/>
+      <c r="D263" s="4"/>
+      <c r="E263" s="4"/>
+      <c r="F263" s="4"/>
+      <c r="G263" s="3"/>
+    </row>
+    <row r="264" spans="1:7">
+      <c r="A264" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="B264" s="4"/>
+      <c r="C264" s="4"/>
+      <c r="D264" s="4"/>
+      <c r="E264" s="4"/>
+      <c r="F264" s="4"/>
+      <c r="G264" s="3"/>
+    </row>
+    <row r="265" spans="1:7">
+      <c r="A265" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="B265" s="4"/>
+      <c r="C265" s="4"/>
+      <c r="D265" s="4"/>
+      <c r="E265" s="4"/>
+      <c r="F265" s="4"/>
+      <c r="G265" s="3"/>
+    </row>
+    <row r="266" spans="1:7">
+      <c r="A266" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="B266" s="4"/>
+      <c r="C266" s="4"/>
+      <c r="D266" s="4"/>
+      <c r="E266" s="4"/>
+      <c r="F266" s="4"/>
+      <c r="G266" s="3"/>
+    </row>
+    <row r="267" spans="1:7">
+      <c r="A267" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="B267" s="4"/>
+      <c r="C267" s="4"/>
+      <c r="D267" s="4"/>
+      <c r="E267" s="4"/>
+      <c r="F267" s="4"/>
+      <c r="G267" s="3"/>
+    </row>
+    <row r="268" spans="1:7">
+      <c r="A268" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="B268" s="4"/>
+      <c r="C268" s="4"/>
+      <c r="D268" s="4"/>
+      <c r="E268" s="4"/>
+      <c r="F268" s="4"/>
+      <c r="G268" s="3"/>
+    </row>
+    <row r="269" spans="1:7">
+      <c r="A269" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="B269" s="4"/>
+      <c r="C269" s="4"/>
+      <c r="D269" s="4"/>
+      <c r="E269" s="4"/>
+      <c r="F269" s="4"/>
+      <c r="G269" s="3"/>
+    </row>
+    <row r="270" spans="1:7">
+      <c r="A270" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="B270" s="4"/>
+      <c r="C270" s="4"/>
+      <c r="D270" s="4"/>
+      <c r="E270" s="4"/>
+      <c r="F270" s="4"/>
+      <c r="G270" s="3"/>
+    </row>
+    <row r="271" spans="1:7">
+      <c r="A271" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="B271" s="4"/>
+      <c r="C271" s="4"/>
+      <c r="D271" s="4"/>
+      <c r="E271" s="4"/>
+      <c r="F271" s="4"/>
+      <c r="G271" s="3"/>
+    </row>
+    <row r="272" spans="1:7">
+      <c r="A272" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="B272" s="4"/>
+      <c r="C272" s="4"/>
+      <c r="D272" s="4"/>
+      <c r="E272" s="4"/>
+      <c r="F272" s="4"/>
+      <c r="G272" s="3"/>
+    </row>
+    <row r="273" spans="1:7">
+      <c r="A273" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="B273" s="4"/>
+      <c r="C273" s="4"/>
+      <c r="D273" s="4"/>
+      <c r="E273" s="4"/>
+      <c r="F273" s="4"/>
+      <c r="G273" s="3"/>
+    </row>
+    <row r="274" spans="1:7">
+      <c r="A274" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="B274" s="4"/>
+      <c r="C274" s="4"/>
+      <c r="D274" s="4"/>
+      <c r="E274" s="4"/>
+      <c r="F274" s="4"/>
+      <c r="G274" s="3"/>
+    </row>
+    <row r="275" spans="1:7">
+      <c r="A275" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="B275" s="4"/>
+      <c r="C275" s="4"/>
+      <c r="D275" s="4"/>
+      <c r="E275" s="4"/>
+      <c r="F275" s="4"/>
+      <c r="G275" s="3"/>
+    </row>
+    <row r="276" spans="1:7">
+      <c r="A276" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="B276" s="4"/>
+      <c r="C276" s="4"/>
+      <c r="D276" s="4"/>
+      <c r="E276" s="4"/>
+      <c r="F276" s="4"/>
+      <c r="G276" s="3"/>
+    </row>
+    <row r="277" spans="1:7">
+      <c r="A277" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="B277" s="4"/>
+      <c r="C277" s="4"/>
+      <c r="D277" s="4"/>
+      <c r="E277" s="4"/>
+      <c r="F277" s="4"/>
+      <c r="G277" s="3"/>
+    </row>
+    <row r="278" spans="1:7">
+      <c r="A278" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="B278" s="4"/>
+      <c r="C278" s="4"/>
+      <c r="D278" s="4"/>
+      <c r="E278" s="4"/>
+      <c r="F278" s="4"/>
+      <c r="G278" s="3"/>
+    </row>
+    <row r="279" spans="1:7">
+      <c r="A279" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="B279" s="4"/>
+      <c r="C279" s="4"/>
+      <c r="D279" s="4"/>
+      <c r="E279" s="4"/>
+      <c r="F279" s="4"/>
+      <c r="G279" s="3"/>
+    </row>
+    <row r="280" spans="1:7">
+      <c r="A280" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="B280" s="4"/>
+      <c r="C280" s="4"/>
+      <c r="D280" s="4"/>
+      <c r="E280" s="4"/>
+      <c r="F280" s="4"/>
+      <c r="G280" s="3"/>
+    </row>
+    <row r="281" spans="1:7">
+      <c r="A281" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="B281" s="4"/>
+      <c r="C281" s="4"/>
+      <c r="D281" s="4"/>
+      <c r="E281" s="4"/>
+      <c r="F281" s="4"/>
+      <c r="G281" s="3"/>
+    </row>
+    <row r="282" spans="1:7">
+      <c r="A282" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="B282" s="4"/>
+      <c r="C282" s="4"/>
+      <c r="D282" s="4"/>
+      <c r="E282" s="4"/>
+      <c r="F282" s="4"/>
+      <c r="G282" s="3"/>
+    </row>
+    <row r="283" spans="1:7">
+      <c r="A283" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="B283" s="4"/>
+      <c r="C283" s="4"/>
+      <c r="D283" s="4"/>
+      <c r="E283" s="4"/>
+      <c r="F283" s="4"/>
+      <c r="G283" s="3"/>
+    </row>
+    <row r="284" spans="1:7">
+      <c r="A284" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="B284" s="4"/>
+      <c r="C284" s="4"/>
+      <c r="D284" s="4"/>
+      <c r="E284" s="4"/>
+      <c r="F284" s="4"/>
+      <c r="G284" s="3"/>
+    </row>
+    <row r="285" spans="1:7">
+      <c r="A285" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="B285" s="4"/>
+      <c r="C285" s="4"/>
+      <c r="D285" s="4"/>
+      <c r="E285" s="4"/>
+      <c r="F285" s="4"/>
+      <c r="G285" s="3"/>
+    </row>
+    <row r="286" spans="1:7">
+      <c r="A286" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="B286" s="4"/>
+      <c r="C286" s="4"/>
+      <c r="D286" s="4"/>
+      <c r="E286" s="4"/>
+      <c r="F286" s="4"/>
+      <c r="G286" s="3"/>
+    </row>
+    <row r="287" spans="1:7">
+      <c r="A287" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="B287" s="4"/>
+      <c r="C287" s="4"/>
+      <c r="D287" s="4"/>
+      <c r="E287" s="4"/>
+      <c r="F287" s="4"/>
+      <c r="G287" s="3"/>
+    </row>
+    <row r="288" spans="1:7">
+      <c r="A288" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="B288" s="4"/>
+      <c r="C288" s="4"/>
+      <c r="D288" s="4"/>
+      <c r="E288" s="4"/>
+      <c r="F288" s="4"/>
+      <c r="G288" s="3"/>
+    </row>
+    <row r="289" spans="1:7">
+      <c r="A289" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="B289" s="4"/>
+      <c r="C289" s="4"/>
+      <c r="D289" s="4"/>
+      <c r="E289" s="4"/>
+      <c r="F289" s="4"/>
+      <c r="G289" s="3"/>
+    </row>
+    <row r="290" spans="1:7">
+      <c r="A290" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="B290" s="4"/>
+      <c r="C290" s="4"/>
+      <c r="D290" s="4"/>
+      <c r="E290" s="4"/>
+      <c r="F290" s="4"/>
+      <c r="G290" s="3"/>
+    </row>
+    <row r="291" spans="1:7">
+      <c r="A291" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="B291" s="4"/>
+      <c r="C291" s="4"/>
+      <c r="D291" s="4"/>
+      <c r="E291" s="4"/>
+      <c r="F291" s="4"/>
+      <c r="G291" s="3"/>
+    </row>
+    <row r="292" spans="1:7">
+      <c r="A292" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="B292" s="4"/>
+      <c r="C292" s="4"/>
+      <c r="D292" s="4"/>
+      <c r="E292" s="4"/>
+      <c r="F292" s="4"/>
+      <c r="G292" s="3"/>
+    </row>
+    <row r="293" spans="1:7">
+      <c r="A293" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="B293" s="4"/>
+      <c r="C293" s="4"/>
+      <c r="D293" s="4"/>
+      <c r="E293" s="4"/>
+      <c r="F293" s="4"/>
+      <c r="G293" s="3"/>
+    </row>
+    <row r="294" spans="1:7">
+      <c r="A294" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="B294" s="4"/>
+      <c r="C294" s="4"/>
+      <c r="D294" s="4"/>
+      <c r="E294" s="4"/>
+      <c r="F294" s="4"/>
+      <c r="G294" s="3"/>
+    </row>
+    <row r="295" spans="1:7">
+      <c r="A295" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="B295" s="4"/>
+      <c r="C295" s="4"/>
+      <c r="D295" s="4"/>
+      <c r="E295" s="4"/>
+      <c r="F295" s="4"/>
+      <c r="G295" s="3"/>
+    </row>
+    <row r="296" spans="1:7">
+      <c r="A296" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="B296" s="4"/>
+      <c r="C296" s="4"/>
+      <c r="D296" s="4"/>
+      <c r="E296" s="4"/>
+      <c r="F296" s="4"/>
+      <c r="G296" s="3"/>
+    </row>
+    <row r="297" spans="1:7">
+      <c r="A297" s="3" t="s">
+        <v>435</v>
+      </c>
+      <c r="B297" s="4"/>
+      <c r="C297" s="4"/>
+      <c r="D297" s="4"/>
+      <c r="E297" s="4"/>
+      <c r="F297" s="4"/>
+      <c r="G297" s="3"/>
+    </row>
+    <row r="298" spans="1:7">
+      <c r="A298" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="B298" s="4"/>
+      <c r="C298" s="4"/>
+      <c r="D298" s="4"/>
+      <c r="E298" s="4"/>
+      <c r="F298" s="4"/>
+      <c r="G298" s="3"/>
+    </row>
+    <row r="299" spans="1:7">
+      <c r="A299" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="B299" s="4"/>
+      <c r="C299" s="4"/>
+      <c r="D299" s="4"/>
+      <c r="E299" s="4"/>
+      <c r="F299" s="4"/>
+      <c r="G299" s="3"/>
+    </row>
+    <row r="300" spans="1:7">
+      <c r="A300" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="B300" s="4"/>
+      <c r="C300" s="4"/>
+      <c r="D300" s="4"/>
+      <c r="E300" s="4"/>
+      <c r="F300" s="4"/>
+      <c r="G300" s="3"/>
+    </row>
+    <row r="301" spans="1:7">
+      <c r="A301" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="B301" s="4"/>
+      <c r="C301" s="4"/>
+      <c r="D301" s="4"/>
+      <c r="E301" s="4"/>
+      <c r="F301" s="4"/>
+      <c r="G301" s="3"/>
+    </row>
+    <row r="302" spans="1:7">
+      <c r="A302" s="3" t="s">
+        <v>440</v>
+      </c>
+      <c r="B302" s="4"/>
+      <c r="C302" s="4"/>
+      <c r="D302" s="4"/>
+      <c r="E302" s="4"/>
+      <c r="F302" s="4"/>
+      <c r="G302" s="3"/>
+    </row>
+    <row r="303" spans="1:7">
+      <c r="A303" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="B303" s="4"/>
+      <c r="C303" s="4"/>
+      <c r="D303" s="4"/>
+      <c r="E303" s="4"/>
+      <c r="F303" s="4"/>
+      <c r="G303" s="3"/>
+    </row>
+    <row r="304" spans="1:7">
+      <c r="A304" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="B304" s="4"/>
+      <c r="C304" s="4"/>
+      <c r="D304" s="4"/>
+      <c r="E304" s="4"/>
+      <c r="F304" s="4"/>
+      <c r="G304" s="3"/>
+    </row>
+    <row r="305" spans="1:7">
+      <c r="A305" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="B305" s="4"/>
+      <c r="C305" s="4"/>
+      <c r="D305" s="4"/>
+      <c r="E305" s="4"/>
+      <c r="F305" s="4"/>
+      <c r="G305" s="3"/>
+    </row>
+    <row r="306" spans="1:7">
+      <c r="A306" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="B306" s="4"/>
+      <c r="C306" s="4"/>
+      <c r="D306" s="4"/>
+      <c r="E306" s="4"/>
+      <c r="F306" s="4"/>
+      <c r="G306" s="3"/>
+    </row>
+    <row r="307" spans="1:7">
+      <c r="A307" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="B307" s="4"/>
+      <c r="C307" s="4"/>
+      <c r="D307" s="4"/>
+      <c r="E307" s="4"/>
+      <c r="F307" s="4"/>
+      <c r="G307" s="3"/>
+    </row>
+    <row r="308" spans="1:7">
+      <c r="A308" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="B308" s="4"/>
+      <c r="C308" s="4"/>
+      <c r="D308" s="4"/>
+      <c r="E308" s="4"/>
+      <c r="F308" s="4"/>
+      <c r="G308" s="3"/>
+    </row>
+    <row r="309" spans="1:7">
+      <c r="A309" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="B309" s="4"/>
+      <c r="C309" s="4"/>
+      <c r="D309" s="4"/>
+      <c r="E309" s="4"/>
+      <c r="F309" s="4"/>
+      <c r="G309" s="3"/>
+    </row>
+    <row r="310" spans="1:7">
+      <c r="A310" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="B310" s="4"/>
+      <c r="C310" s="4"/>
+      <c r="D310" s="4"/>
+      <c r="E310" s="4"/>
+      <c r="F310" s="4"/>
+      <c r="G310" s="3"/>
+    </row>
+    <row r="311" spans="1:7">
+      <c r="A311" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="B311" s="4"/>
+      <c r="C311" s="4"/>
+      <c r="D311" s="4"/>
+      <c r="E311" s="4"/>
+      <c r="F311" s="4"/>
+      <c r="G311" s="3"/>
+    </row>
+    <row r="312" spans="1:7">
+      <c r="A312" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="B312" s="4"/>
+      <c r="C312" s="4"/>
+      <c r="D312" s="4"/>
+      <c r="E312" s="4"/>
+      <c r="F312" s="4"/>
+      <c r="G312" s="3"/>
+    </row>
+    <row r="313" spans="1:7">
+      <c r="A313" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="B313" s="4"/>
+      <c r="C313" s="4"/>
+      <c r="D313" s="4"/>
+      <c r="E313" s="4"/>
+      <c r="F313" s="4"/>
+      <c r="G313" s="3"/>
+    </row>
+    <row r="314" spans="1:7">
+      <c r="A314" s="3" t="s">
+        <v>452</v>
+      </c>
+      <c r="B314" s="4"/>
+      <c r="C314" s="4"/>
+      <c r="D314" s="4"/>
+      <c r="E314" s="4"/>
+      <c r="F314" s="4"/>
+      <c r="G314" s="3"/>
+    </row>
+    <row r="315" spans="1:7">
+      <c r="A315" s="3" t="s">
+        <v>453</v>
+      </c>
+      <c r="B315" s="4"/>
+      <c r="C315" s="4"/>
+      <c r="D315" s="4"/>
+      <c r="E315" s="4"/>
+      <c r="F315" s="4"/>
+      <c r="G315" s="3"/>
+    </row>
+    <row r="316" spans="1:7">
+      <c r="A316" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="B316" s="4"/>
+      <c r="C316" s="4"/>
+      <c r="D316" s="4"/>
+      <c r="E316" s="4"/>
+      <c r="F316" s="4"/>
+      <c r="G316" s="3"/>
+    </row>
+    <row r="317" spans="1:7">
+      <c r="A317" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="B317" s="4"/>
+      <c r="C317" s="4"/>
+      <c r="D317" s="4"/>
+      <c r="E317" s="4"/>
+      <c r="F317" s="4"/>
+      <c r="G317" s="3"/>
+    </row>
+    <row r="318" spans="1:7">
+      <c r="A318" s="3" t="s">
+        <v>456</v>
+      </c>
+      <c r="B318" s="4"/>
+      <c r="C318" s="4"/>
+      <c r="D318" s="4"/>
+      <c r="E318" s="4"/>
+      <c r="F318" s="4"/>
+      <c r="G318" s="3"/>
+    </row>
+    <row r="319" spans="1:7">
+      <c r="A319" s="3" t="s">
+        <v>457</v>
+      </c>
+      <c r="B319" s="4"/>
+      <c r="C319" s="4"/>
+      <c r="D319" s="4"/>
+      <c r="E319" s="4"/>
+      <c r="F319" s="4"/>
+      <c r="G319" s="3"/>
+    </row>
+    <row r="320" spans="1:7">
+      <c r="A320" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="B320" s="4"/>
+      <c r="C320" s="4"/>
+      <c r="D320" s="4"/>
+      <c r="E320" s="4"/>
+      <c r="F320" s="4"/>
+      <c r="G320" s="3"/>
+    </row>
+    <row r="321" spans="1:7">
+      <c r="A321" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="B321" s="4"/>
+      <c r="C321" s="4"/>
+      <c r="D321" s="4"/>
+      <c r="E321" s="4"/>
+      <c r="F321" s="4"/>
+      <c r="G321" s="3"/>
+    </row>
+    <row r="322" spans="1:7">
+      <c r="A322" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="B322" s="4"/>
+      <c r="C322" s="4"/>
+      <c r="D322" s="4"/>
+      <c r="E322" s="4"/>
+      <c r="F322" s="4"/>
+      <c r="G322" s="3"/>
+    </row>
+    <row r="323" spans="1:7">
+      <c r="A323" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="B323" s="4"/>
+      <c r="C323" s="4"/>
+      <c r="D323" s="4"/>
+      <c r="E323" s="4"/>
+      <c r="F323" s="4"/>
+      <c r="G323" s="3"/>
+    </row>
+    <row r="324" spans="1:7">
+      <c r="A324" s="3" t="s">
+        <v>462</v>
+      </c>
+      <c r="B324" s="4"/>
+      <c r="C324" s="4"/>
+      <c r="D324" s="4"/>
+      <c r="E324" s="4"/>
+      <c r="F324" s="4"/>
+      <c r="G324" s="3"/>
+    </row>
+    <row r="325" spans="1:7">
+      <c r="A325" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="B325" s="4"/>
+      <c r="C325" s="4"/>
+      <c r="D325" s="4"/>
+      <c r="E325" s="4"/>
+      <c r="F325" s="4"/>
+      <c r="G325" s="3"/>
+    </row>
+    <row r="326" spans="1:7">
+      <c r="A326" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="B326" s="4"/>
+      <c r="C326" s="4"/>
+      <c r="D326" s="4"/>
+      <c r="E326" s="4"/>
+      <c r="F326" s="4"/>
+      <c r="G326" s="3"/>
+    </row>
+    <row r="327" spans="1:7">
+      <c r="A327" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="B327" s="4"/>
+      <c r="C327" s="4"/>
+      <c r="D327" s="4"/>
+      <c r="E327" s="4"/>
+      <c r="F327" s="4"/>
+      <c r="G327" s="3"/>
+    </row>
+    <row r="328" spans="1:7">
+      <c r="A328" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="B328" s="4"/>
+      <c r="C328" s="4"/>
+      <c r="D328" s="4"/>
+      <c r="E328" s="4"/>
+      <c r="F328" s="4"/>
+      <c r="G328" s="3"/>
+    </row>
+    <row r="329" spans="1:7">
+      <c r="A329" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="B329" s="4"/>
+      <c r="C329" s="4"/>
+      <c r="D329" s="4"/>
+      <c r="E329" s="4"/>
+      <c r="F329" s="4"/>
+      <c r="G329" s="3"/>
+    </row>
+    <row r="330" spans="1:7">
+      <c r="A330" s="3" t="s">
+        <v>468</v>
+      </c>
+      <c r="B330" s="4"/>
+      <c r="C330" s="4"/>
+      <c r="D330" s="4"/>
+      <c r="E330" s="4"/>
+      <c r="F330" s="4"/>
+      <c r="G330" s="3"/>
+    </row>
+    <row r="331" spans="1:7">
+      <c r="A331" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="B331" s="4"/>
+      <c r="C331" s="4"/>
+      <c r="D331" s="4"/>
+      <c r="E331" s="4"/>
+      <c r="F331" s="4"/>
+      <c r="G331" s="3"/>
+    </row>
+    <row r="332" spans="1:7">
+      <c r="A332" s="3" t="s">
+        <v>470</v>
+      </c>
+      <c r="B332" s="4"/>
+      <c r="C332" s="4"/>
+      <c r="D332" s="4"/>
+      <c r="E332" s="4"/>
+      <c r="F332" s="4"/>
+      <c r="G332" s="3"/>
+    </row>
+    <row r="333" spans="1:7">
+      <c r="A333" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="B333" s="4"/>
+      <c r="C333" s="4"/>
+      <c r="D333" s="4"/>
+      <c r="E333" s="4"/>
+      <c r="F333" s="4"/>
+      <c r="G333" s="3"/>
+    </row>
+    <row r="334" spans="1:7">
+      <c r="A334" s="3" t="s">
+        <v>472</v>
+      </c>
+      <c r="B334" s="4"/>
+      <c r="C334" s="4"/>
+      <c r="D334" s="4"/>
+      <c r="E334" s="4"/>
+      <c r="F334" s="4"/>
+      <c r="G334" s="3"/>
+    </row>
+    <row r="335" spans="1:7">
+      <c r="A335" s="3" t="s">
+        <v>542</v>
+      </c>
+      <c r="B335" s="4"/>
+      <c r="C335" s="4"/>
+      <c r="D335" s="4"/>
+      <c r="E335" s="4"/>
+      <c r="F335" s="4"/>
+      <c r="G335" s="3"/>
+    </row>
+    <row r="336" spans="1:7">
+      <c r="A336" s="3" t="s">
+        <v>543</v>
+      </c>
+      <c r="B336" s="4"/>
+      <c r="C336" s="4"/>
+      <c r="D336" s="4"/>
+      <c r="E336" s="4"/>
+      <c r="F336" s="4"/>
+      <c r="G336" s="3"/>
+    </row>
+    <row r="337" spans="1:7">
+      <c r="A337" s="3" t="s">
+        <v>544</v>
+      </c>
+      <c r="B337" s="4"/>
+      <c r="C337" s="4"/>
+      <c r="D337" s="4"/>
+      <c r="E337" s="4"/>
+      <c r="F337" s="4"/>
+      <c r="G337" s="3"/>
+    </row>
+    <row r="338" spans="1:7">
+      <c r="A338" s="3" t="s">
+        <v>545</v>
+      </c>
+      <c r="B338" s="4"/>
+      <c r="C338" s="4"/>
+      <c r="D338" s="4"/>
+      <c r="E338" s="4"/>
+      <c r="F338" s="4"/>
+      <c r="G338" s="3"/>
+    </row>
+    <row r="339" spans="1:7">
+      <c r="A339" s="3" t="s">
+        <v>546</v>
+      </c>
+      <c r="B339" s="4"/>
+      <c r="C339" s="4"/>
+      <c r="D339" s="4"/>
+      <c r="E339" s="4"/>
+      <c r="F339" s="4"/>
+      <c r="G339" s="3"/>
+    </row>
+    <row r="340" spans="1:7">
+      <c r="A340" s="3" t="s">
+        <v>547</v>
+      </c>
+      <c r="B340" s="4"/>
+      <c r="C340" s="4"/>
+      <c r="D340" s="4"/>
+      <c r="E340" s="4"/>
+      <c r="F340" s="4"/>
+      <c r="G340" s="3"/>
+    </row>
+    <row r="341" spans="1:7">
+      <c r="A341" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="B341" s="4"/>
+      <c r="C341" s="4"/>
+      <c r="D341" s="4"/>
+      <c r="E341" s="4"/>
+      <c r="F341" s="4"/>
+      <c r="G341" s="3"/>
+    </row>
+    <row r="342" spans="1:7">
+      <c r="A342" s="3" t="s">
+        <v>549</v>
+      </c>
+      <c r="B342" s="4"/>
+      <c r="C342" s="4"/>
+      <c r="D342" s="4"/>
+      <c r="E342" s="4"/>
+      <c r="F342" s="4"/>
+      <c r="G342" s="3"/>
     </row>
   </sheetData>
+  <autoFilter ref="A2:H342" xr:uid="{833B9C12-88F9-F440-902B-BDAD178A24F6}"/>
   <phoneticPr fontId="1"/>
-  <conditionalFormatting sqref="A3:G102">
-    <cfRule type="expression" dxfId="0" priority="1">
+  <conditionalFormatting sqref="A3:G342">
+    <cfRule type="expression" dxfId="0" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>

--- a/docs/確認事項リスト.xlsx
+++ b/docs/確認事項リスト.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A581A4D-724D-0044-829A-003ECFD84904}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9506CCBC-C77D-644A-A085-5CF25612E002}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{E987AAC5-D7CB-4143-BFFD-E0642F54BEB6}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1014" uniqueCount="599">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1104" uniqueCount="615">
   <si>
     <t>質問</t>
     <rPh sb="0" eb="2">
@@ -2417,31 +2417,13 @@
     <t>はい、公開APIとして認証認可なしで取得可能です。</t>
   </si>
   <si>
-    <t>はい、BookPolicy により他ユーザーの書籍編集アクセスは 403 Forbidden を返してください。</t>
-  </si>
-  <si>
-    <t>はい、ReviewPolicy により他ユーザーのレビュー編集アクセスは 403 Forbidden を返してください。</t>
-  </si>
-  <si>
-    <t>はい、403 Forbidden とともに { "error": "この操作を実行する権限がありません。" } のJSONを返してください。</t>
-  </si>
-  <si>
-    <t>はい、ReadingPlanPolicy により他ユーザーの計画編集アクセスは 403 Forbidden を返してください。（なお、完了済み completed 計画の編集も 403 となります）</t>
-  </si>
-  <si>
     <t>はい、size:13 による13桁チェックおよび unique:books,isbn による一意性チェックが必要です。エラーメッセージは「ISBNは13桁で入力してください。」「そのISBNは既に使用されています。」としてください。</t>
   </si>
   <si>
     <t>はい、Rule::unique('books')-&gt;ignore($this-&gt;book) により自身のレコードを除外する設計で問題ありません。</t>
   </si>
   <si>
-    <t>仕様上、同一ユーザーが同一書籍に対して複数回レビューを投稿することは可能です。</t>
-  </si>
-  <si>
     <t>はい、いいね機能はトグル処理（review_likesテーブルの追加/解除）として動作します。</t>
-  </si>
-  <si>
-    <t>同一ユーザー×同一書籍で in_progress 状態の計画が既に存在する場合は新規作成不可（バリデーションエラー「この書籍は既に進行中の読書計画が存在します。」）とし、completed 後の再計画は許可します。</t>
   </si>
   <si>
     <t>回答済み</t>
@@ -2491,19 +2473,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ISBNは13桁固定で一意性チェックも入れる想定ですが、桁数チェックは必要ですか？
-エラーメッセージは「422 ValidationException」にて、Q-65と同様のエラーメッセージでよろしいですか？</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ISBNは13桁固定で一意性チェック(自信を除外)も入れる想定ですが、桁数チェックは必要ですか？
-エラーメッセージは「422 ValidationException」にて、Q-65と同様のエラーメッセージでよろしいですか？</t>
-    <rPh sb="19" eb="21">
-      <t>ジシn</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>画像URLは任意・最大255文字で設計しましたが、この制約で合っていますか？
 また、エラーメッセージは「画像URLは255文字以内で入力してください。」としましたがよろしいですか？</t>
     <rPh sb="1" eb="3">
@@ -2544,32 +2513,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ジャンル名は必須・最大255文字・一意性チェックを入れる想定ですが、この制約で合っていますか？
-また、エラーメッセージは「ジャンル名は入力必須です。」「ジャンル名は255文字以内で入力してください。」「既に使用されているジャンル名です。」としましたがよろしいですか？</t>
-    <rPh sb="6" eb="8">
-      <t>ヒッス</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>サイダイ</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>モジ</t>
-    </rPh>
-    <rPh sb="17" eb="20">
-      <t>１イ</t>
-    </rPh>
-    <rPh sb="25" eb="26">
-      <t>イレ</t>
-    </rPh>
-    <rPh sb="101" eb="102">
-      <t xml:space="preserve">スデニ </t>
-    </rPh>
-    <rPh sb="103" eb="105">
-      <t>シヨウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>著者は必須・最大255文字で設計しましたが、この制約で合っていますか？
 また、エラーメッセージは「著者は入力必須です。」「著者は255文字以内で入力してください。」としましたがよろしいですか？</t>
     <rPh sb="5" eb="12">
@@ -2627,122 +2570,8 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>APIでの一覧取得のページネーションの最大表示数は100件としましたが、この制約で合っていますか？
-エラーメッセージは「422 ValidationException」にて、「ページネーションの最大表示件数は100件です。」としましたがよろしいですか？
-また、デフォルトのページネーションは何件としますか？</t>
-    <rPh sb="5" eb="7">
-      <t>イチラn</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>シュトク</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>キノウ</t>
-    </rPh>
-    <rPh sb="97" eb="103">
-      <t>サイダイ</t>
-    </rPh>
-    <rPh sb="107" eb="108">
-      <t>ケn</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>キーワードは任意・最大255文字で設計しましたが、この制約で合っていますか？
-エラーメッセージは「422 ValidationException」にて、「キーワードは255文字以内で入力してください。」としましたがよろしいですか？</t>
-    <rPh sb="6" eb="8">
-      <t>ニn</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>サイダイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>タイトルは必須・最大255文字で設計しましたが、この制約で合っていますか？
-エラーメッセージは「422 ValidationException」にて、「タイトルは入力必須です。」「タイトルは255文字以内で入力してください。」としましたがよろしいですか？</t>
-    <rPh sb="5" eb="12">
-      <t>ヒッス</t>
-    </rPh>
-    <rPh sb="12" eb="13">
-      <t>ニn</t>
-    </rPh>
-    <rPh sb="13" eb="17">
-      <t>サイダイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ISBNは入力は必須ですか？
-エラーメッセージは「422 ValidationException」にて、「ISBNは入力必須です。」としましたがよろしいですか？</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>著者は必須・最大255文字で設計しましたが、この制約で合っていますか？
-エラーメッセージは「422 ValidationException」にて、「筆者は入力必須です。」「筆者は255文字以内で入力してください。」としましたがよろしいですか？</t>
-    <rPh sb="5" eb="12">
-      <t>ヒッス</t>
-    </rPh>
-    <rPh sb="12" eb="13">
-      <t>ニ_x0000_</t>
-    </rPh>
-    <rPh sb="13" eb="17">
-      <t>_x0005__x0007__x0003__x000C_</t>
-    </rPh>
-    <rPh sb="74" eb="76">
-      <t xml:space="preserve">_x0001__x0005__x000D__x0004_	</t>
-    </rPh>
-    <rPh sb="76" eb="77">
-      <t/>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>ISBNは入力は必須ですか？
 エラーメッセージは「ISBNは入力必須です。」としましたがよろしいですか？</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ジャンルは任意・登録されたジャンルのみ検索可能で設計しましたが、この制約で合っていますか？
-エラーメッセージは「422 ValidationException」にて、「登録されたジャンルのみ検索可能です。」としましたがよろしいですか？</t>
-    <rPh sb="6" eb="8">
-      <t>ニn</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="19" eb="23">
-      <t>ケンサク</t>
-    </rPh>
-    <rPh sb="84" eb="86">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="95" eb="97">
-      <t>ケンサク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ジャンルは任意・登録されたジャンルのみ選択可能で設計しましたが、この制約で合っていますか？
-エラーメッセージは「422 ValidationException」にて、「登録されたジャンルのみ選択可能です。」としましたがよろしいですか？</t>
-    <rPh sb="0" eb="6">
-      <t>ヒッス</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>ニn</t>
-    </rPh>
-    <rPh sb="7" eb="11">
-      <t>サイダイ</t>
-    </rPh>
-    <rPh sb="19" eb="21">
-      <t>🧺</t>
-    </rPh>
-    <rPh sb="21" eb="23">
-      <t>カノウ</t>
-    </rPh>
-    <rPh sb="84" eb="86">
-      <t>トウロク</t>
-    </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -2921,26 +2750,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ページ番号は任意・最小値1で設計しましたが、この制約で合っていますか？
-エラーメッセージは「422 ValidationException」にて、「ページ番号は1以上で入力してください。」としましたがよろしいですか？</t>
-    <rPh sb="3" eb="5">
-      <t>バンゴウ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>サイセィオ</t>
-    </rPh>
-    <rPh sb="11" eb="12">
-      <t>🩸</t>
-    </rPh>
-    <rPh sb="81" eb="83">
-      <t>イジョウ</t>
-    </rPh>
-    <rPh sb="84" eb="86">
-      <t>ニュウリョク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>Q-333</t>
   </si>
   <si>
@@ -3058,52 +2867,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>画像URLは任意・最大255文字で設計しましたが、この制約で合っていますか？
-エラーメッセージは「422 ValidationException」にて、「画像URLは255文字以内で入力してください。」としましたがよろしいですか？</t>
-    <rPh sb="1" eb="3">
-      <t>ニn</t>
-    </rPh>
-    <rPh sb="3" eb="10">
-      <t>ヒッス</t>
-    </rPh>
-    <rPh sb="10" eb="11">
-      <t>ニn</t>
-    </rPh>
-    <rPh sb="11" eb="15">
-      <t>サイダイ</t>
-    </rPh>
-    <rPh sb="77" eb="79">
-      <t>ガゾウ</t>
-    </rPh>
-    <rPh sb="82" eb="84">
-      <t/>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>説明は任意・最大255文字で設計しましたが、この制約で合っていますか？
-エラーメッセージは「422 ValidationException」にて、「説明は255文字以内で入力してください。」としましたがよろしいですか？</t>
-    <rPh sb="3" eb="5">
-      <t>ニn</t>
-    </rPh>
-    <rPh sb="5" eb="12">
-      <t>ヒッス</t>
-    </rPh>
-    <rPh sb="12" eb="13">
-      <t>ニn</t>
-    </rPh>
-    <rPh sb="13" eb="17">
-      <t>サイダイ</t>
-    </rPh>
-    <rPh sb="74" eb="76">
-      <t>セツメイ</t>
-    </rPh>
-    <rPh sb="76" eb="78">
-      <t/>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>期日は必須・日付形式必須(YYYY-mm-dd)で設計しましたが、この制約で合っていますか？
 また、エラーメッセージは「期日は入力必須です。」「期日はYYYY-mm-ddで入力してください。」としましたがよろしいですか？</t>
     <rPh sb="0" eb="2">
@@ -3293,6 +3056,337 @@
   </si>
   <si>
     <t>ランキングはレビュー平均評価TOP10を表示し、レビューのない書籍は非表示とします。なお、ゲストユーザーも閲覧可能です。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>はい、BookPolicy により他ユーザーの書籍編集アクセスは 403 Forbidden を返してください。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>はい、ReviewPolicy により他ユーザーのレビュー編集アクセスは 403 Forbidden を返してください。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>はい、ReadingPlanPolicy により他ユーザーの計画編集アクセスは 403 Forbidden を返してください。（なお、完了済み completed 計画の編集も 403 となります）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>はい、403 Forbidden とともに { "error": "この操作を実行する権限がありません。" } のJSONを返してください。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>仕様上、同一ユーザーが同一書籍に対して複数回レビューを投稿することは可能です。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>同一ユーザー×同一書籍で in_progress 状態の計画が既に存在する場合は新規作成不可（バリデーションエラー「この書籍は既に進行中の読書計画が存在します。」）とし、completed 後の再計画は許可します。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>はい、公開APIとして認証認可なしで取得可能です。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AP01</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>API</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>APIのページネーションはデフォルト20件/ページで設計しましたが、この件数で問題ないですか？</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>書籍が見つからない場合は404とエラーJSONを返す設計にしましたが、レスポンス形式は「"error": "書籍情報が見つかりませんでした。"」でよろしいですか？</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>書籍詳細API</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>成功レスポンスにはID・タイトル・著者・ISBN・出版日・説明・ジャンルを含める設計にしましたが、他に必要な項目はありますか？</t>
+    <rPh sb="0" eb="2">
+      <t>セイコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>成功レスポンスにはID・タイトル・著者・ISBN・出版日・説明・ジャンル・レビューを含める設計にしましたが、他に必要な項目はありますか？</t>
+    <rPh sb="0" eb="2">
+      <t>セイコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>成功レスポンスにはID・タイトル・著者・ISBN・出版日・説明・ジャンル・平均評価・レビュー件数を含める設計にしましたが、他に必要な項目はありますか？</t>
+    <rPh sb="0" eb="2">
+      <t>セイコウ</t>
+    </rPh>
+    <rPh sb="25" eb="28">
+      <t>シュッパn</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>セツメイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>未認証時は401とエラーJSONを返す設計にしましたが、レスポンス形式は「"message": "Unauthenticated."」でよろしいですか？</t>
+    <rPh sb="0" eb="1">
+      <t>ミニンショウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>書籍更新の認可（ポリシー）は本人のみ操作可能としましたが、よろしいですか？</t>
+    <rPh sb="0" eb="4">
+      <t>ショセキ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>_x0000__x0000_</t>
+    </rPh>
+    <rPh sb="18" eb="22">
+      <t/>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>APIでの一覧取得のページネーションの最大表示数は100件としましたが、この制約で合っていますか？
+エラーメッセージは「422 Unprocessable Entity」にて、「ページネーションの最大表示件数は100件です。」としましたがよろしいですか？
+また、デフォルトのページネーションは何件としますか？</t>
+    <rPh sb="5" eb="7">
+      <t>イチラn</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>シュトク</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>キノウ</t>
+    </rPh>
+    <rPh sb="98" eb="104">
+      <t>サイダイ</t>
+    </rPh>
+    <rPh sb="108" eb="109">
+      <t>ケn</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>キーワードは任意・最大255文字で設計しましたが、この制約で合っていますか？
+エラーメッセージは「422 Unprocessable Entity」にて、「キーワードは255文字以内で入力してください。」としましたがよろしいですか？</t>
+    <rPh sb="6" eb="8">
+      <t>ニn</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>サイダイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ジャンルは任意・登録されたジャンルのみ検索可能で設計しましたが、この制約で合っていますか？
+エラーメッセージは「422 Unprocessable Entity」にて、「登録されたジャンルのみ検索可能です。」としましたがよろしいですか？</t>
+    <rPh sb="6" eb="8">
+      <t>ニn</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="19" eb="23">
+      <t>ケンサク</t>
+    </rPh>
+    <rPh sb="85" eb="87">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="96" eb="98">
+      <t>ケンサク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ページ番号は任意・最小値1で設計しましたが、この制約で合っていますか？
+エラーメッセージは「422 Unprocessable Entity」にて、「ページ番号は1以上で入力してください。」としましたがよろしいですか？</t>
+    <rPh sb="3" eb="5">
+      <t>バンゴウ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>サイセィオ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>🩸</t>
+    </rPh>
+    <rPh sb="82" eb="84">
+      <t>イジョウ</t>
+    </rPh>
+    <rPh sb="85" eb="87">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>タイトルは必須・最大255文字で設計しましたが、この制約で合っていますか？
+エラーメッセージは「422 Unprocessable Entity」にて、「タイトルは入力必須です。」「タイトルは255文字以内で入力してください。」としましたがよろしいですか？</t>
+    <rPh sb="5" eb="12">
+      <t>ヒッス</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ニn</t>
+    </rPh>
+    <rPh sb="13" eb="17">
+      <t>サイダイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>著者は必須・最大255文字で設計しましたが、この制約で合っていますか？
+エラーメッセージは「422 Unprocessable Entity」にて、「筆者は入力必須です。」「筆者は255文字以内で入力してください。」としましたがよろしいですか？</t>
+    <rPh sb="5" eb="12">
+      <t>ヒッス</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ニ_x0000_</t>
+    </rPh>
+    <rPh sb="13" eb="17">
+      <t>_x0005__x0007__x0003__x000C_</t>
+    </rPh>
+    <rPh sb="75" eb="77">
+      <t xml:space="preserve">_x0001__x0005__x000D__x0004_	</t>
+    </rPh>
+    <rPh sb="77" eb="78">
+      <t/>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ISBNは入力は必須ですか？
+エラーメッセージは「422 Unprocessable Entity」にて、「ISBNは入力必須です。」としましたがよろしいですか？</t>
+  </si>
+  <si>
+    <t>ISBNは13桁固定で一意性チェックも入れる想定ですが、桁数チェックは必要ですか？
+エラーメッセージは「422 Unprocessable Entity」にて、Q-65と同様のエラーメッセージでよろしいですか？</t>
+  </si>
+  <si>
+    <t>ISBNは13桁固定で一意性チェック(自信を除外)も入れる想定ですが、桁数チェックは必要ですか？
+エラーメッセージは「422 Unprocessable Entity」にて、Q-65と同様のエラーメッセージでよろしいですか？</t>
+    <rPh sb="19" eb="21">
+      <t>ジシn</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>説明は任意・最大255文字で設計しましたが、この制約で合っていますか？
+エラーメッセージは「422 Unprocessable Entity」にて、「説明は255文字以内で入力してください。」としましたがよろしいですか？</t>
+    <rPh sb="3" eb="5">
+      <t>ニn</t>
+    </rPh>
+    <rPh sb="5" eb="12">
+      <t>ヒッス</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ニn</t>
+    </rPh>
+    <rPh sb="13" eb="17">
+      <t>サイダイ</t>
+    </rPh>
+    <rPh sb="75" eb="77">
+      <t>セツメイ</t>
+    </rPh>
+    <rPh sb="77" eb="79">
+      <t/>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>画像URLは任意・最大255文字で設計しましたが、この制約で合っていますか？
+エラーメッセージは「422 Unprocessable Entity」にて、「画像URLは255文字以内で入力してください。」としましたがよろしいですか？</t>
+    <rPh sb="1" eb="3">
+      <t>ニn</t>
+    </rPh>
+    <rPh sb="3" eb="10">
+      <t>ヒッス</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ニn</t>
+    </rPh>
+    <rPh sb="11" eb="15">
+      <t>サイダイ</t>
+    </rPh>
+    <rPh sb="78" eb="80">
+      <t>ガゾウ</t>
+    </rPh>
+    <rPh sb="83" eb="85">
+      <t/>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ジャンルは任意・登録されたジャンルのみ選択可能で設計しましたが、この制約で合っていますか？
+エラーメッセージは「422 Unprocessable Entity」にて、「登録されたジャンルのみ選択可能です。」としましたがよろしいですか？</t>
+    <rPh sb="0" eb="6">
+      <t>ヒッス</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ニn</t>
+    </rPh>
+    <rPh sb="7" eb="11">
+      <t>サイダイ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>🧺</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>カノウ</t>
+    </rPh>
+    <rPh sb="85" eb="87">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>書籍削除の認可（ポリシー）は本人のみ操作可能としましたが、よろしいですか？</t>
+    <rPh sb="0" eb="2">
+      <t>ショセキ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>_x0000__x0000_</t>
+    </rPh>
+    <rPh sb="18" eb="22">
+      <t/>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>書籍削除API</t>
+  </si>
+  <si>
+    <t>成功レスポンスには204にて、ボディは返却しない設計にしましたが、よろしいですか？</t>
+    <rPh sb="0" eb="2">
+      <t>セイコウ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ヘンキャク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>他ユーザーの書籍の削除試行時は403 とエラーJSONを返す設計にしましたが、レスポンス形式は「"error": "この操作を実行する権限がありません。" 」でよろしいですか？</t>
+    <rPh sb="9" eb="11">
+      <t>サクジョ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>他ユーザーの書籍の更新試行時は403 とエラーJSONを返す設計にしましたが、レスポンス形式は「"error": "この操作を実行する権限がありません。" 」でよろしいですか？</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ジャンル名は必須・最大255文字・一意性チェックを入れる想定ですが、この制約で合っていますか？
+また、エラーメッセージは「ジャンル名は入力必須です。」「ジャンル名は255文字以内で入力してください。」「既に使用されているジャンル名です。」としましたがよろしいですか？</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -3455,14 +3549,35 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="4">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -3820,7 +3935,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{833B9C12-88F9-F440-902B-BDAD178A24F6}">
-  <dimension ref="A1:H342"/>
+  <dimension ref="A2:H342"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
     <col min="2" max="2" width="28.85546875" customWidth="1"/>
@@ -3829,9 +3944,6 @@
     <col min="5" max="6" width="60.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
-      <c r="H1" s="13"/>
-    </row>
     <row r="2" spans="1:8">
       <c r="A2" s="1" t="s">
         <v>14</v>
@@ -3855,7 +3967,7 @@
         <v>2</v>
       </c>
       <c r="H2" s="12" t="s">
-        <v>596</v>
+        <v>577</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42">
@@ -3878,10 +3990,10 @@
         <v>484</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="H3" s="11" t="s">
-        <v>561</v>
+        <v>542</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="42">
@@ -3904,10 +4016,10 @@
         <v>485</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>561</v>
+        <v>542</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="42">
@@ -3930,10 +4042,10 @@
         <v>486</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>561</v>
+        <v>542</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="42">
@@ -3956,10 +4068,10 @@
         <v>487</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>561</v>
+        <v>542</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="63">
@@ -3982,10 +4094,10 @@
         <v>488</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>561</v>
+        <v>542</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="63">
@@ -4008,10 +4120,10 @@
         <v>489</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="H8" s="11" t="s">
-        <v>561</v>
+        <v>542</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="63">
@@ -4031,13 +4143,13 @@
         <v>11</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>562</v>
+        <v>543</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="H9" s="11" t="s">
-        <v>561</v>
+        <v>542</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="42">
@@ -4057,13 +4169,13 @@
         <v>184</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>563</v>
+        <v>544</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>561</v>
+        <v>542</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="63">
@@ -4083,13 +4195,13 @@
         <v>183</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>564</v>
+        <v>545</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="H11" s="11" t="s">
-        <v>561</v>
+        <v>542</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="42">
@@ -4109,13 +4221,13 @@
         <v>18</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>565</v>
+        <v>546</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="H12" s="11" t="s">
-        <v>561</v>
+        <v>542</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="63">
@@ -4135,13 +4247,13 @@
         <v>21</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>566</v>
+        <v>547</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="H13" s="11" t="s">
-        <v>561</v>
+        <v>542</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="42">
@@ -4161,13 +4273,13 @@
         <v>19</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>567</v>
+        <v>548</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>561</v>
+        <v>542</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="63">
@@ -4187,13 +4299,13 @@
         <v>121</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>568</v>
+        <v>549</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="H15" s="11" t="s">
-        <v>561</v>
+        <v>542</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="42">
@@ -4216,10 +4328,10 @@
         <v>491</v>
       </c>
       <c r="G16" s="9" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="H16" s="11" t="s">
-        <v>561</v>
+        <v>542</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="42">
@@ -4242,10 +4354,10 @@
         <v>492</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="H17" s="11" t="s">
-        <v>561</v>
+        <v>542</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="63">
@@ -4268,10 +4380,10 @@
         <v>493</v>
       </c>
       <c r="G18" s="9" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="H18" s="11" t="s">
-        <v>561</v>
+        <v>542</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="63">
@@ -4291,13 +4403,13 @@
         <v>128</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>569</v>
+        <v>550</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="H19" s="11" t="s">
-        <v>561</v>
+        <v>542</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="42">
@@ -4320,10 +4432,10 @@
         <v>490</v>
       </c>
       <c r="G20" s="9" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="H20" s="11" t="s">
-        <v>561</v>
+        <v>542</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="63">
@@ -4343,13 +4455,13 @@
         <v>181</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>570</v>
+        <v>551</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="H21" s="11" t="s">
-        <v>561</v>
+        <v>542</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="42">
@@ -4372,10 +4484,10 @@
         <v>491</v>
       </c>
       <c r="G22" s="9" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="H22" s="11" t="s">
-        <v>561</v>
+        <v>542</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="63">
@@ -4395,13 +4507,13 @@
         <v>182</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>571</v>
+        <v>552</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="H23" s="11" t="s">
-        <v>561</v>
+        <v>542</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="42">
@@ -4421,13 +4533,13 @@
         <v>134</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>572</v>
+        <v>553</v>
       </c>
       <c r="G24" s="9" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="H24" s="11" t="s">
-        <v>561</v>
+        <v>542</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="63">
@@ -4447,13 +4559,13 @@
         <v>135</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>573</v>
+        <v>554</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="H25" s="11" t="s">
-        <v>561</v>
+        <v>542</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="63">
@@ -4473,13 +4585,13 @@
         <v>136</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>574</v>
+        <v>555</v>
       </c>
       <c r="G26" s="9" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="H26" s="11" t="s">
-        <v>561</v>
+        <v>542</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="42">
@@ -4502,10 +4614,10 @@
         <v>494</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="H27" s="11" t="s">
-        <v>561</v>
+        <v>542</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="63">
@@ -4525,13 +4637,13 @@
         <v>139</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>575</v>
+        <v>556</v>
       </c>
       <c r="G28" s="9" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="H28" s="11" t="s">
-        <v>561</v>
+        <v>542</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="63">
@@ -4548,16 +4660,16 @@
         <v>140</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>560</v>
+        <v>541</v>
       </c>
       <c r="F29" s="4" t="s">
         <v>495</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="H29" s="11" t="s">
-        <v>561</v>
+        <v>542</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="42">
@@ -4580,10 +4692,10 @@
         <v>491</v>
       </c>
       <c r="G30" s="9" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="H30" s="11" t="s">
-        <v>561</v>
+        <v>542</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="63">
@@ -4603,13 +4715,13 @@
         <v>142</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>576</v>
+        <v>557</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="H31" s="11" t="s">
-        <v>561</v>
+        <v>542</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="63">
@@ -4632,10 +4744,10 @@
         <v>495</v>
       </c>
       <c r="G32" s="9" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="H32" s="11" t="s">
-        <v>561</v>
+        <v>542</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="63">
@@ -4655,13 +4767,13 @@
         <v>145</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>577</v>
+        <v>558</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="H33" s="11" t="s">
-        <v>561</v>
+        <v>542</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="42">
@@ -4681,13 +4793,13 @@
         <v>164</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>578</v>
+        <v>559</v>
       </c>
       <c r="G34" s="9" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="H34" s="11" t="s">
-        <v>561</v>
+        <v>542</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="84">
@@ -4710,10 +4822,10 @@
         <v>496</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="H35" s="11" t="s">
-        <v>561</v>
+        <v>542</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="63">
@@ -4733,13 +4845,13 @@
         <v>170</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>580</v>
+        <v>561</v>
       </c>
       <c r="G36" s="9" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="H36" s="11" t="s">
-        <v>561</v>
+        <v>542</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="63">
@@ -4762,10 +4874,10 @@
         <v>497</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="H37" s="11" t="s">
-        <v>561</v>
+        <v>542</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="63">
@@ -4785,13 +4897,13 @@
         <v>172</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>581</v>
+        <v>562</v>
       </c>
       <c r="G38" s="9" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="H38" s="11" t="s">
-        <v>561</v>
+        <v>542</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="63">
@@ -4811,13 +4923,13 @@
         <v>173</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>582</v>
+        <v>563</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="H39" s="11" t="s">
-        <v>561</v>
+        <v>542</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="63">
@@ -4837,13 +4949,13 @@
         <v>174</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>583</v>
+        <v>564</v>
       </c>
       <c r="G40" s="9" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="H40" s="11" t="s">
-        <v>561</v>
+        <v>542</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="63">
@@ -4863,13 +4975,13 @@
         <v>175</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>584</v>
+        <v>565</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="H41" s="11" t="s">
-        <v>561</v>
+        <v>542</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="63">
@@ -4889,13 +5001,13 @@
         <v>177</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>585</v>
+        <v>566</v>
       </c>
       <c r="G42" s="9" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="H42" s="11" t="s">
-        <v>561</v>
+        <v>542</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="63">
@@ -4915,13 +5027,13 @@
         <v>178</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>586</v>
+        <v>567</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="H43" s="11" t="s">
-        <v>561</v>
+        <v>542</v>
       </c>
     </row>
     <row r="44" spans="1:8" ht="63">
@@ -4941,13 +5053,13 @@
         <v>179</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>587</v>
+        <v>568</v>
       </c>
       <c r="G44" s="9" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="H44" s="11" t="s">
-        <v>561</v>
+        <v>542</v>
       </c>
     </row>
     <row r="45" spans="1:8" ht="42">
@@ -4967,13 +5079,13 @@
         <v>222</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>588</v>
+        <v>569</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="H45" s="11" t="s">
-        <v>561</v>
+        <v>542</v>
       </c>
     </row>
     <row r="46" spans="1:8" ht="63">
@@ -4993,13 +5105,13 @@
         <v>180</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>589</v>
+        <v>570</v>
       </c>
       <c r="G46" s="9" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="H46" s="11" t="s">
-        <v>561</v>
+        <v>542</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="63">
@@ -5019,13 +5131,13 @@
         <v>185</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>590</v>
+        <v>571</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="H47" s="11" t="s">
-        <v>561</v>
+        <v>542</v>
       </c>
     </row>
     <row r="48" spans="1:8" ht="63">
@@ -5045,13 +5157,13 @@
         <v>186</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>591</v>
+        <v>572</v>
       </c>
       <c r="G48" s="9" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="H48" s="11" t="s">
-        <v>561</v>
+        <v>542</v>
       </c>
     </row>
     <row r="49" spans="1:8" ht="63">
@@ -5071,13 +5183,13 @@
         <v>187</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>592</v>
+        <v>573</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="H49" s="11" t="s">
-        <v>561</v>
+        <v>542</v>
       </c>
     </row>
     <row r="50" spans="1:8" ht="63">
@@ -5097,13 +5209,13 @@
         <v>188</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>593</v>
+        <v>574</v>
       </c>
       <c r="G50" s="9" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="H50" s="11" t="s">
-        <v>561</v>
+        <v>542</v>
       </c>
     </row>
     <row r="51" spans="1:8" ht="63">
@@ -5123,13 +5235,13 @@
         <v>189</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>594</v>
+        <v>575</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="H51" s="11" t="s">
-        <v>561</v>
+        <v>542</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="63">
@@ -5149,13 +5261,13 @@
         <v>190</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>595</v>
+        <v>576</v>
       </c>
       <c r="G52" s="9" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="H52" s="11" t="s">
-        <v>561</v>
+        <v>542</v>
       </c>
     </row>
     <row r="53" spans="1:8" ht="63">
@@ -5178,10 +5290,10 @@
         <v>495</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="H53" s="11" t="s">
-        <v>561</v>
+        <v>542</v>
       </c>
     </row>
     <row r="54" spans="1:8" ht="63">
@@ -5204,10 +5316,10 @@
         <v>495</v>
       </c>
       <c r="G54" s="9" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="H54" s="11" t="s">
-        <v>561</v>
+        <v>542</v>
       </c>
     </row>
     <row r="55" spans="1:8" ht="42">
@@ -5227,13 +5339,13 @@
         <v>195</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>597</v>
+        <v>578</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="H55" s="11" t="s">
-        <v>561</v>
+        <v>542</v>
       </c>
     </row>
     <row r="56" spans="1:8" ht="42">
@@ -5256,10 +5368,10 @@
         <v>498</v>
       </c>
       <c r="G56" s="9" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="H56" s="11" t="s">
-        <v>561</v>
+        <v>542</v>
       </c>
     </row>
     <row r="57" spans="1:8" ht="63">
@@ -5279,13 +5391,13 @@
         <v>197</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>598</v>
+        <v>579</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="H57" s="10" t="s">
-        <v>561</v>
+        <v>542</v>
       </c>
     </row>
     <row r="58" spans="1:8" ht="63">
@@ -5305,13 +5417,13 @@
         <v>201</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>579</v>
+        <v>560</v>
       </c>
       <c r="G58" s="9" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="H58" s="10" t="s">
-        <v>561</v>
+        <v>542</v>
       </c>
     </row>
     <row r="59" spans="1:8" ht="63">
@@ -5334,7 +5446,10 @@
         <v>499</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>510</v>
+        <v>504</v>
+      </c>
+      <c r="H59" s="11" t="s">
+        <v>542</v>
       </c>
     </row>
     <row r="60" spans="1:8" ht="21">
@@ -5354,10 +5469,13 @@
         <v>208</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>500</v>
+        <v>586</v>
       </c>
       <c r="G60" s="9" t="s">
-        <v>510</v>
+        <v>504</v>
+      </c>
+      <c r="H60" s="11" t="s">
+        <v>542</v>
       </c>
     </row>
     <row r="61" spans="1:8" ht="21">
@@ -5380,7 +5498,7 @@
         <v>500</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
     </row>
     <row r="62" spans="1:8" ht="42">
@@ -5400,10 +5518,13 @@
         <v>214</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>501</v>
+        <v>580</v>
       </c>
       <c r="G62" s="9" t="s">
-        <v>510</v>
+        <v>504</v>
+      </c>
+      <c r="H62" s="13" t="s">
+        <v>542</v>
       </c>
     </row>
     <row r="63" spans="1:8" ht="42">
@@ -5423,10 +5544,13 @@
         <v>213</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>502</v>
+        <v>581</v>
       </c>
       <c r="G63" s="9" t="s">
-        <v>510</v>
+        <v>504</v>
+      </c>
+      <c r="H63" s="13" t="s">
+        <v>542</v>
       </c>
     </row>
     <row r="64" spans="1:8" ht="84">
@@ -5446,12 +5570,14 @@
         <v>219</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>503</v>
+        <v>583</v>
       </c>
       <c r="G64" s="9" t="s">
-        <v>510</v>
-      </c>
-      <c r="H64" s="10"/>
+        <v>504</v>
+      </c>
+      <c r="H64" s="11" t="s">
+        <v>542</v>
+      </c>
     </row>
     <row r="65" spans="1:8" ht="84">
       <c r="A65" s="3" t="s">
@@ -5470,12 +5596,14 @@
         <v>220</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>503</v>
+        <v>583</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>510</v>
-      </c>
-      <c r="H65" s="10"/>
+        <v>504</v>
+      </c>
+      <c r="H65" s="11" t="s">
+        <v>542</v>
+      </c>
     </row>
     <row r="66" spans="1:8" ht="63">
       <c r="A66" s="3" t="s">
@@ -5494,16 +5622,18 @@
         <v>221</v>
       </c>
       <c r="F66" s="4" t="s">
+        <v>582</v>
+      </c>
+      <c r="G66" s="9" t="s">
         <v>504</v>
       </c>
-      <c r="G66" s="9" t="s">
-        <v>510</v>
-      </c>
-      <c r="H66" s="10"/>
+      <c r="H66" s="11" t="s">
+        <v>542</v>
+      </c>
     </row>
     <row r="67" spans="1:8" ht="63">
       <c r="A67" s="3" t="s">
-        <v>513</v>
+        <v>507</v>
       </c>
       <c r="B67" s="4" t="s">
         <v>223</v>
@@ -5518,10 +5648,10 @@
         <v>226</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="H67" s="10"/>
     </row>
@@ -5542,10 +5672,10 @@
         <v>227</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="G68" s="9" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="H68" s="10"/>
     </row>
@@ -5566,12 +5696,14 @@
         <v>230</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>507</v>
+        <v>584</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>510</v>
-      </c>
-      <c r="H69" s="10"/>
+        <v>504</v>
+      </c>
+      <c r="H69" s="10" t="s">
+        <v>542</v>
+      </c>
     </row>
     <row r="70" spans="1:8" ht="42">
       <c r="A70" s="3" t="s">
@@ -5590,12 +5722,14 @@
         <v>233</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>508</v>
+        <v>503</v>
       </c>
       <c r="G70" s="9" t="s">
-        <v>510</v>
-      </c>
-      <c r="H70" s="10"/>
+        <v>504</v>
+      </c>
+      <c r="H70" s="10" t="s">
+        <v>542</v>
+      </c>
     </row>
     <row r="71" spans="1:8" ht="63">
       <c r="A71" s="3" t="s">
@@ -5614,19 +5748,21 @@
         <v>234</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>509</v>
+        <v>585</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>510</v>
-      </c>
-      <c r="H71" s="10"/>
+        <v>504</v>
+      </c>
+      <c r="H71" s="10" t="s">
+        <v>542</v>
+      </c>
     </row>
     <row r="72" spans="1:8" ht="84">
       <c r="A72" s="3" t="s">
         <v>89</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="C72" s="4" t="s">
         <v>237</v>
@@ -5635,7 +5771,7 @@
         <v>163</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>512</v>
+        <v>506</v>
       </c>
       <c r="F72" s="4"/>
       <c r="G72" s="3" t="s">
@@ -5647,7 +5783,7 @@
         <v>90</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="C73" s="4" t="s">
         <v>237</v>
@@ -5656,7 +5792,7 @@
         <v>163</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>533</v>
+        <v>517</v>
       </c>
       <c r="F73" s="4"/>
       <c r="G73" s="3" t="s">
@@ -5689,7 +5825,7 @@
         <v>92</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="C75" s="4" t="s">
         <v>237</v>
@@ -5698,7 +5834,7 @@
         <v>163</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>534</v>
+        <v>518</v>
       </c>
       <c r="F75" s="4"/>
       <c r="G75" s="3" t="s">
@@ -5710,7 +5846,7 @@
         <v>93</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="C76" s="4" t="s">
         <v>477</v>
@@ -5719,7 +5855,7 @@
         <v>476</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>535</v>
+        <v>519</v>
       </c>
       <c r="F76" s="4"/>
       <c r="G76" s="3" t="s">
@@ -5731,7 +5867,7 @@
         <v>94</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="C77" s="4" t="s">
         <v>477</v>
@@ -5740,7 +5876,7 @@
         <v>476</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>536</v>
+        <v>520</v>
       </c>
       <c r="F77" s="4"/>
       <c r="G77" s="3" t="s">
@@ -5752,7 +5888,7 @@
         <v>95</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="C78" s="4" t="s">
         <v>475</v>
@@ -5761,7 +5897,7 @@
         <v>474</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>522</v>
+        <v>513</v>
       </c>
       <c r="F78" s="4"/>
       <c r="G78" s="3" t="s">
@@ -5773,7 +5909,7 @@
         <v>96</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="C79" s="4" t="s">
         <v>475</v>
@@ -5782,7 +5918,7 @@
         <v>474</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>521</v>
+        <v>512</v>
       </c>
       <c r="F79" s="4"/>
       <c r="G79" s="3" t="s">
@@ -5794,7 +5930,7 @@
         <v>97</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="C80" s="4" t="s">
         <v>475</v>
@@ -5803,7 +5939,7 @@
         <v>474</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>529</v>
+        <v>515</v>
       </c>
       <c r="F80" s="4"/>
       <c r="G80" s="3" t="s">
@@ -5815,7 +5951,7 @@
         <v>98</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="C81" s="4" t="s">
         <v>150</v>
@@ -5827,10 +5963,10 @@
         <v>226</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="G81" s="9" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
     </row>
     <row r="82" spans="1:7" ht="63">
@@ -5838,7 +5974,7 @@
         <v>99</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="C82" s="4" t="s">
         <v>151</v>
@@ -5847,7 +5983,7 @@
         <v>20</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>515</v>
+        <v>509</v>
       </c>
       <c r="F82" s="4"/>
       <c r="G82" s="3" t="s">
@@ -5859,7 +5995,7 @@
         <v>100</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="C83" s="4" t="s">
         <v>475</v>
@@ -5868,7 +6004,7 @@
         <v>474</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>537</v>
+        <v>521</v>
       </c>
       <c r="F83" s="4"/>
       <c r="G83" s="3" t="s">
@@ -5880,7 +6016,7 @@
         <v>101</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="C84" s="4" t="s">
         <v>475</v>
@@ -5889,7 +6025,7 @@
         <v>474</v>
       </c>
       <c r="E84" s="4" t="s">
-        <v>519</v>
+        <v>511</v>
       </c>
       <c r="F84" s="4"/>
       <c r="G84" s="3" t="s">
@@ -5901,7 +6037,7 @@
         <v>102</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="C85" s="4" t="s">
         <v>475</v>
@@ -5910,7 +6046,7 @@
         <v>474</v>
       </c>
       <c r="E85" s="4" t="s">
-        <v>518</v>
+        <v>510</v>
       </c>
       <c r="F85" s="4"/>
       <c r="G85" s="3" t="s">
@@ -5922,7 +6058,7 @@
         <v>103</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="C86" s="4" t="s">
         <v>475</v>
@@ -5931,7 +6067,7 @@
         <v>474</v>
       </c>
       <c r="E86" s="4" t="s">
-        <v>532</v>
+        <v>516</v>
       </c>
       <c r="F86" s="4"/>
       <c r="G86" s="3" t="s">
@@ -5943,7 +6079,7 @@
         <v>104</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="C87" s="4" t="s">
         <v>156</v>
@@ -5952,7 +6088,7 @@
         <v>129</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>520</v>
+        <v>614</v>
       </c>
       <c r="F87" s="4"/>
       <c r="G87" s="3" t="s">
@@ -5964,7 +6100,7 @@
         <v>105</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="C88" s="4" t="s">
         <v>157</v>
@@ -5973,7 +6109,7 @@
         <v>131</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>523</v>
+        <v>514</v>
       </c>
       <c r="F88" s="4"/>
       <c r="G88" s="3" t="s">
@@ -6006,7 +6142,7 @@
         <v>107</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="C90" s="4" t="s">
         <v>159</v>
@@ -6015,7 +6151,7 @@
         <v>137</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>538</v>
+        <v>522</v>
       </c>
       <c r="F90" s="4"/>
       <c r="G90" s="3" t="s">
@@ -6027,16 +6163,16 @@
         <v>108</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>539</v>
+        <v>523</v>
       </c>
       <c r="D91" s="4" t="s">
+        <v>524</v>
+      </c>
+      <c r="E91" s="4" t="s">
         <v>540</v>
-      </c>
-      <c r="E91" s="4" t="s">
-        <v>559</v>
       </c>
       <c r="F91" s="4"/>
       <c r="G91" s="3" t="s">
@@ -6069,7 +6205,7 @@
         <v>110</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="C93" s="4" t="s">
         <v>205</v>
@@ -6078,7 +6214,7 @@
         <v>239</v>
       </c>
       <c r="E93" s="4" t="s">
-        <v>524</v>
+        <v>597</v>
       </c>
       <c r="F93" s="4"/>
       <c r="G93" s="3" t="s">
@@ -6090,7 +6226,7 @@
         <v>111</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="C94" s="4" t="s">
         <v>205</v>
@@ -6099,7 +6235,7 @@
         <v>239</v>
       </c>
       <c r="E94" s="4" t="s">
-        <v>525</v>
+        <v>598</v>
       </c>
       <c r="F94" s="4"/>
       <c r="G94" s="3" t="s">
@@ -6111,7 +6247,7 @@
         <v>112</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="C95" s="4" t="s">
         <v>205</v>
@@ -6120,7 +6256,7 @@
         <v>239</v>
       </c>
       <c r="E95" s="4" t="s">
-        <v>530</v>
+        <v>599</v>
       </c>
       <c r="F95" s="4"/>
       <c r="G95" s="3" t="s">
@@ -6132,7 +6268,7 @@
         <v>113</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="C96" s="4" t="s">
         <v>205</v>
@@ -6141,7 +6277,7 @@
         <v>239</v>
       </c>
       <c r="E96" s="4" t="s">
-        <v>541</v>
+        <v>600</v>
       </c>
       <c r="F96" s="4"/>
       <c r="G96" s="3" t="s">
@@ -6153,7 +6289,7 @@
         <v>114</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="C97" s="4" t="s">
         <v>481</v>
@@ -6162,7 +6298,7 @@
         <v>482</v>
       </c>
       <c r="E97" s="4" t="s">
-        <v>526</v>
+        <v>601</v>
       </c>
       <c r="F97" s="4"/>
       <c r="G97" s="3" t="s">
@@ -6174,7 +6310,7 @@
         <v>115</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="C98" s="4" t="s">
         <v>481</v>
@@ -6183,7 +6319,7 @@
         <v>482</v>
       </c>
       <c r="E98" s="4" t="s">
-        <v>528</v>
+        <v>602</v>
       </c>
       <c r="F98" s="4"/>
       <c r="G98" s="3" t="s">
@@ -6195,7 +6331,7 @@
         <v>116</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="C99" s="4" t="s">
         <v>481</v>
@@ -6204,7 +6340,7 @@
         <v>482</v>
       </c>
       <c r="E99" s="4" t="s">
-        <v>527</v>
+        <v>603</v>
       </c>
       <c r="F99" s="4"/>
       <c r="G99" s="3" t="s">
@@ -6216,7 +6352,7 @@
         <v>117</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="C100" s="4" t="s">
         <v>479</v>
@@ -6225,7 +6361,7 @@
         <v>480</v>
       </c>
       <c r="E100" s="4" t="s">
-        <v>516</v>
+        <v>604</v>
       </c>
       <c r="F100" s="4"/>
       <c r="G100" s="3" t="s">
@@ -6237,7 +6373,7 @@
         <v>118</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="C101" s="4" t="s">
         <v>483</v>
@@ -6246,7 +6382,7 @@
         <v>215</v>
       </c>
       <c r="E101" s="4" t="s">
-        <v>517</v>
+        <v>605</v>
       </c>
       <c r="F101" s="4"/>
       <c r="G101" s="3" t="s">
@@ -6258,7 +6394,7 @@
         <v>119</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="C102" s="4" t="s">
         <v>481</v>
@@ -6267,7 +6403,7 @@
         <v>482</v>
       </c>
       <c r="E102" s="4" t="s">
-        <v>537</v>
+        <v>521</v>
       </c>
       <c r="F102" s="4"/>
       <c r="G102" s="3" t="s">
@@ -6279,7 +6415,7 @@
         <v>241</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="C103" s="4" t="s">
         <v>481</v>
@@ -6288,7 +6424,7 @@
         <v>482</v>
       </c>
       <c r="E103" s="4" t="s">
-        <v>558</v>
+        <v>606</v>
       </c>
       <c r="F103" s="4"/>
       <c r="G103" s="3" t="s">
@@ -6300,7 +6436,7 @@
         <v>242</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="C104" s="4" t="s">
         <v>481</v>
@@ -6309,7 +6445,7 @@
         <v>482</v>
       </c>
       <c r="E104" s="4" t="s">
-        <v>557</v>
+        <v>607</v>
       </c>
       <c r="F104" s="4"/>
       <c r="G104" s="3" t="s">
@@ -6321,7 +6457,7 @@
         <v>243</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="C105" s="4" t="s">
         <v>481</v>
@@ -6330,7 +6466,7 @@
         <v>482</v>
       </c>
       <c r="E105" s="4" t="s">
-        <v>531</v>
+        <v>608</v>
       </c>
       <c r="F105" s="4"/>
       <c r="G105" s="3" t="s">
@@ -6342,16 +6478,16 @@
         <v>244</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="C106" s="4" t="s">
         <v>146</v>
       </c>
       <c r="D106" s="4" t="s">
-        <v>550</v>
+        <v>533</v>
       </c>
       <c r="E106" s="4" t="s">
-        <v>551</v>
+        <v>534</v>
       </c>
       <c r="F106" s="4"/>
       <c r="G106" s="3" t="s">
@@ -6363,16 +6499,16 @@
         <v>245</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="C107" s="4" t="s">
         <v>146</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>550</v>
+        <v>533</v>
       </c>
       <c r="E107" s="4" t="s">
-        <v>552</v>
+        <v>535</v>
       </c>
       <c r="F107" s="4"/>
       <c r="G107" s="3" t="s">
@@ -6384,16 +6520,16 @@
         <v>246</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="C108" s="4" t="s">
         <v>147</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>553</v>
+        <v>536</v>
       </c>
       <c r="E108" s="4" t="s">
-        <v>554</v>
+        <v>537</v>
       </c>
       <c r="F108" s="4"/>
       <c r="G108" s="3" t="s">
@@ -6405,16 +6541,16 @@
         <v>247</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="C109" s="4" t="s">
         <v>147</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>553</v>
+        <v>536</v>
       </c>
       <c r="E109" s="4" t="s">
-        <v>555</v>
+        <v>538</v>
       </c>
       <c r="F109" s="4"/>
       <c r="G109" s="3" t="s">
@@ -6426,197 +6562,357 @@
         <v>248</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="C110" s="4" t="s">
         <v>147</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>553</v>
+        <v>536</v>
       </c>
       <c r="E110" s="4" t="s">
-        <v>556</v>
+        <v>539</v>
       </c>
       <c r="F110" s="4"/>
       <c r="G110" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="111" spans="1:7">
+    <row r="111" spans="1:7" ht="42">
       <c r="A111" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="B111" s="4"/>
-      <c r="C111" s="4"/>
-      <c r="D111" s="4"/>
-      <c r="E111" s="4"/>
+      <c r="B111" s="4" t="s">
+        <v>588</v>
+      </c>
+      <c r="C111" s="4" t="s">
+        <v>587</v>
+      </c>
+      <c r="D111" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="E111" s="4" t="s">
+        <v>589</v>
+      </c>
       <c r="F111" s="4"/>
-      <c r="G111" s="3"/>
-    </row>
-    <row r="112" spans="1:7">
+      <c r="G111" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" ht="63">
       <c r="A112" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="B112" s="4"/>
-      <c r="C112" s="4"/>
-      <c r="D112" s="4"/>
-      <c r="E112" s="4"/>
+      <c r="B112" s="4" t="s">
+        <v>588</v>
+      </c>
+      <c r="C112" s="4" t="s">
+        <v>587</v>
+      </c>
+      <c r="D112" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="E112" s="4" t="s">
+        <v>594</v>
+      </c>
       <c r="F112" s="4"/>
-      <c r="G112" s="3"/>
-    </row>
-    <row r="113" spans="1:7">
+      <c r="G112" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" ht="63">
       <c r="A113" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="B113" s="4"/>
-      <c r="C113" s="4"/>
-      <c r="D113" s="4"/>
-      <c r="E113" s="4"/>
+      <c r="B113" s="4" t="s">
+        <v>588</v>
+      </c>
+      <c r="C113" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="D113" s="4" t="s">
+        <v>591</v>
+      </c>
+      <c r="E113" s="4" t="s">
+        <v>590</v>
+      </c>
       <c r="F113" s="4"/>
-      <c r="G113" s="3"/>
-    </row>
-    <row r="114" spans="1:7">
+      <c r="G113" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" ht="42">
       <c r="A114" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="B114" s="4"/>
-      <c r="C114" s="4"/>
-      <c r="D114" s="4"/>
-      <c r="E114" s="4"/>
+      <c r="B114" s="4" t="s">
+        <v>588</v>
+      </c>
+      <c r="C114" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="D114" s="4" t="s">
+        <v>591</v>
+      </c>
+      <c r="E114" s="4" t="s">
+        <v>593</v>
+      </c>
       <c r="F114" s="4"/>
-      <c r="G114" s="3"/>
-    </row>
-    <row r="115" spans="1:7">
+      <c r="G114" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" ht="42">
       <c r="A115" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="B115" s="4"/>
-      <c r="C115" s="4"/>
-      <c r="D115" s="4"/>
-      <c r="E115" s="4"/>
+      <c r="B115" s="4" t="s">
+        <v>588</v>
+      </c>
+      <c r="C115" s="4" t="s">
+        <v>479</v>
+      </c>
+      <c r="D115" s="4" t="s">
+        <v>480</v>
+      </c>
+      <c r="E115" s="4" t="s">
+        <v>592</v>
+      </c>
       <c r="F115" s="4"/>
-      <c r="G115" s="3"/>
-    </row>
-    <row r="116" spans="1:7">
+      <c r="G115" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" ht="42">
       <c r="A116" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="B116" s="4"/>
-      <c r="C116" s="4"/>
-      <c r="D116" s="4"/>
-      <c r="E116" s="4"/>
+      <c r="B116" s="4" t="s">
+        <v>588</v>
+      </c>
+      <c r="C116" s="4" t="s">
+        <v>479</v>
+      </c>
+      <c r="D116" s="4" t="s">
+        <v>480</v>
+      </c>
+      <c r="E116" s="4" t="s">
+        <v>595</v>
+      </c>
       <c r="F116" s="4"/>
-      <c r="G116" s="3"/>
-    </row>
-    <row r="117" spans="1:7">
+      <c r="G116" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" ht="42">
       <c r="A117" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="B117" s="4"/>
-      <c r="C117" s="4"/>
-      <c r="D117" s="4"/>
-      <c r="E117" s="4"/>
+      <c r="B117" s="4" t="s">
+        <v>588</v>
+      </c>
+      <c r="C117" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="D117" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="E117" s="4" t="s">
+        <v>596</v>
+      </c>
       <c r="F117" s="4"/>
-      <c r="G117" s="3"/>
-    </row>
-    <row r="118" spans="1:7">
+      <c r="G117" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" ht="42">
       <c r="A118" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="B118" s="4"/>
-      <c r="C118" s="4"/>
-      <c r="D118" s="4"/>
-      <c r="E118" s="4"/>
+      <c r="B118" s="4" t="s">
+        <v>588</v>
+      </c>
+      <c r="C118" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="D118" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="E118" s="4" t="s">
+        <v>592</v>
+      </c>
       <c r="F118" s="4"/>
-      <c r="G118" s="3"/>
-    </row>
-    <row r="119" spans="1:7">
+      <c r="G118" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" ht="63">
       <c r="A119" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="B119" s="4"/>
-      <c r="C119" s="4"/>
-      <c r="D119" s="4"/>
-      <c r="E119" s="4"/>
+      <c r="B119" s="4" t="s">
+        <v>588</v>
+      </c>
+      <c r="C119" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="D119" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="E119" s="4" t="s">
+        <v>590</v>
+      </c>
       <c r="F119" s="4"/>
-      <c r="G119" s="3"/>
-    </row>
-    <row r="120" spans="1:7">
+      <c r="G119" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" ht="42">
       <c r="A120" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="B120" s="4"/>
-      <c r="C120" s="4"/>
-      <c r="D120" s="4"/>
-      <c r="E120" s="4"/>
+      <c r="B120" s="4" t="s">
+        <v>588</v>
+      </c>
+      <c r="C120" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="D120" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="E120" s="4" t="s">
+        <v>595</v>
+      </c>
       <c r="F120" s="4"/>
-      <c r="G120" s="3"/>
-    </row>
-    <row r="121" spans="1:7">
+      <c r="G120" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" ht="63">
       <c r="A121" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="B121" s="4"/>
-      <c r="C121" s="4"/>
-      <c r="D121" s="4"/>
-      <c r="E121" s="4"/>
+      <c r="B121" s="4" t="s">
+        <v>588</v>
+      </c>
+      <c r="C121" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="D121" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="E121" s="4" t="s">
+        <v>613</v>
+      </c>
       <c r="F121" s="4"/>
-      <c r="G121" s="3"/>
-    </row>
-    <row r="122" spans="1:7">
+      <c r="G121" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" ht="42">
       <c r="A122" s="3" t="s">
         <v>260</v>
       </c>
-      <c r="B122" s="4"/>
-      <c r="C122" s="4"/>
-      <c r="D122" s="4"/>
-      <c r="E122" s="4"/>
+      <c r="B122" s="4" t="s">
+        <v>588</v>
+      </c>
+      <c r="C122" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="D122" s="4" t="s">
+        <v>610</v>
+      </c>
+      <c r="E122" s="4" t="s">
+        <v>609</v>
+      </c>
       <c r="F122" s="4"/>
-      <c r="G122" s="3"/>
-    </row>
-    <row r="123" spans="1:7">
+      <c r="G122" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" ht="42">
       <c r="A123" s="3" t="s">
         <v>261</v>
       </c>
-      <c r="B123" s="4"/>
-      <c r="C123" s="4"/>
-      <c r="D123" s="4"/>
-      <c r="E123" s="4"/>
+      <c r="B123" s="4" t="s">
+        <v>588</v>
+      </c>
+      <c r="C123" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="D123" s="4" t="s">
+        <v>610</v>
+      </c>
+      <c r="E123" s="4" t="s">
+        <v>611</v>
+      </c>
       <c r="F123" s="4"/>
-      <c r="G123" s="3"/>
-    </row>
-    <row r="124" spans="1:7">
+      <c r="G123" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" ht="63">
       <c r="A124" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="B124" s="4"/>
-      <c r="C124" s="4"/>
-      <c r="D124" s="4"/>
-      <c r="E124" s="4"/>
+      <c r="B124" s="4" t="s">
+        <v>588</v>
+      </c>
+      <c r="C124" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="D124" s="4" t="s">
+        <v>610</v>
+      </c>
+      <c r="E124" s="4" t="s">
+        <v>590</v>
+      </c>
       <c r="F124" s="4"/>
-      <c r="G124" s="3"/>
-    </row>
-    <row r="125" spans="1:7">
+      <c r="G124" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" ht="42">
       <c r="A125" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="B125" s="4"/>
-      <c r="C125" s="4"/>
-      <c r="D125" s="4"/>
-      <c r="E125" s="4"/>
+      <c r="B125" s="4" t="s">
+        <v>588</v>
+      </c>
+      <c r="C125" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="D125" s="4" t="s">
+        <v>610</v>
+      </c>
+      <c r="E125" s="4" t="s">
+        <v>595</v>
+      </c>
       <c r="F125" s="4"/>
-      <c r="G125" s="3"/>
-    </row>
-    <row r="126" spans="1:7">
+      <c r="G125" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" ht="63">
       <c r="A126" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="B126" s="4"/>
-      <c r="C126" s="4"/>
-      <c r="D126" s="4"/>
-      <c r="E126" s="4"/>
+      <c r="B126" s="4" t="s">
+        <v>588</v>
+      </c>
+      <c r="C126" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="D126" s="4" t="s">
+        <v>610</v>
+      </c>
+      <c r="E126" s="4" t="s">
+        <v>612</v>
+      </c>
       <c r="F126" s="4"/>
-      <c r="G126" s="3"/>
+      <c r="G126" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="127" spans="1:7">
       <c r="A127" s="3" t="s">
@@ -8908,7 +9204,7 @@
     </row>
     <row r="335" spans="1:7">
       <c r="A335" s="3" t="s">
-        <v>542</v>
+        <v>525</v>
       </c>
       <c r="B335" s="4"/>
       <c r="C335" s="4"/>
@@ -8919,7 +9215,7 @@
     </row>
     <row r="336" spans="1:7">
       <c r="A336" s="3" t="s">
-        <v>543</v>
+        <v>526</v>
       </c>
       <c r="B336" s="4"/>
       <c r="C336" s="4"/>
@@ -8930,7 +9226,7 @@
     </row>
     <row r="337" spans="1:7">
       <c r="A337" s="3" t="s">
-        <v>544</v>
+        <v>527</v>
       </c>
       <c r="B337" s="4"/>
       <c r="C337" s="4"/>
@@ -8941,7 +9237,7 @@
     </row>
     <row r="338" spans="1:7">
       <c r="A338" s="3" t="s">
-        <v>545</v>
+        <v>528</v>
       </c>
       <c r="B338" s="4"/>
       <c r="C338" s="4"/>
@@ -8952,7 +9248,7 @@
     </row>
     <row r="339" spans="1:7">
       <c r="A339" s="3" t="s">
-        <v>546</v>
+        <v>529</v>
       </c>
       <c r="B339" s="4"/>
       <c r="C339" s="4"/>
@@ -8963,7 +9259,7 @@
     </row>
     <row r="340" spans="1:7">
       <c r="A340" s="3" t="s">
-        <v>547</v>
+        <v>530</v>
       </c>
       <c r="B340" s="4"/>
       <c r="C340" s="4"/>
@@ -8974,7 +9270,7 @@
     </row>
     <row r="341" spans="1:7">
       <c r="A341" s="3" t="s">
-        <v>548</v>
+        <v>531</v>
       </c>
       <c r="B341" s="4"/>
       <c r="C341" s="4"/>
@@ -8985,7 +9281,7 @@
     </row>
     <row r="342" spans="1:7">
       <c r="A342" s="3" t="s">
-        <v>549</v>
+        <v>532</v>
       </c>
       <c r="B342" s="4"/>
       <c r="C342" s="4"/>
@@ -8997,8 +9293,8 @@
   </sheetData>
   <autoFilter ref="A2:H342" xr:uid="{833B9C12-88F9-F440-902B-BDAD178A24F6}"/>
   <phoneticPr fontId="1"/>
-  <conditionalFormatting sqref="A3:G342">
-    <cfRule type="expression" dxfId="0" priority="2">
+  <conditionalFormatting sqref="H62:H63 A3:G342">
+    <cfRule type="expression" dxfId="3" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>

--- a/docs/確認事項リスト.xlsx
+++ b/docs/確認事項リスト.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9506CCBC-C77D-644A-A085-5CF25612E002}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70E9C054-A9F0-3149-BAAF-B33E43360C4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{E987AAC5-D7CB-4143-BFFD-E0642F54BEB6}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1104" uniqueCount="615">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1139" uniqueCount="624">
   <si>
     <t>質問</t>
     <rPh sb="0" eb="2">
@@ -475,9 +475,6 @@
   </si>
   <si>
     <t>Q-86</t>
-  </si>
-  <si>
-    <t>Q-87</t>
   </si>
   <si>
     <t>Q-88</t>
@@ -3387,6 +3384,171 @@
   <si>
     <t>ジャンル名は必須・最大255文字・一意性チェックを入れる想定ですが、この制約で合っていますか？
 また、エラーメッセージは「ジャンル名は入力必須です。」「ジャンル名は255文字以内で入力してください。」「既に使用されているジャンル名です。」としましたがよろしいですか？</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>通知機能</t>
+    <rPh sb="0" eb="4">
+      <t>ツウティ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>日時バッチ処理を実行する時間は毎日0:00と設計しましたが、問題ないですか？</t>
+    <rPh sb="0" eb="2">
+      <t>ニチジバ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ジッコウ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ジカn</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>マイニティ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>★ 通知一覧画面</t>
+    <rPh sb="6" eb="8">
+      <t>ガメn</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>計画を設定した書籍は編集・削除が可能と設計しましたが、問題ないですか？</t>
+    <rPh sb="0" eb="2">
+      <t>ケイカク</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>sy</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>サクジョ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>リマインダー通知を発報するタイミングは期限3日前、期限前日、期限当日と設計しましたが、問題ないですか？
+また、通知内容はそれぞれ、「読書計画の期限3日前です」「読書計画の期限前日です」「読書計画の期限日です」としましたがよろしいですか？</t>
+    <rPh sb="9" eb="11">
+      <t>ハッポウ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>キゲn</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>ニティ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>キゲn</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>ゼンジテゥ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>キゲn</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>トウジテゥ</t>
+    </rPh>
+    <rPh sb="55" eb="59">
+      <t>ツウティ</t>
+    </rPh>
+    <rPh sb="66" eb="70">
+      <t>ドクセィオ</t>
+    </rPh>
+    <rPh sb="71" eb="73">
+      <t>キゲn</t>
+    </rPh>
+    <rPh sb="74" eb="75">
+      <t>ニティ</t>
+    </rPh>
+    <rPh sb="75" eb="76">
+      <t>マエ</t>
+    </rPh>
+    <rPh sb="87" eb="89">
+      <t>ゼンジテゥ</t>
+    </rPh>
+    <rPh sb="100" eb="101">
+      <t>_x0000_</t>
+    </rPh>
+    <rPh sb="100" eb="101">
+      <t xml:space="preserve">	</t>
+    </rPh>
+    <rPh sb="100" eb="101">
+      <t>_x0002_</t>
+    </rPh>
+    <rPh sb="100" eb="101">
+      <t/>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>日時バッチ処理を実行する対象の計画は、ステータスがin_progressのものと設計しましたが、問題ないですか？</t>
+    <rPh sb="0" eb="2">
+      <t>ニチジバ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ジッコウ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>タイショウ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ケイカク</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>マイニティ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Q-87</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Q-87を再質問：
+状態は任意・「in_progress」、「completed」、「expired」を選択可能で設計しましたが、この制約で合っていますか？</t>
+    <rPh sb="5" eb="6">
+      <t>SAI</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>シツモn</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>期日を経過した計画のステータスはexpiredにする設計としましたが、問題ないですか？</t>
+    <rPh sb="0" eb="2">
+      <t>ケイカク</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>キゲn</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>チョウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>期日を経過した計画の再エンゲージメントは3日後に通知で設計しましたが、問題ないですか？</t>
+    <rPh sb="10" eb="11">
+      <t xml:space="preserve">サイ </t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>ニティ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t xml:space="preserve">ゴ </t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>ツウティ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -3556,28 +3718,7 @@
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="1">
     <dxf>
       <fill>
         <patternFill>
@@ -3949,10 +4090,10 @@
         <v>14</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D2" s="5" t="s">
         <v>13</v>
@@ -3967,7 +4108,7 @@
         <v>2</v>
       </c>
       <c r="H2" s="12" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42">
@@ -3975,10 +4116,10 @@
         <v>15</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>3</v>
@@ -3987,13 +4128,13 @@
         <v>7</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H3" s="11" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="42">
@@ -4001,10 +4142,10 @@
         <v>22</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>4</v>
@@ -4013,13 +4154,13 @@
         <v>8</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="42">
@@ -4027,10 +4168,10 @@
         <v>23</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>3</v>
@@ -4039,13 +4180,13 @@
         <v>5</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="42">
@@ -4053,10 +4194,10 @@
         <v>24</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>4</v>
@@ -4065,13 +4206,13 @@
         <v>6</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="63">
@@ -4079,25 +4220,25 @@
         <v>25</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E7" s="4" t="s">
         <v>12</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="63">
@@ -4105,10 +4246,10 @@
         <v>26</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>10</v>
@@ -4117,13 +4258,13 @@
         <v>9</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H8" s="11" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="63">
@@ -4131,10 +4272,10 @@
         <v>27</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>10</v>
@@ -4143,13 +4284,13 @@
         <v>11</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H9" s="11" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="42">
@@ -4157,25 +4298,25 @@
         <v>28</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>10</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="63">
@@ -4183,25 +4324,25 @@
         <v>29</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>17</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H11" s="11" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="42">
@@ -4209,10 +4350,10 @@
         <v>30</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>17</v>
@@ -4221,13 +4362,13 @@
         <v>18</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H12" s="11" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="63">
@@ -4235,10 +4376,10 @@
         <v>31</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>20</v>
@@ -4247,13 +4388,13 @@
         <v>21</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H13" s="11" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="42">
@@ -4261,10 +4402,10 @@
         <v>32</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>20</v>
@@ -4273,13 +4414,13 @@
         <v>19</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="63">
@@ -4287,25 +4428,25 @@
         <v>33</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D15" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="E15" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="E15" s="4" t="s">
-        <v>121</v>
-      </c>
       <c r="F15" s="4" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H15" s="11" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="42">
@@ -4313,25 +4454,25 @@
         <v>34</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="G16" s="9" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H16" s="11" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="42">
@@ -4339,25 +4480,25 @@
         <v>35</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D17" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="E17" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="E17" s="4" t="s">
-        <v>124</v>
-      </c>
       <c r="F17" s="4" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H17" s="11" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="63">
@@ -4365,25 +4506,25 @@
         <v>36</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D18" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="E18" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="E18" s="4" t="s">
-        <v>126</v>
-      </c>
       <c r="F18" s="4" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="G18" s="9" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H18" s="11" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="63">
@@ -4391,25 +4532,25 @@
         <v>37</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D19" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="E19" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="E19" s="4" t="s">
-        <v>128</v>
-      </c>
       <c r="F19" s="4" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H19" s="11" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="42">
@@ -4417,25 +4558,25 @@
         <v>38</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D20" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="E20" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="E20" s="4" t="s">
-        <v>130</v>
-      </c>
       <c r="F20" s="4" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="G20" s="9" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H20" s="11" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="63">
@@ -4443,25 +4584,25 @@
         <v>39</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H21" s="11" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="42">
@@ -4469,25 +4610,25 @@
         <v>40</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D22" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="E22" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="E22" s="4" t="s">
-        <v>132</v>
-      </c>
       <c r="F22" s="4" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="G22" s="9" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H22" s="11" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="63">
@@ -4495,25 +4636,25 @@
         <v>41</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H23" s="11" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="42">
@@ -4521,25 +4662,25 @@
         <v>42</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D24" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="E24" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="E24" s="4" t="s">
-        <v>134</v>
-      </c>
       <c r="F24" s="4" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="G24" s="9" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H24" s="11" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="63">
@@ -4547,25 +4688,25 @@
         <v>43</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H25" s="11" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="63">
@@ -4573,25 +4714,25 @@
         <v>44</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="G26" s="9" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H26" s="11" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="42">
@@ -4599,25 +4740,25 @@
         <v>45</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D27" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="E27" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="E27" s="4" t="s">
-        <v>138</v>
-      </c>
       <c r="F27" s="4" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H27" s="11" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="63">
@@ -4625,25 +4766,25 @@
         <v>46</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="G28" s="9" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H28" s="11" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="63">
@@ -4651,25 +4792,25 @@
         <v>47</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E29" s="4" t="s">
+        <v>540</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>494</v>
+      </c>
+      <c r="G29" s="9" t="s">
+        <v>503</v>
+      </c>
+      <c r="H29" s="11" t="s">
         <v>541</v>
-      </c>
-      <c r="F29" s="4" t="s">
-        <v>495</v>
-      </c>
-      <c r="G29" s="9" t="s">
-        <v>504</v>
-      </c>
-      <c r="H29" s="11" t="s">
-        <v>542</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="42">
@@ -4677,25 +4818,25 @@
         <v>48</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D30" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="E30" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="E30" s="4" t="s">
-        <v>141</v>
-      </c>
       <c r="F30" s="4" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="G30" s="9" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H30" s="11" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="63">
@@ -4703,25 +4844,25 @@
         <v>49</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H31" s="11" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="63">
@@ -4729,25 +4870,25 @@
         <v>50</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D32" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="E32" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="E32" s="4" t="s">
-        <v>144</v>
-      </c>
       <c r="F32" s="4" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="G32" s="9" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H32" s="11" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="63">
@@ -4755,25 +4896,25 @@
         <v>51</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H33" s="11" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="42">
@@ -4781,25 +4922,25 @@
         <v>52</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D34" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="E34" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="E34" s="4" t="s">
-        <v>164</v>
-      </c>
       <c r="F34" s="4" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="G34" s="9" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H34" s="11" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="84">
@@ -4807,25 +4948,25 @@
         <v>53</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D35" s="4" t="s">
         <v>10</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H35" s="11" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="63">
@@ -4833,25 +4974,25 @@
         <v>54</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D36" s="4" t="s">
         <v>10</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="G36" s="9" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H36" s="11" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="63">
@@ -4859,25 +5000,25 @@
         <v>55</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D37" s="4" t="s">
         <v>10</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H37" s="11" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="63">
@@ -4885,25 +5026,25 @@
         <v>56</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D38" s="4" t="s">
         <v>10</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="G38" s="9" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H38" s="11" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="63">
@@ -4911,25 +5052,25 @@
         <v>57</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D39" s="4" t="s">
         <v>10</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H39" s="11" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="63">
@@ -4937,25 +5078,25 @@
         <v>58</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D40" s="4" t="s">
         <v>17</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="G40" s="9" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H40" s="11" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="63">
@@ -4963,25 +5104,25 @@
         <v>59</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D41" s="4" t="s">
         <v>17</v>
       </c>
       <c r="E41" s="8" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H41" s="11" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="63">
@@ -4989,25 +5130,25 @@
         <v>60</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D42" s="4" t="s">
         <v>20</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G42" s="9" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H42" s="11" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="63">
@@ -5015,25 +5156,25 @@
         <v>61</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H43" s="11" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="44" spans="1:8" ht="63">
@@ -5041,25 +5182,25 @@
         <v>62</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="G44" s="9" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H44" s="11" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="45" spans="1:8" ht="42">
@@ -5067,25 +5208,25 @@
         <v>63</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H45" s="11" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="46" spans="1:8" ht="63">
@@ -5093,25 +5234,25 @@
         <v>64</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="G46" s="9" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H46" s="11" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="63">
@@ -5119,25 +5260,25 @@
         <v>65</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H47" s="11" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="48" spans="1:8" ht="63">
@@ -5145,25 +5286,25 @@
         <v>66</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="G48" s="9" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H48" s="11" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="49" spans="1:8" ht="63">
@@ -5171,25 +5312,25 @@
         <v>67</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H49" s="11" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="50" spans="1:8" ht="63">
@@ -5197,25 +5338,25 @@
         <v>68</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="G50" s="9" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H50" s="11" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="51" spans="1:8" ht="63">
@@ -5223,25 +5364,25 @@
         <v>69</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H51" s="11" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="63">
@@ -5249,25 +5390,25 @@
         <v>70</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="G52" s="9" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H52" s="11" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="53" spans="1:8" ht="63">
@@ -5275,25 +5416,25 @@
         <v>71</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D53" s="4" t="s">
         <v>20</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H53" s="11" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="54" spans="1:8" ht="63">
@@ -5301,25 +5442,25 @@
         <v>72</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="G54" s="9" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H54" s="11" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="55" spans="1:8" ht="42">
@@ -5327,25 +5468,25 @@
         <v>73</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H55" s="11" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="56" spans="1:8" ht="42">
@@ -5353,25 +5494,25 @@
         <v>74</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="G56" s="9" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H56" s="11" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="57" spans="1:8" ht="63">
@@ -5379,25 +5520,25 @@
         <v>75</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H57" s="10" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="58" spans="1:8" ht="63">
@@ -5405,25 +5546,25 @@
         <v>76</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="G58" s="9" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H58" s="10" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="59" spans="1:8" ht="63">
@@ -5431,25 +5572,25 @@
         <v>77</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H59" s="11" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="60" spans="1:8" ht="21">
@@ -5457,25 +5598,25 @@
         <v>78</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C60" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="D60" s="4" t="s">
         <v>205</v>
       </c>
-      <c r="D60" s="4" t="s">
-        <v>206</v>
-      </c>
       <c r="E60" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="G60" s="9" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H60" s="11" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="61" spans="1:8" ht="21">
@@ -5483,22 +5624,22 @@
         <v>79</v>
       </c>
       <c r="B61" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="C61" s="4" t="s">
         <v>209</v>
       </c>
-      <c r="C61" s="4" t="s">
+      <c r="D61" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="D61" s="4" t="s">
+      <c r="E61" s="4" t="s">
         <v>211</v>
       </c>
-      <c r="E61" s="4" t="s">
-        <v>212</v>
-      </c>
       <c r="F61" s="4" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="62" spans="1:8" ht="42">
@@ -5506,25 +5647,25 @@
         <v>80</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D62" s="4" t="s">
         <v>20</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="G62" s="9" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H62" s="13" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="63" spans="1:8" ht="42">
@@ -5532,25 +5673,25 @@
         <v>81</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="G63" s="9" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H63" s="13" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="64" spans="1:8" ht="84">
@@ -5558,25 +5699,25 @@
         <v>82</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="G64" s="9" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H64" s="11" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="65" spans="1:8" ht="84">
@@ -5584,25 +5725,25 @@
         <v>83</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H65" s="11" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="63">
@@ -5610,48 +5751,48 @@
         <v>84</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G66" s="9" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H66" s="11" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="67" spans="1:8" ht="63">
       <c r="A67" s="3" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B67" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="C67" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="C67" s="4" t="s">
+      <c r="D67" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="D67" s="4" t="s">
+      <c r="E67" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="E67" s="4" t="s">
-        <v>226</v>
-      </c>
       <c r="F67" s="4" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H67" s="10"/>
     </row>
@@ -5660,22 +5801,22 @@
         <v>85</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D68" s="4" t="s">
         <v>20</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="G68" s="9" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H68" s="10"/>
     </row>
@@ -5684,25 +5825,25 @@
         <v>86</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C69" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="D69" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="E69" s="4" t="s">
         <v>229</v>
       </c>
-      <c r="D69" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="E69" s="4" t="s">
-        <v>230</v>
-      </c>
       <c r="F69" s="4" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="70" spans="1:8" ht="42">
@@ -5710,25 +5851,25 @@
         <v>87</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C70" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="D70" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="E70" s="4" t="s">
         <v>232</v>
       </c>
-      <c r="D70" s="4" t="s">
-        <v>231</v>
-      </c>
-      <c r="E70" s="4" t="s">
-        <v>233</v>
-      </c>
       <c r="F70" s="4" t="s">
+        <v>502</v>
+      </c>
+      <c r="G70" s="9" t="s">
         <v>503</v>
       </c>
-      <c r="G70" s="9" t="s">
-        <v>504</v>
-      </c>
       <c r="H70" s="10" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="63">
@@ -5736,25 +5877,25 @@
         <v>88</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C71" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="D71" s="4" t="s">
         <v>235</v>
       </c>
-      <c r="D71" s="4" t="s">
-        <v>236</v>
-      </c>
       <c r="E71" s="4" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H71" s="10" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="72" spans="1:8" ht="84">
@@ -5762,16 +5903,16 @@
         <v>89</v>
       </c>
       <c r="B72" s="4" t="s">
+        <v>504</v>
+      </c>
+      <c r="C72" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="D72" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="E72" s="4" t="s">
         <v>505</v>
-      </c>
-      <c r="C72" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="D72" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="E72" s="4" t="s">
-        <v>506</v>
       </c>
       <c r="F72" s="4"/>
       <c r="G72" s="3" t="s">
@@ -5783,16 +5924,16 @@
         <v>90</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="F73" s="4"/>
       <c r="G73" s="3" t="s">
@@ -5804,16 +5945,16 @@
         <v>91</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="F74" s="4"/>
       <c r="G74" s="3" t="s">
@@ -5825,16 +5966,16 @@
         <v>92</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="F75" s="4"/>
       <c r="G75" s="3" t="s">
@@ -5846,16 +5987,16 @@
         <v>93</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="F76" s="4"/>
       <c r="G76" s="3" t="s">
@@ -5867,16 +6008,16 @@
         <v>94</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="F77" s="4"/>
       <c r="G77" s="3" t="s">
@@ -5888,16 +6029,16 @@
         <v>95</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="F78" s="4"/>
       <c r="G78" s="3" t="s">
@@ -5909,16 +6050,16 @@
         <v>96</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="F79" s="4"/>
       <c r="G79" s="3" t="s">
@@ -5930,16 +6071,16 @@
         <v>97</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="F80" s="4"/>
       <c r="G80" s="3" t="s">
@@ -5951,22 +6092,22 @@
         <v>98</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D81" s="4" t="s">
         <v>17</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="G81" s="9" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="82" spans="1:7" ht="63">
@@ -5974,16 +6115,16 @@
         <v>99</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D82" s="4" t="s">
         <v>20</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="F82" s="4"/>
       <c r="G82" s="3" t="s">
@@ -5995,16 +6136,16 @@
         <v>100</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="F83" s="4"/>
       <c r="G83" s="3" t="s">
@@ -6016,16 +6157,16 @@
         <v>101</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="E84" s="4" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="F84" s="4"/>
       <c r="G84" s="3" t="s">
@@ -6037,16 +6178,16 @@
         <v>102</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="E85" s="4" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="F85" s="4"/>
       <c r="G85" s="3" t="s">
@@ -6058,16 +6199,16 @@
         <v>103</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="E86" s="4" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="F86" s="4"/>
       <c r="G86" s="3" t="s">
@@ -6079,16 +6220,16 @@
         <v>104</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="F87" s="4"/>
       <c r="G87" s="3" t="s">
@@ -6100,16 +6241,16 @@
         <v>105</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F88" s="4"/>
       <c r="G88" s="3" t="s">
@@ -6118,19 +6259,19 @@
     </row>
     <row r="89" spans="1:7" ht="42">
       <c r="A89" s="3" t="s">
-        <v>106</v>
+        <v>620</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="F89" s="4"/>
       <c r="G89" s="3" t="s">
@@ -6139,19 +6280,19 @@
     </row>
     <row r="90" spans="1:7" ht="84">
       <c r="A90" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F90" s="4"/>
       <c r="G90" s="3" t="s">
@@ -6160,19 +6301,19 @@
     </row>
     <row r="91" spans="1:7" ht="84">
       <c r="A91" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C91" s="4" t="s">
+        <v>522</v>
+      </c>
+      <c r="D91" s="4" t="s">
         <v>523</v>
       </c>
-      <c r="D91" s="4" t="s">
-        <v>524</v>
-      </c>
       <c r="E91" s="4" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="F91" s="4"/>
       <c r="G91" s="3" t="s">
@@ -6181,19 +6322,19 @@
     </row>
     <row r="92" spans="1:7" ht="21">
       <c r="A92" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B92" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="C92" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="D92" s="4" t="s">
         <v>238</v>
       </c>
-      <c r="C92" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="D92" s="4" t="s">
+      <c r="E92" s="4" t="s">
         <v>239</v>
-      </c>
-      <c r="E92" s="4" t="s">
-        <v>240</v>
       </c>
       <c r="F92" s="4"/>
       <c r="G92" s="3" t="s">
@@ -6202,19 +6343,19 @@
     </row>
     <row r="93" spans="1:7" ht="105">
       <c r="A93" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E93" s="4" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="F93" s="4"/>
       <c r="G93" s="3" t="s">
@@ -6223,19 +6364,19 @@
     </row>
     <row r="94" spans="1:7" ht="84">
       <c r="A94" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E94" s="4" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="F94" s="4"/>
       <c r="G94" s="3" t="s">
@@ -6244,19 +6385,19 @@
     </row>
     <row r="95" spans="1:7" ht="84">
       <c r="A95" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E95" s="4" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="F95" s="4"/>
       <c r="G95" s="3" t="s">
@@ -6265,19 +6406,19 @@
     </row>
     <row r="96" spans="1:7" ht="63">
       <c r="A96" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E96" s="4" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="F96" s="4"/>
       <c r="G96" s="3" t="s">
@@ -6286,19 +6427,19 @@
     </row>
     <row r="97" spans="1:7" ht="105">
       <c r="A97" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C97" s="4" t="s">
+        <v>480</v>
+      </c>
+      <c r="D97" s="4" t="s">
         <v>481</v>
       </c>
-      <c r="D97" s="4" t="s">
-        <v>482</v>
-      </c>
       <c r="E97" s="4" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="F97" s="4"/>
       <c r="G97" s="3" t="s">
@@ -6307,19 +6448,19 @@
     </row>
     <row r="98" spans="1:7" ht="84">
       <c r="A98" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C98" s="4" t="s">
+        <v>480</v>
+      </c>
+      <c r="D98" s="4" t="s">
         <v>481</v>
       </c>
-      <c r="D98" s="4" t="s">
-        <v>482</v>
-      </c>
       <c r="E98" s="4" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="F98" s="4"/>
       <c r="G98" s="3" t="s">
@@ -6328,19 +6469,19 @@
     </row>
     <row r="99" spans="1:7" ht="63">
       <c r="A99" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C99" s="4" t="s">
+        <v>480</v>
+      </c>
+      <c r="D99" s="4" t="s">
         <v>481</v>
       </c>
-      <c r="D99" s="4" t="s">
-        <v>482</v>
-      </c>
       <c r="E99" s="4" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="F99" s="4"/>
       <c r="G99" s="3" t="s">
@@ -6349,19 +6490,19 @@
     </row>
     <row r="100" spans="1:7" ht="84">
       <c r="A100" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C100" s="4" t="s">
+        <v>478</v>
+      </c>
+      <c r="D100" s="4" t="s">
         <v>479</v>
       </c>
-      <c r="D100" s="4" t="s">
-        <v>480</v>
-      </c>
       <c r="E100" s="4" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="F100" s="4"/>
       <c r="G100" s="3" t="s">
@@ -6370,19 +6511,19 @@
     </row>
     <row r="101" spans="1:7" ht="84">
       <c r="A101" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E101" s="4" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="F101" s="4"/>
       <c r="G101" s="3" t="s">
@@ -6391,19 +6532,19 @@
     </row>
     <row r="102" spans="1:7" ht="84">
       <c r="A102" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C102" s="4" t="s">
+        <v>480</v>
+      </c>
+      <c r="D102" s="4" t="s">
         <v>481</v>
       </c>
-      <c r="D102" s="4" t="s">
-        <v>482</v>
-      </c>
       <c r="E102" s="4" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="F102" s="4"/>
       <c r="G102" s="3" t="s">
@@ -6412,19 +6553,19 @@
     </row>
     <row r="103" spans="1:7" ht="63">
       <c r="A103" s="3" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C103" s="4" t="s">
+        <v>480</v>
+      </c>
+      <c r="D103" s="4" t="s">
         <v>481</v>
       </c>
-      <c r="D103" s="4" t="s">
-        <v>482</v>
-      </c>
       <c r="E103" s="4" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="F103" s="4"/>
       <c r="G103" s="3" t="s">
@@ -6433,19 +6574,19 @@
     </row>
     <row r="104" spans="1:7" ht="84">
       <c r="A104" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C104" s="4" t="s">
+        <v>480</v>
+      </c>
+      <c r="D104" s="4" t="s">
         <v>481</v>
       </c>
-      <c r="D104" s="4" t="s">
-        <v>482</v>
-      </c>
       <c r="E104" s="4" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="F104" s="4"/>
       <c r="G104" s="3" t="s">
@@ -6454,19 +6595,19 @@
     </row>
     <row r="105" spans="1:7" ht="84">
       <c r="A105" s="3" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C105" s="4" t="s">
+        <v>480</v>
+      </c>
+      <c r="D105" s="4" t="s">
         <v>481</v>
       </c>
-      <c r="D105" s="4" t="s">
-        <v>482</v>
-      </c>
       <c r="E105" s="4" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="F105" s="4"/>
       <c r="G105" s="3" t="s">
@@ -6475,19 +6616,19 @@
     </row>
     <row r="106" spans="1:7" ht="84">
       <c r="A106" s="3" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C106" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D106" s="4" t="s">
+        <v>532</v>
+      </c>
+      <c r="E106" s="4" t="s">
         <v>533</v>
-      </c>
-      <c r="E106" s="4" t="s">
-        <v>534</v>
       </c>
       <c r="F106" s="4"/>
       <c r="G106" s="3" t="s">
@@ -6496,19 +6637,19 @@
     </row>
     <row r="107" spans="1:7" ht="63">
       <c r="A107" s="3" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C107" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="E107" s="4" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="F107" s="4"/>
       <c r="G107" s="3" t="s">
@@ -6517,19 +6658,19 @@
     </row>
     <row r="108" spans="1:7" ht="84">
       <c r="A108" s="3" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D108" s="4" t="s">
+        <v>535</v>
+      </c>
+      <c r="E108" s="4" t="s">
         <v>536</v>
-      </c>
-      <c r="E108" s="4" t="s">
-        <v>537</v>
       </c>
       <c r="F108" s="4"/>
       <c r="G108" s="3" t="s">
@@ -6538,19 +6679,19 @@
     </row>
     <row r="109" spans="1:7" ht="126">
       <c r="A109" s="3" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C109" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="E109" s="4" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="F109" s="4"/>
       <c r="G109" s="3" t="s">
@@ -6559,19 +6700,19 @@
     </row>
     <row r="110" spans="1:7" ht="105">
       <c r="A110" s="3" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="E110" s="4" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="F110" s="4"/>
       <c r="G110" s="3" t="s">
@@ -6580,19 +6721,19 @@
     </row>
     <row r="111" spans="1:7" ht="42">
       <c r="A111" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B111" s="4" t="s">
+        <v>587</v>
+      </c>
+      <c r="C111" s="4" t="s">
+        <v>586</v>
+      </c>
+      <c r="D111" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="E111" s="4" t="s">
         <v>588</v>
-      </c>
-      <c r="C111" s="4" t="s">
-        <v>587</v>
-      </c>
-      <c r="D111" s="4" t="s">
-        <v>206</v>
-      </c>
-      <c r="E111" s="4" t="s">
-        <v>589</v>
       </c>
       <c r="F111" s="4"/>
       <c r="G111" s="3" t="s">
@@ -6601,19 +6742,19 @@
     </row>
     <row r="112" spans="1:7" ht="63">
       <c r="A112" s="3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="C112" s="4" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="D112" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E112" s="4" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="F112" s="4"/>
       <c r="G112" s="3" t="s">
@@ -6622,19 +6763,19 @@
     </row>
     <row r="113" spans="1:7" ht="63">
       <c r="A113" s="3" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="C113" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D113" s="4" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E113" s="4" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="F113" s="4"/>
       <c r="G113" s="3" t="s">
@@ -6643,19 +6784,19 @@
     </row>
     <row r="114" spans="1:7" ht="42">
       <c r="A114" s="3" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="C114" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D114" s="4" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E114" s="4" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="F114" s="4"/>
       <c r="G114" s="3" t="s">
@@ -6664,19 +6805,19 @@
     </row>
     <row r="115" spans="1:7" ht="42">
       <c r="A115" s="3" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="C115" s="4" t="s">
+        <v>478</v>
+      </c>
+      <c r="D115" s="4" t="s">
         <v>479</v>
       </c>
-      <c r="D115" s="4" t="s">
-        <v>480</v>
-      </c>
       <c r="E115" s="4" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="F115" s="4"/>
       <c r="G115" s="3" t="s">
@@ -6685,19 +6826,19 @@
     </row>
     <row r="116" spans="1:7" ht="42">
       <c r="A116" s="3" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="C116" s="4" t="s">
+        <v>478</v>
+      </c>
+      <c r="D116" s="4" t="s">
         <v>479</v>
       </c>
-      <c r="D116" s="4" t="s">
-        <v>480</v>
-      </c>
       <c r="E116" s="4" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="F116" s="4"/>
       <c r="G116" s="3" t="s">
@@ -6706,19 +6847,19 @@
     </row>
     <row r="117" spans="1:7" ht="42">
       <c r="A117" s="3" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="C117" s="4" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D117" s="4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E117" s="4" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="F117" s="4"/>
       <c r="G117" s="3" t="s">
@@ -6727,19 +6868,19 @@
     </row>
     <row r="118" spans="1:7" ht="42">
       <c r="A118" s="3" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="C118" s="4" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D118" s="4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E118" s="4" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="F118" s="4"/>
       <c r="G118" s="3" t="s">
@@ -6748,19 +6889,19 @@
     </row>
     <row r="119" spans="1:7" ht="63">
       <c r="A119" s="3" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="C119" s="4" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D119" s="4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E119" s="4" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="F119" s="4"/>
       <c r="G119" s="3" t="s">
@@ -6769,19 +6910,19 @@
     </row>
     <row r="120" spans="1:7" ht="42">
       <c r="A120" s="3" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="C120" s="4" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D120" s="4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E120" s="4" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="F120" s="4"/>
       <c r="G120" s="3" t="s">
@@ -6790,19 +6931,19 @@
     </row>
     <row r="121" spans="1:7" ht="63">
       <c r="A121" s="3" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="C121" s="4" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D121" s="4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E121" s="4" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="F121" s="4"/>
       <c r="G121" s="3" t="s">
@@ -6811,19 +6952,19 @@
     </row>
     <row r="122" spans="1:7" ht="42">
       <c r="A122" s="3" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="C122" s="4" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D122" s="4" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="E122" s="4" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="F122" s="4"/>
       <c r="G122" s="3" t="s">
@@ -6832,19 +6973,19 @@
     </row>
     <row r="123" spans="1:7" ht="42">
       <c r="A123" s="3" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="C123" s="4" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D123" s="4" t="s">
+        <v>609</v>
+      </c>
+      <c r="E123" s="4" t="s">
         <v>610</v>
-      </c>
-      <c r="E123" s="4" t="s">
-        <v>611</v>
       </c>
       <c r="F123" s="4"/>
       <c r="G123" s="3" t="s">
@@ -6853,19 +6994,19 @@
     </row>
     <row r="124" spans="1:7" ht="63">
       <c r="A124" s="3" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="C124" s="4" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D124" s="4" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="E124" s="4" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="F124" s="4"/>
       <c r="G124" s="3" t="s">
@@ -6874,19 +7015,19 @@
     </row>
     <row r="125" spans="1:7" ht="42">
       <c r="A125" s="3" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="C125" s="4" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D125" s="4" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="E125" s="4" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="F125" s="4"/>
       <c r="G125" s="3" t="s">
@@ -6895,105 +7036,175 @@
     </row>
     <row r="126" spans="1:7" ht="63">
       <c r="A126" s="3" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="C126" s="4" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D126" s="4" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="E126" s="4" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="F126" s="4"/>
       <c r="G126" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="127" spans="1:7">
+    <row r="127" spans="1:7" ht="42">
       <c r="A127" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="B127" s="4" t="s">
+        <v>614</v>
+      </c>
+      <c r="C127" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="D127" s="4" t="s">
+        <v>616</v>
+      </c>
+      <c r="E127" s="4" t="s">
+        <v>615</v>
+      </c>
+      <c r="F127" s="4"/>
+      <c r="G127" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" ht="84">
+      <c r="A128" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="B127" s="4"/>
-      <c r="C127" s="4"/>
-      <c r="D127" s="4"/>
-      <c r="E127" s="4"/>
-      <c r="F127" s="4"/>
-      <c r="G127" s="3"/>
-    </row>
-    <row r="128" spans="1:7">
-      <c r="A128" s="3" t="s">
+      <c r="B128" s="4" t="s">
+        <v>614</v>
+      </c>
+      <c r="C128" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="D128" s="4" t="s">
+        <v>616</v>
+      </c>
+      <c r="E128" s="4" t="s">
+        <v>618</v>
+      </c>
+      <c r="F128" s="4"/>
+      <c r="G128" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" ht="63">
+      <c r="A129" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="B128" s="4"/>
-      <c r="C128" s="4"/>
-      <c r="D128" s="4"/>
-      <c r="E128" s="4"/>
-      <c r="F128" s="4"/>
-      <c r="G128" s="3"/>
-    </row>
-    <row r="129" spans="1:7">
-      <c r="A129" s="3" t="s">
+      <c r="B129" s="4" t="s">
+        <v>614</v>
+      </c>
+      <c r="C129" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="D129" s="4" t="s">
+        <v>616</v>
+      </c>
+      <c r="E129" s="4" t="s">
+        <v>621</v>
+      </c>
+      <c r="F129" s="4"/>
+      <c r="G129" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" ht="42">
+      <c r="A130" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="B129" s="4"/>
-      <c r="C129" s="4"/>
-      <c r="D129" s="4"/>
-      <c r="E129" s="4"/>
-      <c r="F129" s="4"/>
-      <c r="G129" s="3"/>
-    </row>
-    <row r="130" spans="1:7">
-      <c r="A130" s="3" t="s">
+      <c r="B130" s="4" t="s">
+        <v>614</v>
+      </c>
+      <c r="C130" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="D130" s="4" t="s">
+        <v>616</v>
+      </c>
+      <c r="E130" s="4" t="s">
+        <v>622</v>
+      </c>
+      <c r="F130" s="4"/>
+      <c r="G130" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" ht="42">
+      <c r="A131" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="B130" s="4"/>
-      <c r="C130" s="4"/>
-      <c r="D130" s="4"/>
-      <c r="E130" s="4"/>
-      <c r="F130" s="4"/>
-      <c r="G130" s="3"/>
-    </row>
-    <row r="131" spans="1:7">
-      <c r="A131" s="3" t="s">
+      <c r="B131" s="4" t="s">
+        <v>614</v>
+      </c>
+      <c r="C131" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="D131" s="4" t="s">
+        <v>616</v>
+      </c>
+      <c r="E131" s="4" t="s">
+        <v>617</v>
+      </c>
+      <c r="F131" s="4"/>
+      <c r="G131" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" ht="42">
+      <c r="A132" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="B131" s="4"/>
-      <c r="C131" s="4"/>
-      <c r="D131" s="4"/>
-      <c r="E131" s="4"/>
-      <c r="F131" s="4"/>
-      <c r="G131" s="3"/>
-    </row>
-    <row r="132" spans="1:7">
-      <c r="A132" s="3" t="s">
+      <c r="B132" s="4" t="s">
+        <v>614</v>
+      </c>
+      <c r="C132" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="D132" s="4" t="s">
+        <v>616</v>
+      </c>
+      <c r="E132" s="4" t="s">
+        <v>619</v>
+      </c>
+      <c r="F132" s="4"/>
+      <c r="G132" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" ht="42">
+      <c r="A133" s="3" t="s">
         <v>270</v>
       </c>
-      <c r="B132" s="4"/>
-      <c r="C132" s="4"/>
-      <c r="D132" s="4"/>
-      <c r="E132" s="4"/>
-      <c r="F132" s="4"/>
-      <c r="G132" s="3"/>
-    </row>
-    <row r="133" spans="1:7">
-      <c r="A133" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="B133" s="4"/>
-      <c r="C133" s="4"/>
-      <c r="D133" s="4"/>
-      <c r="E133" s="4"/>
+      <c r="B133" s="4" t="s">
+        <v>614</v>
+      </c>
+      <c r="C133" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="D133" s="4" t="s">
+        <v>616</v>
+      </c>
+      <c r="E133" s="4" t="s">
+        <v>623</v>
+      </c>
       <c r="F133" s="4"/>
-      <c r="G133" s="3"/>
+      <c r="G133" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="134" spans="1:7">
       <c r="A134" s="3" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B134" s="4"/>
       <c r="C134" s="4"/>
@@ -7004,7 +7215,7 @@
     </row>
     <row r="135" spans="1:7">
       <c r="A135" s="3" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B135" s="4"/>
       <c r="C135" s="4"/>
@@ -7015,7 +7226,7 @@
     </row>
     <row r="136" spans="1:7">
       <c r="A136" s="3" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B136" s="4"/>
       <c r="C136" s="4"/>
@@ -7026,7 +7237,7 @@
     </row>
     <row r="137" spans="1:7">
       <c r="A137" s="3" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B137" s="4"/>
       <c r="C137" s="4"/>
@@ -7037,7 +7248,7 @@
     </row>
     <row r="138" spans="1:7">
       <c r="A138" s="3" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B138" s="4"/>
       <c r="C138" s="4"/>
@@ -7048,7 +7259,7 @@
     </row>
     <row r="139" spans="1:7">
       <c r="A139" s="3" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B139" s="4"/>
       <c r="C139" s="4"/>
@@ -7059,7 +7270,7 @@
     </row>
     <row r="140" spans="1:7">
       <c r="A140" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B140" s="4"/>
       <c r="C140" s="4"/>
@@ -7070,7 +7281,7 @@
     </row>
     <row r="141" spans="1:7">
       <c r="A141" s="3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B141" s="4"/>
       <c r="C141" s="4"/>
@@ -7081,7 +7292,7 @@
     </row>
     <row r="142" spans="1:7">
       <c r="A142" s="3" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B142" s="4"/>
       <c r="C142" s="4"/>
@@ -7092,7 +7303,7 @@
     </row>
     <row r="143" spans="1:7">
       <c r="A143" s="3" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B143" s="4"/>
       <c r="C143" s="4"/>
@@ -7103,7 +7314,7 @@
     </row>
     <row r="144" spans="1:7">
       <c r="A144" s="3" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B144" s="4"/>
       <c r="C144" s="4"/>
@@ -7114,7 +7325,7 @@
     </row>
     <row r="145" spans="1:7">
       <c r="A145" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B145" s="4"/>
       <c r="C145" s="4"/>
@@ -7125,7 +7336,7 @@
     </row>
     <row r="146" spans="1:7">
       <c r="A146" s="3" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B146" s="4"/>
       <c r="C146" s="4"/>
@@ -7136,7 +7347,7 @@
     </row>
     <row r="147" spans="1:7">
       <c r="A147" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B147" s="4"/>
       <c r="C147" s="4"/>
@@ -7147,7 +7358,7 @@
     </row>
     <row r="148" spans="1:7">
       <c r="A148" s="3" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B148" s="4"/>
       <c r="C148" s="4"/>
@@ -7158,7 +7369,7 @@
     </row>
     <row r="149" spans="1:7">
       <c r="A149" s="3" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B149" s="4"/>
       <c r="C149" s="4"/>
@@ -7169,7 +7380,7 @@
     </row>
     <row r="150" spans="1:7">
       <c r="A150" s="3" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B150" s="4"/>
       <c r="C150" s="4"/>
@@ -7180,7 +7391,7 @@
     </row>
     <row r="151" spans="1:7">
       <c r="A151" s="3" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B151" s="4"/>
       <c r="C151" s="4"/>
@@ -7191,7 +7402,7 @@
     </row>
     <row r="152" spans="1:7">
       <c r="A152" s="3" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B152" s="4"/>
       <c r="C152" s="4"/>
@@ -7202,7 +7413,7 @@
     </row>
     <row r="153" spans="1:7">
       <c r="A153" s="3" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B153" s="4"/>
       <c r="C153" s="4"/>
@@ -7213,7 +7424,7 @@
     </row>
     <row r="154" spans="1:7">
       <c r="A154" s="3" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B154" s="4"/>
       <c r="C154" s="4"/>
@@ -7224,7 +7435,7 @@
     </row>
     <row r="155" spans="1:7">
       <c r="A155" s="3" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B155" s="4"/>
       <c r="C155" s="4"/>
@@ -7235,7 +7446,7 @@
     </row>
     <row r="156" spans="1:7">
       <c r="A156" s="3" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B156" s="4"/>
       <c r="C156" s="4"/>
@@ -7246,7 +7457,7 @@
     </row>
     <row r="157" spans="1:7">
       <c r="A157" s="3" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B157" s="4"/>
       <c r="C157" s="4"/>
@@ -7257,7 +7468,7 @@
     </row>
     <row r="158" spans="1:7">
       <c r="A158" s="3" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B158" s="4"/>
       <c r="C158" s="4"/>
@@ -7268,7 +7479,7 @@
     </row>
     <row r="159" spans="1:7">
       <c r="A159" s="3" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B159" s="4"/>
       <c r="C159" s="4"/>
@@ -7279,7 +7490,7 @@
     </row>
     <row r="160" spans="1:7">
       <c r="A160" s="3" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B160" s="4"/>
       <c r="C160" s="4"/>
@@ -7290,7 +7501,7 @@
     </row>
     <row r="161" spans="1:7">
       <c r="A161" s="3" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B161" s="4"/>
       <c r="C161" s="4"/>
@@ -7301,7 +7512,7 @@
     </row>
     <row r="162" spans="1:7">
       <c r="A162" s="3" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B162" s="4"/>
       <c r="C162" s="4"/>
@@ -7312,7 +7523,7 @@
     </row>
     <row r="163" spans="1:7">
       <c r="A163" s="3" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B163" s="4"/>
       <c r="C163" s="4"/>
@@ -7323,7 +7534,7 @@
     </row>
     <row r="164" spans="1:7">
       <c r="A164" s="3" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B164" s="4"/>
       <c r="C164" s="4"/>
@@ -7334,7 +7545,7 @@
     </row>
     <row r="165" spans="1:7">
       <c r="A165" s="3" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B165" s="4"/>
       <c r="C165" s="4"/>
@@ -7345,7 +7556,7 @@
     </row>
     <row r="166" spans="1:7">
       <c r="A166" s="3" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B166" s="4"/>
       <c r="C166" s="4"/>
@@ -7356,7 +7567,7 @@
     </row>
     <row r="167" spans="1:7">
       <c r="A167" s="3" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B167" s="4"/>
       <c r="C167" s="4"/>
@@ -7367,7 +7578,7 @@
     </row>
     <row r="168" spans="1:7">
       <c r="A168" s="3" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B168" s="4"/>
       <c r="C168" s="4"/>
@@ -7378,7 +7589,7 @@
     </row>
     <row r="169" spans="1:7">
       <c r="A169" s="3" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B169" s="4"/>
       <c r="C169" s="4"/>
@@ -7389,7 +7600,7 @@
     </row>
     <row r="170" spans="1:7">
       <c r="A170" s="3" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B170" s="4"/>
       <c r="C170" s="4"/>
@@ -7400,7 +7611,7 @@
     </row>
     <row r="171" spans="1:7">
       <c r="A171" s="3" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B171" s="4"/>
       <c r="C171" s="4"/>
@@ -7411,7 +7622,7 @@
     </row>
     <row r="172" spans="1:7">
       <c r="A172" s="3" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B172" s="4"/>
       <c r="C172" s="4"/>
@@ -7422,7 +7633,7 @@
     </row>
     <row r="173" spans="1:7">
       <c r="A173" s="3" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B173" s="4"/>
       <c r="C173" s="4"/>
@@ -7433,7 +7644,7 @@
     </row>
     <row r="174" spans="1:7">
       <c r="A174" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B174" s="4"/>
       <c r="C174" s="4"/>
@@ -7444,7 +7655,7 @@
     </row>
     <row r="175" spans="1:7">
       <c r="A175" s="3" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B175" s="4"/>
       <c r="C175" s="4"/>
@@ -7455,7 +7666,7 @@
     </row>
     <row r="176" spans="1:7">
       <c r="A176" s="3" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B176" s="4"/>
       <c r="C176" s="4"/>
@@ -7466,7 +7677,7 @@
     </row>
     <row r="177" spans="1:7">
       <c r="A177" s="3" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B177" s="4"/>
       <c r="C177" s="4"/>
@@ -7477,7 +7688,7 @@
     </row>
     <row r="178" spans="1:7">
       <c r="A178" s="3" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B178" s="4"/>
       <c r="C178" s="4"/>
@@ -7488,7 +7699,7 @@
     </row>
     <row r="179" spans="1:7">
       <c r="A179" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B179" s="4"/>
       <c r="C179" s="4"/>
@@ -7499,7 +7710,7 @@
     </row>
     <row r="180" spans="1:7">
       <c r="A180" s="3" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B180" s="4"/>
       <c r="C180" s="4"/>
@@ -7510,7 +7721,7 @@
     </row>
     <row r="181" spans="1:7">
       <c r="A181" s="3" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B181" s="4"/>
       <c r="C181" s="4"/>
@@ -7521,7 +7732,7 @@
     </row>
     <row r="182" spans="1:7">
       <c r="A182" s="3" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B182" s="4"/>
       <c r="C182" s="4"/>
@@ -7532,7 +7743,7 @@
     </row>
     <row r="183" spans="1:7">
       <c r="A183" s="3" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B183" s="4"/>
       <c r="C183" s="4"/>
@@ -7543,7 +7754,7 @@
     </row>
     <row r="184" spans="1:7">
       <c r="A184" s="3" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B184" s="4"/>
       <c r="C184" s="4"/>
@@ -7554,7 +7765,7 @@
     </row>
     <row r="185" spans="1:7">
       <c r="A185" s="3" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B185" s="4"/>
       <c r="C185" s="4"/>
@@ -7565,7 +7776,7 @@
     </row>
     <row r="186" spans="1:7">
       <c r="A186" s="3" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B186" s="4"/>
       <c r="C186" s="4"/>
@@ -7576,7 +7787,7 @@
     </row>
     <row r="187" spans="1:7">
       <c r="A187" s="3" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B187" s="4"/>
       <c r="C187" s="4"/>
@@ -7587,7 +7798,7 @@
     </row>
     <row r="188" spans="1:7">
       <c r="A188" s="3" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B188" s="4"/>
       <c r="C188" s="4"/>
@@ -7598,7 +7809,7 @@
     </row>
     <row r="189" spans="1:7">
       <c r="A189" s="3" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B189" s="4"/>
       <c r="C189" s="4"/>
@@ -7609,7 +7820,7 @@
     </row>
     <row r="190" spans="1:7">
       <c r="A190" s="3" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B190" s="4"/>
       <c r="C190" s="4"/>
@@ -7620,7 +7831,7 @@
     </row>
     <row r="191" spans="1:7">
       <c r="A191" s="3" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B191" s="4"/>
       <c r="C191" s="4"/>
@@ -7631,7 +7842,7 @@
     </row>
     <row r="192" spans="1:7">
       <c r="A192" s="3" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B192" s="4"/>
       <c r="C192" s="4"/>
@@ -7642,7 +7853,7 @@
     </row>
     <row r="193" spans="1:7">
       <c r="A193" s="3" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B193" s="4"/>
       <c r="C193" s="4"/>
@@ -7653,7 +7864,7 @@
     </row>
     <row r="194" spans="1:7">
       <c r="A194" s="3" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B194" s="4"/>
       <c r="C194" s="4"/>
@@ -7664,7 +7875,7 @@
     </row>
     <row r="195" spans="1:7">
       <c r="A195" s="3" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B195" s="4"/>
       <c r="C195" s="4"/>
@@ -7675,7 +7886,7 @@
     </row>
     <row r="196" spans="1:7">
       <c r="A196" s="3" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B196" s="4"/>
       <c r="C196" s="4"/>
@@ -7686,7 +7897,7 @@
     </row>
     <row r="197" spans="1:7">
       <c r="A197" s="3" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B197" s="4"/>
       <c r="C197" s="4"/>
@@ -7697,7 +7908,7 @@
     </row>
     <row r="198" spans="1:7">
       <c r="A198" s="3" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B198" s="4"/>
       <c r="C198" s="4"/>
@@ -7708,7 +7919,7 @@
     </row>
     <row r="199" spans="1:7">
       <c r="A199" s="3" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B199" s="4"/>
       <c r="C199" s="4"/>
@@ -7719,7 +7930,7 @@
     </row>
     <row r="200" spans="1:7">
       <c r="A200" s="3" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B200" s="4"/>
       <c r="C200" s="4"/>
@@ -7730,7 +7941,7 @@
     </row>
     <row r="201" spans="1:7">
       <c r="A201" s="3" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B201" s="4"/>
       <c r="C201" s="4"/>
@@ -7741,7 +7952,7 @@
     </row>
     <row r="202" spans="1:7">
       <c r="A202" s="3" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B202" s="4"/>
       <c r="C202" s="4"/>
@@ -7752,7 +7963,7 @@
     </row>
     <row r="203" spans="1:7">
       <c r="A203" s="3" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B203" s="4"/>
       <c r="C203" s="4"/>
@@ -7763,7 +7974,7 @@
     </row>
     <row r="204" spans="1:7">
       <c r="A204" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B204" s="4"/>
       <c r="C204" s="4"/>
@@ -7774,7 +7985,7 @@
     </row>
     <row r="205" spans="1:7">
       <c r="A205" s="3" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B205" s="4"/>
       <c r="C205" s="4"/>
@@ -7785,7 +7996,7 @@
     </row>
     <row r="206" spans="1:7">
       <c r="A206" s="3" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B206" s="4"/>
       <c r="C206" s="4"/>
@@ -7796,7 +8007,7 @@
     </row>
     <row r="207" spans="1:7">
       <c r="A207" s="3" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B207" s="4"/>
       <c r="C207" s="4"/>
@@ -7807,7 +8018,7 @@
     </row>
     <row r="208" spans="1:7">
       <c r="A208" s="3" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B208" s="4"/>
       <c r="C208" s="4"/>
@@ -7818,7 +8029,7 @@
     </row>
     <row r="209" spans="1:7">
       <c r="A209" s="3" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B209" s="4"/>
       <c r="C209" s="4"/>
@@ -7829,7 +8040,7 @@
     </row>
     <row r="210" spans="1:7">
       <c r="A210" s="3" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B210" s="4"/>
       <c r="C210" s="4"/>
@@ -7840,7 +8051,7 @@
     </row>
     <row r="211" spans="1:7">
       <c r="A211" s="3" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B211" s="4"/>
       <c r="C211" s="4"/>
@@ -7851,7 +8062,7 @@
     </row>
     <row r="212" spans="1:7">
       <c r="A212" s="3" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B212" s="4"/>
       <c r="C212" s="4"/>
@@ -7862,7 +8073,7 @@
     </row>
     <row r="213" spans="1:7">
       <c r="A213" s="3" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B213" s="4"/>
       <c r="C213" s="4"/>
@@ -7873,7 +8084,7 @@
     </row>
     <row r="214" spans="1:7">
       <c r="A214" s="3" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B214" s="4"/>
       <c r="C214" s="4"/>
@@ -7884,7 +8095,7 @@
     </row>
     <row r="215" spans="1:7">
       <c r="A215" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B215" s="4"/>
       <c r="C215" s="4"/>
@@ -7895,7 +8106,7 @@
     </row>
     <row r="216" spans="1:7">
       <c r="A216" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B216" s="4"/>
       <c r="C216" s="4"/>
@@ -7906,7 +8117,7 @@
     </row>
     <row r="217" spans="1:7">
       <c r="A217" s="3" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B217" s="4"/>
       <c r="C217" s="4"/>
@@ -7917,7 +8128,7 @@
     </row>
     <row r="218" spans="1:7">
       <c r="A218" s="3" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B218" s="4"/>
       <c r="C218" s="4"/>
@@ -7928,7 +8139,7 @@
     </row>
     <row r="219" spans="1:7">
       <c r="A219" s="3" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B219" s="4"/>
       <c r="C219" s="4"/>
@@ -7939,7 +8150,7 @@
     </row>
     <row r="220" spans="1:7">
       <c r="A220" s="3" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B220" s="4"/>
       <c r="C220" s="4"/>
@@ -7950,7 +8161,7 @@
     </row>
     <row r="221" spans="1:7">
       <c r="A221" s="3" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B221" s="4"/>
       <c r="C221" s="4"/>
@@ -7961,7 +8172,7 @@
     </row>
     <row r="222" spans="1:7">
       <c r="A222" s="3" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B222" s="4"/>
       <c r="C222" s="4"/>
@@ -7972,7 +8183,7 @@
     </row>
     <row r="223" spans="1:7">
       <c r="A223" s="3" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B223" s="4"/>
       <c r="C223" s="4"/>
@@ -7983,7 +8194,7 @@
     </row>
     <row r="224" spans="1:7">
       <c r="A224" s="3" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B224" s="4"/>
       <c r="C224" s="4"/>
@@ -7994,7 +8205,7 @@
     </row>
     <row r="225" spans="1:7">
       <c r="A225" s="3" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B225" s="4"/>
       <c r="C225" s="4"/>
@@ -8005,7 +8216,7 @@
     </row>
     <row r="226" spans="1:7">
       <c r="A226" s="3" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B226" s="4"/>
       <c r="C226" s="4"/>
@@ -8016,7 +8227,7 @@
     </row>
     <row r="227" spans="1:7">
       <c r="A227" s="3" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B227" s="4"/>
       <c r="C227" s="4"/>
@@ -8027,7 +8238,7 @@
     </row>
     <row r="228" spans="1:7">
       <c r="A228" s="3" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B228" s="4"/>
       <c r="C228" s="4"/>
@@ -8038,7 +8249,7 @@
     </row>
     <row r="229" spans="1:7">
       <c r="A229" s="3" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B229" s="4"/>
       <c r="C229" s="4"/>
@@ -8049,7 +8260,7 @@
     </row>
     <row r="230" spans="1:7">
       <c r="A230" s="3" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B230" s="4"/>
       <c r="C230" s="4"/>
@@ -8060,7 +8271,7 @@
     </row>
     <row r="231" spans="1:7">
       <c r="A231" s="3" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B231" s="4"/>
       <c r="C231" s="4"/>
@@ -8071,7 +8282,7 @@
     </row>
     <row r="232" spans="1:7">
       <c r="A232" s="3" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B232" s="4"/>
       <c r="C232" s="4"/>
@@ -8082,7 +8293,7 @@
     </row>
     <row r="233" spans="1:7">
       <c r="A233" s="3" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B233" s="4"/>
       <c r="C233" s="4"/>
@@ -8093,7 +8304,7 @@
     </row>
     <row r="234" spans="1:7">
       <c r="A234" s="3" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B234" s="4"/>
       <c r="C234" s="4"/>
@@ -8104,7 +8315,7 @@
     </row>
     <row r="235" spans="1:7">
       <c r="A235" s="3" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B235" s="4"/>
       <c r="C235" s="4"/>
@@ -8115,7 +8326,7 @@
     </row>
     <row r="236" spans="1:7">
       <c r="A236" s="3" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B236" s="4"/>
       <c r="C236" s="4"/>
@@ -8126,7 +8337,7 @@
     </row>
     <row r="237" spans="1:7">
       <c r="A237" s="3" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B237" s="4"/>
       <c r="C237" s="4"/>
@@ -8137,7 +8348,7 @@
     </row>
     <row r="238" spans="1:7">
       <c r="A238" s="3" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B238" s="4"/>
       <c r="C238" s="4"/>
@@ -8148,7 +8359,7 @@
     </row>
     <row r="239" spans="1:7">
       <c r="A239" s="3" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B239" s="4"/>
       <c r="C239" s="4"/>
@@ -8159,7 +8370,7 @@
     </row>
     <row r="240" spans="1:7">
       <c r="A240" s="3" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B240" s="4"/>
       <c r="C240" s="4"/>
@@ -8170,7 +8381,7 @@
     </row>
     <row r="241" spans="1:7">
       <c r="A241" s="3" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B241" s="4"/>
       <c r="C241" s="4"/>
@@ -8181,7 +8392,7 @@
     </row>
     <row r="242" spans="1:7">
       <c r="A242" s="3" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B242" s="4"/>
       <c r="C242" s="4"/>
@@ -8192,7 +8403,7 @@
     </row>
     <row r="243" spans="1:7">
       <c r="A243" s="3" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B243" s="4"/>
       <c r="C243" s="4"/>
@@ -8203,7 +8414,7 @@
     </row>
     <row r="244" spans="1:7">
       <c r="A244" s="3" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B244" s="4"/>
       <c r="C244" s="4"/>
@@ -8214,7 +8425,7 @@
     </row>
     <row r="245" spans="1:7">
       <c r="A245" s="3" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B245" s="4"/>
       <c r="C245" s="4"/>
@@ -8225,7 +8436,7 @@
     </row>
     <row r="246" spans="1:7">
       <c r="A246" s="3" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B246" s="4"/>
       <c r="C246" s="4"/>
@@ -8236,7 +8447,7 @@
     </row>
     <row r="247" spans="1:7">
       <c r="A247" s="3" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B247" s="4"/>
       <c r="C247" s="4"/>
@@ -8247,7 +8458,7 @@
     </row>
     <row r="248" spans="1:7">
       <c r="A248" s="3" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B248" s="4"/>
       <c r="C248" s="4"/>
@@ -8258,7 +8469,7 @@
     </row>
     <row r="249" spans="1:7">
       <c r="A249" s="3" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B249" s="4"/>
       <c r="C249" s="4"/>
@@ -8269,7 +8480,7 @@
     </row>
     <row r="250" spans="1:7">
       <c r="A250" s="3" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B250" s="4"/>
       <c r="C250" s="4"/>
@@ -8280,7 +8491,7 @@
     </row>
     <row r="251" spans="1:7">
       <c r="A251" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B251" s="4"/>
       <c r="C251" s="4"/>
@@ -8291,7 +8502,7 @@
     </row>
     <row r="252" spans="1:7">
       <c r="A252" s="3" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B252" s="4"/>
       <c r="C252" s="4"/>
@@ -8302,7 +8513,7 @@
     </row>
     <row r="253" spans="1:7">
       <c r="A253" s="3" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B253" s="4"/>
       <c r="C253" s="4"/>
@@ -8313,7 +8524,7 @@
     </row>
     <row r="254" spans="1:7">
       <c r="A254" s="3" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B254" s="4"/>
       <c r="C254" s="4"/>
@@ -8324,7 +8535,7 @@
     </row>
     <row r="255" spans="1:7">
       <c r="A255" s="3" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B255" s="4"/>
       <c r="C255" s="4"/>
@@ -8335,7 +8546,7 @@
     </row>
     <row r="256" spans="1:7">
       <c r="A256" s="3" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B256" s="4"/>
       <c r="C256" s="4"/>
@@ -8346,7 +8557,7 @@
     </row>
     <row r="257" spans="1:7">
       <c r="A257" s="3" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B257" s="4"/>
       <c r="C257" s="4"/>
@@ -8357,7 +8568,7 @@
     </row>
     <row r="258" spans="1:7">
       <c r="A258" s="3" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B258" s="4"/>
       <c r="C258" s="4"/>
@@ -8368,7 +8579,7 @@
     </row>
     <row r="259" spans="1:7">
       <c r="A259" s="3" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B259" s="4"/>
       <c r="C259" s="4"/>
@@ -8379,7 +8590,7 @@
     </row>
     <row r="260" spans="1:7">
       <c r="A260" s="3" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B260" s="4"/>
       <c r="C260" s="4"/>
@@ -8390,7 +8601,7 @@
     </row>
     <row r="261" spans="1:7">
       <c r="A261" s="3" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B261" s="4"/>
       <c r="C261" s="4"/>
@@ -8401,7 +8612,7 @@
     </row>
     <row r="262" spans="1:7">
       <c r="A262" s="3" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B262" s="4"/>
       <c r="C262" s="4"/>
@@ -8412,7 +8623,7 @@
     </row>
     <row r="263" spans="1:7">
       <c r="A263" s="3" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B263" s="4"/>
       <c r="C263" s="4"/>
@@ -8423,7 +8634,7 @@
     </row>
     <row r="264" spans="1:7">
       <c r="A264" s="3" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B264" s="4"/>
       <c r="C264" s="4"/>
@@ -8434,7 +8645,7 @@
     </row>
     <row r="265" spans="1:7">
       <c r="A265" s="3" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B265" s="4"/>
       <c r="C265" s="4"/>
@@ -8445,7 +8656,7 @@
     </row>
     <row r="266" spans="1:7">
       <c r="A266" s="3" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B266" s="4"/>
       <c r="C266" s="4"/>
@@ -8456,7 +8667,7 @@
     </row>
     <row r="267" spans="1:7">
       <c r="A267" s="3" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B267" s="4"/>
       <c r="C267" s="4"/>
@@ -8467,7 +8678,7 @@
     </row>
     <row r="268" spans="1:7">
       <c r="A268" s="3" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B268" s="4"/>
       <c r="C268" s="4"/>
@@ -8478,7 +8689,7 @@
     </row>
     <row r="269" spans="1:7">
       <c r="A269" s="3" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B269" s="4"/>
       <c r="C269" s="4"/>
@@ -8489,7 +8700,7 @@
     </row>
     <row r="270" spans="1:7">
       <c r="A270" s="3" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B270" s="4"/>
       <c r="C270" s="4"/>
@@ -8500,7 +8711,7 @@
     </row>
     <row r="271" spans="1:7">
       <c r="A271" s="3" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B271" s="4"/>
       <c r="C271" s="4"/>
@@ -8511,7 +8722,7 @@
     </row>
     <row r="272" spans="1:7">
       <c r="A272" s="3" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B272" s="4"/>
       <c r="C272" s="4"/>
@@ -8522,7 +8733,7 @@
     </row>
     <row r="273" spans="1:7">
       <c r="A273" s="3" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B273" s="4"/>
       <c r="C273" s="4"/>
@@ -8533,7 +8744,7 @@
     </row>
     <row r="274" spans="1:7">
       <c r="A274" s="3" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B274" s="4"/>
       <c r="C274" s="4"/>
@@ -8544,7 +8755,7 @@
     </row>
     <row r="275" spans="1:7">
       <c r="A275" s="3" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B275" s="4"/>
       <c r="C275" s="4"/>
@@ -8555,7 +8766,7 @@
     </row>
     <row r="276" spans="1:7">
       <c r="A276" s="3" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B276" s="4"/>
       <c r="C276" s="4"/>
@@ -8566,7 +8777,7 @@
     </row>
     <row r="277" spans="1:7">
       <c r="A277" s="3" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B277" s="4"/>
       <c r="C277" s="4"/>
@@ -8577,7 +8788,7 @@
     </row>
     <row r="278" spans="1:7">
       <c r="A278" s="3" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B278" s="4"/>
       <c r="C278" s="4"/>
@@ -8588,7 +8799,7 @@
     </row>
     <row r="279" spans="1:7">
       <c r="A279" s="3" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B279" s="4"/>
       <c r="C279" s="4"/>
@@ -8599,7 +8810,7 @@
     </row>
     <row r="280" spans="1:7">
       <c r="A280" s="3" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B280" s="4"/>
       <c r="C280" s="4"/>
@@ -8610,7 +8821,7 @@
     </row>
     <row r="281" spans="1:7">
       <c r="A281" s="3" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B281" s="4"/>
       <c r="C281" s="4"/>
@@ -8621,7 +8832,7 @@
     </row>
     <row r="282" spans="1:7">
       <c r="A282" s="3" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B282" s="4"/>
       <c r="C282" s="4"/>
@@ -8632,7 +8843,7 @@
     </row>
     <row r="283" spans="1:7">
       <c r="A283" s="3" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B283" s="4"/>
       <c r="C283" s="4"/>
@@ -8643,7 +8854,7 @@
     </row>
     <row r="284" spans="1:7">
       <c r="A284" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B284" s="4"/>
       <c r="C284" s="4"/>
@@ -8654,7 +8865,7 @@
     </row>
     <row r="285" spans="1:7">
       <c r="A285" s="3" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B285" s="4"/>
       <c r="C285" s="4"/>
@@ -8665,7 +8876,7 @@
     </row>
     <row r="286" spans="1:7">
       <c r="A286" s="3" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B286" s="4"/>
       <c r="C286" s="4"/>
@@ -8676,7 +8887,7 @@
     </row>
     <row r="287" spans="1:7">
       <c r="A287" s="3" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B287" s="4"/>
       <c r="C287" s="4"/>
@@ -8687,7 +8898,7 @@
     </row>
     <row r="288" spans="1:7">
       <c r="A288" s="3" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B288" s="4"/>
       <c r="C288" s="4"/>
@@ -8698,7 +8909,7 @@
     </row>
     <row r="289" spans="1:7">
       <c r="A289" s="3" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B289" s="4"/>
       <c r="C289" s="4"/>
@@ -8709,7 +8920,7 @@
     </row>
     <row r="290" spans="1:7">
       <c r="A290" s="3" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B290" s="4"/>
       <c r="C290" s="4"/>
@@ -8720,7 +8931,7 @@
     </row>
     <row r="291" spans="1:7">
       <c r="A291" s="3" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B291" s="4"/>
       <c r="C291" s="4"/>
@@ -8731,7 +8942,7 @@
     </row>
     <row r="292" spans="1:7">
       <c r="A292" s="3" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B292" s="4"/>
       <c r="C292" s="4"/>
@@ -8742,7 +8953,7 @@
     </row>
     <row r="293" spans="1:7">
       <c r="A293" s="3" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B293" s="4"/>
       <c r="C293" s="4"/>
@@ -8753,7 +8964,7 @@
     </row>
     <row r="294" spans="1:7">
       <c r="A294" s="3" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B294" s="4"/>
       <c r="C294" s="4"/>
@@ -8764,7 +8975,7 @@
     </row>
     <row r="295" spans="1:7">
       <c r="A295" s="3" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B295" s="4"/>
       <c r="C295" s="4"/>
@@ -8775,7 +8986,7 @@
     </row>
     <row r="296" spans="1:7">
       <c r="A296" s="3" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B296" s="4"/>
       <c r="C296" s="4"/>
@@ -8786,7 +8997,7 @@
     </row>
     <row r="297" spans="1:7">
       <c r="A297" s="3" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B297" s="4"/>
       <c r="C297" s="4"/>
@@ -8797,7 +9008,7 @@
     </row>
     <row r="298" spans="1:7">
       <c r="A298" s="3" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B298" s="4"/>
       <c r="C298" s="4"/>
@@ -8808,7 +9019,7 @@
     </row>
     <row r="299" spans="1:7">
       <c r="A299" s="3" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B299" s="4"/>
       <c r="C299" s="4"/>
@@ -8819,7 +9030,7 @@
     </row>
     <row r="300" spans="1:7">
       <c r="A300" s="3" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B300" s="4"/>
       <c r="C300" s="4"/>
@@ -8830,7 +9041,7 @@
     </row>
     <row r="301" spans="1:7">
       <c r="A301" s="3" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B301" s="4"/>
       <c r="C301" s="4"/>
@@ -8841,7 +9052,7 @@
     </row>
     <row r="302" spans="1:7">
       <c r="A302" s="3" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B302" s="4"/>
       <c r="C302" s="4"/>
@@ -8852,7 +9063,7 @@
     </row>
     <row r="303" spans="1:7">
       <c r="A303" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B303" s="4"/>
       <c r="C303" s="4"/>
@@ -8863,7 +9074,7 @@
     </row>
     <row r="304" spans="1:7">
       <c r="A304" s="3" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B304" s="4"/>
       <c r="C304" s="4"/>
@@ -8874,7 +9085,7 @@
     </row>
     <row r="305" spans="1:7">
       <c r="A305" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B305" s="4"/>
       <c r="C305" s="4"/>
@@ -8885,7 +9096,7 @@
     </row>
     <row r="306" spans="1:7">
       <c r="A306" s="3" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B306" s="4"/>
       <c r="C306" s="4"/>
@@ -8896,7 +9107,7 @@
     </row>
     <row r="307" spans="1:7">
       <c r="A307" s="3" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B307" s="4"/>
       <c r="C307" s="4"/>
@@ -8907,7 +9118,7 @@
     </row>
     <row r="308" spans="1:7">
       <c r="A308" s="3" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B308" s="4"/>
       <c r="C308" s="4"/>
@@ -8918,7 +9129,7 @@
     </row>
     <row r="309" spans="1:7">
       <c r="A309" s="3" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B309" s="4"/>
       <c r="C309" s="4"/>
@@ -8929,7 +9140,7 @@
     </row>
     <row r="310" spans="1:7">
       <c r="A310" s="3" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B310" s="4"/>
       <c r="C310" s="4"/>
@@ -8940,7 +9151,7 @@
     </row>
     <row r="311" spans="1:7">
       <c r="A311" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B311" s="4"/>
       <c r="C311" s="4"/>
@@ -8951,7 +9162,7 @@
     </row>
     <row r="312" spans="1:7">
       <c r="A312" s="3" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B312" s="4"/>
       <c r="C312" s="4"/>
@@ -8962,7 +9173,7 @@
     </row>
     <row r="313" spans="1:7">
       <c r="A313" s="3" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B313" s="4"/>
       <c r="C313" s="4"/>
@@ -8973,7 +9184,7 @@
     </row>
     <row r="314" spans="1:7">
       <c r="A314" s="3" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B314" s="4"/>
       <c r="C314" s="4"/>
@@ -8984,7 +9195,7 @@
     </row>
     <row r="315" spans="1:7">
       <c r="A315" s="3" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B315" s="4"/>
       <c r="C315" s="4"/>
@@ -8995,7 +9206,7 @@
     </row>
     <row r="316" spans="1:7">
       <c r="A316" s="3" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B316" s="4"/>
       <c r="C316" s="4"/>
@@ -9006,7 +9217,7 @@
     </row>
     <row r="317" spans="1:7">
       <c r="A317" s="3" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B317" s="4"/>
       <c r="C317" s="4"/>
@@ -9017,7 +9228,7 @@
     </row>
     <row r="318" spans="1:7">
       <c r="A318" s="3" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B318" s="4"/>
       <c r="C318" s="4"/>
@@ -9028,7 +9239,7 @@
     </row>
     <row r="319" spans="1:7">
       <c r="A319" s="3" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B319" s="4"/>
       <c r="C319" s="4"/>
@@ -9039,7 +9250,7 @@
     </row>
     <row r="320" spans="1:7">
       <c r="A320" s="3" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B320" s="4"/>
       <c r="C320" s="4"/>
@@ -9050,7 +9261,7 @@
     </row>
     <row r="321" spans="1:7">
       <c r="A321" s="3" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B321" s="4"/>
       <c r="C321" s="4"/>
@@ -9061,7 +9272,7 @@
     </row>
     <row r="322" spans="1:7">
       <c r="A322" s="3" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B322" s="4"/>
       <c r="C322" s="4"/>
@@ -9072,7 +9283,7 @@
     </row>
     <row r="323" spans="1:7">
       <c r="A323" s="3" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B323" s="4"/>
       <c r="C323" s="4"/>
@@ -9083,7 +9294,7 @@
     </row>
     <row r="324" spans="1:7">
       <c r="A324" s="3" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B324" s="4"/>
       <c r="C324" s="4"/>
@@ -9094,7 +9305,7 @@
     </row>
     <row r="325" spans="1:7">
       <c r="A325" s="3" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B325" s="4"/>
       <c r="C325" s="4"/>
@@ -9105,7 +9316,7 @@
     </row>
     <row r="326" spans="1:7">
       <c r="A326" s="3" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B326" s="4"/>
       <c r="C326" s="4"/>
@@ -9116,7 +9327,7 @@
     </row>
     <row r="327" spans="1:7">
       <c r="A327" s="3" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B327" s="4"/>
       <c r="C327" s="4"/>
@@ -9127,7 +9338,7 @@
     </row>
     <row r="328" spans="1:7">
       <c r="A328" s="3" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B328" s="4"/>
       <c r="C328" s="4"/>
@@ -9138,7 +9349,7 @@
     </row>
     <row r="329" spans="1:7">
       <c r="A329" s="3" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B329" s="4"/>
       <c r="C329" s="4"/>
@@ -9149,7 +9360,7 @@
     </row>
     <row r="330" spans="1:7">
       <c r="A330" s="3" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B330" s="4"/>
       <c r="C330" s="4"/>
@@ -9160,7 +9371,7 @@
     </row>
     <row r="331" spans="1:7">
       <c r="A331" s="3" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B331" s="4"/>
       <c r="C331" s="4"/>
@@ -9171,7 +9382,7 @@
     </row>
     <row r="332" spans="1:7">
       <c r="A332" s="3" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B332" s="4"/>
       <c r="C332" s="4"/>
@@ -9182,7 +9393,7 @@
     </row>
     <row r="333" spans="1:7">
       <c r="A333" s="3" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B333" s="4"/>
       <c r="C333" s="4"/>
@@ -9193,7 +9404,7 @@
     </row>
     <row r="334" spans="1:7">
       <c r="A334" s="3" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B334" s="4"/>
       <c r="C334" s="4"/>
@@ -9204,7 +9415,7 @@
     </row>
     <row r="335" spans="1:7">
       <c r="A335" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B335" s="4"/>
       <c r="C335" s="4"/>
@@ -9215,7 +9426,7 @@
     </row>
     <row r="336" spans="1:7">
       <c r="A336" s="3" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B336" s="4"/>
       <c r="C336" s="4"/>
@@ -9226,7 +9437,7 @@
     </row>
     <row r="337" spans="1:7">
       <c r="A337" s="3" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B337" s="4"/>
       <c r="C337" s="4"/>
@@ -9237,7 +9448,7 @@
     </row>
     <row r="338" spans="1:7">
       <c r="A338" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B338" s="4"/>
       <c r="C338" s="4"/>
@@ -9248,7 +9459,7 @@
     </row>
     <row r="339" spans="1:7">
       <c r="A339" s="3" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B339" s="4"/>
       <c r="C339" s="4"/>
@@ -9259,7 +9470,7 @@
     </row>
     <row r="340" spans="1:7">
       <c r="A340" s="3" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B340" s="4"/>
       <c r="C340" s="4"/>
@@ -9270,7 +9481,7 @@
     </row>
     <row r="341" spans="1:7">
       <c r="A341" s="3" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B341" s="4"/>
       <c r="C341" s="4"/>
@@ -9281,7 +9492,7 @@
     </row>
     <row r="342" spans="1:7">
       <c r="A342" s="3" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B342" s="4"/>
       <c r="C342" s="4"/>
@@ -9294,7 +9505,7 @@
   <autoFilter ref="A2:H342" xr:uid="{833B9C12-88F9-F440-902B-BDAD178A24F6}"/>
   <phoneticPr fontId="1"/>
   <conditionalFormatting sqref="H62:H63 A3:G342">
-    <cfRule type="expression" dxfId="3" priority="2">
+    <cfRule type="expression" dxfId="0" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>

--- a/docs/確認事項リスト.xlsx
+++ b/docs/確認事項リスト.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70E9C054-A9F0-3149-BAAF-B33E43360C4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95E67417-52A3-EC4E-8F29-E661CF562438}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{E987AAC5-D7CB-4143-BFFD-E0642F54BEB6}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1139" uniqueCount="624">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1242" uniqueCount="682">
   <si>
     <t>質問</t>
     <rPh sb="0" eb="2">
@@ -2455,10 +2455,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>Q-65にて回答済み</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>ISBNは13桁固定で一意性チェック(自信を除外)も入れる想定ですが、桁数チェックは必要ですか？
 →Q-65と同様のエラーメッセージでよろしいですか？</t>
     <rPh sb="19" eb="21">
@@ -3475,16 +3471,7 @@
       <t>ゼンジテゥ</t>
     </rPh>
     <rPh sb="100" eb="101">
-      <t>_x0000_</t>
-    </rPh>
-    <rPh sb="100" eb="101">
-      <t xml:space="preserve">	</t>
-    </rPh>
-    <rPh sb="100" eb="101">
-      <t>_x0002_</t>
-    </rPh>
-    <rPh sb="100" eb="101">
-      <t/>
+      <t>_x0000_	_x0002_</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -3549,6 +3536,222 @@
     <rPh sb="24" eb="26">
       <t>ツウティ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>はい、デフォルト20件/ページで問題ありません。（リクエストパラメータ per_page で変更可能、最大100件まで）</t>
+  </si>
+  <si>
+    <t>はい、一覧レスポンス（BookResource）には id, title, author, isbn, published_date, description, image_url, genres, average_rating, review_count を含めてください（reviews詳細配列は一覧では除外）。meta情報（current_page, last_page, per_page, total）も含まれます。</t>
+  </si>
+  <si>
+    <t>404エラー時は { "error": "書籍が見つかりませんでした。" } のJSONを返してください。</t>
+  </si>
+  <si>
+    <t>はい、詳細レスポンス（BookResource）には id, title, author, isbn, published_date, description, image_url, genres, average_rating, review_count, reviews（投稿者名・評価・コメント・投稿日時を含む配列）を含めて返却してください。</t>
+  </si>
+  <si>
+    <t>登録成功時は 201 Created とともに、作成された書籍のリソース情報（id, title, author, isbn, published_date, description, image_url, genres, average_rating, review_count）を { "data": { ... } } の形式で返却してください。</t>
+  </si>
+  <si>
+    <t>応用機能でSanctum認証を導入した際、未認証時は 401 Unauthorized とともに { "message": "Unauthenticated." } を返してください。</t>
+  </si>
+  <si>
+    <t>はい、BookPolicy@update により自身が登録した書籍のみ更新可能とし、他ユーザーの書籍更新試行時は 403 Forbidden を返してください。</t>
+  </si>
+  <si>
+    <t>更新成功時は 200 OK とともに、更新後の書籍のリソース情報（id, title, author, isbn, published_date, description, image_url, genres, average_rating, review_count）を { "data": { ... } } の形式で返却してください。</t>
+  </si>
+  <si>
+    <t>はい、未認証時は 401 Unauthorized とともに { "message": "Unauthenticated." } を返してください。</t>
+  </si>
+  <si>
+    <t>はい、他ユーザーの書籍更新試行時は 403 Forbidden とともに { "error": "この操作を実行する権限がありません。" } を返してください。</t>
+  </si>
+  <si>
+    <t>はい、BookPolicy@delete により自身が登録した書籍のみ削除可能とし、他ユーザーの書籍削除試行時は 403 Forbidden を返してください。</t>
+  </si>
+  <si>
+    <t>はい、削除成功時は 204 No Content（レスポンスボディなし）を返却してください。</t>
+  </si>
+  <si>
+    <t>はい、他ユーザーの書籍削除試行時は 403 Forbidden とともに { "error": "この操作を実行する権限がありません。" } を返してください。</t>
+  </si>
+  <si>
+    <t>いいえ。日次バッチ処理（リマインダー通知・Auto-expire）の実行時刻は【毎日 20:00】に設定してください。Console Kernel の schedule() にて $schedule-&gt;command('reading-plans:run-daily')-&gt;daily()-&gt;at('20:00') と設定します。</t>
+  </si>
+  <si>
+    <t>いいえ、発報タイミングは【期日 3日前 / 当日 / 3日後（再エンゲージメント）】の3タイミングです。「期限前日」ではなく「期日3日後（Expired計画への再アプローチ）」が含まれます。通知タイトル・本文には各タイミングに応じた文言を設定してください。</t>
+  </si>
+  <si>
+    <t>はい、その制約で問題ありません。読書計画のステータスは ReadingPlanStatus PHP Enum（in_progress / completed / expired）で管理し、一覧画面のフィルタドロップダウンでもこれらを選択可能としてください。</t>
+  </si>
+  <si>
+    <t>はい、問題ありません。期日（target_date）を経過した in_progress 状態の計画は、毎日20:00に実行される日次バッチ処理（Auto-expire）によって自動的に expired へ更新してください。</t>
+  </si>
+  <si>
+    <t>はい、問題ありません。ただし読書計画自体については、ステータスが completed（完了済み）の計画は編集不可（403 Forbiddenを返却）となりますのでご注意ください。なお、書籍自体を削除した場合は、関連する読書計画および通知データも削除（CASCADE/Transaction）されます。</t>
+  </si>
+  <si>
+    <t>基本的に問題ありません。一括 Expired 化および期日3日前・当日のリマインダー通知は in_progress 状態の計画が対象です。ただし、期日3日後の再エンゲージメント通知のみ expired 状態の計画が対象となります。</t>
+  </si>
+  <si>
+    <t>はい、問題ありません。期日経過から3日後の expired 状態の計画に対して、再エンゲージメント通知を発火してください。</t>
+  </si>
+  <si>
+    <t>はい、問題ありません。キーワード検索は任意・最大255文字とし、バリデーションエラー時は「キーワードは255文字以内で入力してください。」と表示してください。なお、クエリパラメータが不正な場合はデフォルト検索条件（または全件表示）で一覧画面を表示してください。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>はい、問題ありません。ジャンル絞り込みは任意とし、exists:genres,id によるバリデーションを行ってください。エラー時は不正なパラメータを無視し、全件またはデフォルト条件で一覧を表示してください。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>デフォルトの表示件数は10件/ページとしてください。（※公開APIではデフォルト20件/ページ、最大100件となります）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>はい、ソート順は latest（登録日新しい順、デフォルト）、oldest（登録日古い順）、title（タイトル昇順）、rating（平均評価降順）から選択可能とし、不正なパラメータの場合はデフォルト（latest）でソートしてください。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>APIでも keyword（キーワード検索）、genre_id（ジャンル絞り込み）、page/per_page（ページネーション）等のリクエストパラメータに対応してください。ソート指定がない場合はデフォルトで最新順（latest()）で返却します。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>はい、評価は必須（1〜5の整数）です。エラーメッセージは「評価は必須です。」「評価は1〜5の整数で入力してください。」と表示してください。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>レビューのコメント（本文）は必須・最大1000文字です。エラーメッセージは「コメントは必須です。」「コメントは1000文字以内で入力してください。」と表示してください。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>はい、タイトルは必須・最大255文字です。エラーメッセージは「タイトルは必須です。」「タイトルは255文字以内で入力してください。」と表示してください。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>はい、著者名は必須・最大255文字です。エラーメッセージは「著者名は必須です。」「著者名は255文字以内で入力してください。」と表示してください。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>基本機能フェーズではISBNは必須（13桁固定・一意）とし、「ISBNは必須です。」と表示してください。（※応用機能フェーズではnullable/任意入力に変更されます。）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Q-65にて回答済みですが、size:13（13桁固定）および unique:books,isbn による一意性チェックが必要です。「ISBNは13桁で入力してください。」「そのISBNは既に使用されています。」と表示してください。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>はい、Q-65/Q-66と同様にsize:13による13桁チェックおよび Rule::unique('books')-&gt;ignore($this-&gt;book) による一意性チェック（自身除外）が必要です。エラーメッセージも同様です。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>基本機能フェーズでは出版日は必須・日付形式（date）です。「出版日は必須です。」「出版日は有効な日付形式で入力してください。」と表示してください。（※応用機能フェーズではnullableに変更されます。）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>説明（description）は任意（nullable）・文字列（string）です。文字数上限は特に255文字に制限せず、テキスト形式（text型）として入力を許可してください。「説明は文字列で入力してください。」と表示してください。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>はい、画像URLは任意（nullable）・URL形式・最大255文字です。エラーメッセージは「画像URLは有効なURL形式で入力してください。」「画像URLは255文字以内で入力してください。」と表示してください。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ジャンル選択は必須（1つ以上選択・配列形式）です。エラーメッセージは「ジャンルは1つ以上選択してください。」「選択されたジャンルは存在しません。」と表示してください。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>はい、ジャンル名は必須・最大255文字・一意（unique:genres,name）です。エラーメッセージは「ジャンル名は必須です。」「ジャンル名は255文字以内で入力してください。」「そのジャンル名は既に使用されています。」と表示してください。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>はい、ジャンル編集時も必須・最大255文字・一意（自身除外: Rule::unique('genres')-&gt;ignore($this-&gt;genre)）とし、エラーメッセージは「ジャンル名は必須です。」「ジャンル名は255文字以内で入力してください。」「そのジャンル名は既に使用されています。」と表示してください。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>読書計画の状態絞り込みは任意とし、ReadingPlanStatus Enumのケース（in_progress, completed, expired）で絞り込めるようにしてください。不正な値の場合はパラメータを無視して全件表示してください。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>はい、対象書籍（book_id）は必須・exists:books,id です。また、同一ユーザー×同一書籍でin_progress状態の計画が既に存在する場合は登録不可とするカスタムルールも実装してください。エラーメッセージは「書籍を選択してください。」「選択された書籍は存在しません。」「この書籍は既に進行中の読書計画が存在します。」と表示してください。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>はい、期日（target_date）は必須・日付形式かつ今日以降（after_or_equal:today）です。エラーメッセージは「期日は必須です。」「期日は有効な日付形式で入力してください。」「期日は今日以降の日付を指定してください。」と表示してください。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>はい、1ページあたりの件数（per_page）はデフォルト20件、最大100件（max:100）です。バリデーションエラー時は422とともに「1ページあたりの件数は100以下で指定してください。」等のエラーJSONを返してください。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>はい、keywordは任意（nullable）・最大255文字です。バリデーション違反時は422とともに「キーワードは255文字以内で入力してください。」と返してください。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>はい、genre_idは任意（nullable）・exists:genres,idです。バリデーション違反時は422とともに「選択されたジャンルは存在しません。」と返してください。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>はい、pageは任意（nullable）・最小値1（min:1）です。バリデーション違反時は422とともに「ページ番号は1以上で入力してください。」と返してください。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>はい、タイトルは必須・最大255文字です。422エラー時は「タイトルは必須です。」「タイトルは255文字以内で入力してください。」と返してください。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>はい、著者名は必須・最大255文字です。422エラー時は「著者名は必須です。」「著者名は255文字以内で入力してください。」と返してください。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>API版の書籍登録・更新APIではISBNは必須（13桁固定・一意）です。422エラー時は「ISBNは必須です。」と返してください。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>はい、size:13およびunique:books,isbnが必要です。422エラー時は「ISBNは13桁で入力してください。」「そのISBNは既に使用されています。」と返してください。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>はい、更新APIでも自身除外の一意性チェック（Rule::unique('books')-&gt;ignore($this-&gt;route('book'))）とsize:13が必要です。エラーメッセージも同様です。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>API版では出版日（published_date）は必須・日付形式（date）です。422エラー時は「出版日は必須です。」「出版日は有効な日付形式で入力してください。」と返してください。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>説明（description）は任意（nullable）・文字列（string）です。422エラー時は「説明は文字列で入力してください。」と返してください。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>はい、画像URLは任意（nullable）・URL形式・最大255文字です。422エラー時は「画像URLは有効なURL形式で入力してください。」「画像URLは255文字以内で入力してください。」と返してください。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ジャンル（genres）は必須（1つ以上選択・配列形式）・exists:genres,idです。422エラー時は「ジャンルは1つ以上選択してください。」「選択されたジャンルは存在しません。」と返してください。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>メールアドレスは必須・メール形式です。エラーメッセージは「メールアドレスを入力してください。」「メールアドレスはメール形式で入力してください。」と表示してください。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>はい、パスワードは必須です。エラーメッセージは「パスワードを入力してください。」と表示してください。なお、認証失敗時は「ログイン情報が登録されていません。」と表示してください。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>はい、お名前は必須・最大255文字です。エラーメッセージは「お名前を入力してください。」「お名前は255文字以内で入力してください。」と表示してください。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>はい、メールアドレスは必須・メール形式・最大255文字・一意（unique:users,email）です。エラーメッセージは「メールアドレスを入力してください。」「メールアドレスはメール形式で入力してください。」「そのメールアドレスは既に使用されています。」と表示してください。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>はい、パスワードは必須・8文字以上・確認用一致（confirmed）です。エラーメッセージは「パスワードを入力してください。」「パスワードは8文字以上で入力してください。」「パスワードと一致しません。」と表示してください。</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -3626,7 +3829,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor rgb="FF00B050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3702,14 +3905,14 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -4107,8 +4310,8 @@
       <c r="G2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="12" t="s">
-        <v>576</v>
+      <c r="H2" s="10" t="s">
+        <v>575</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42">
@@ -4133,8 +4336,8 @@
       <c r="G3" s="9" t="s">
         <v>503</v>
       </c>
-      <c r="H3" s="11" t="s">
-        <v>541</v>
+      <c r="H3" s="12" t="s">
+        <v>540</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="42">
@@ -4159,8 +4362,8 @@
       <c r="G4" s="9" t="s">
         <v>503</v>
       </c>
-      <c r="H4" s="11" t="s">
-        <v>541</v>
+      <c r="H4" s="12" t="s">
+        <v>540</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="42">
@@ -4185,8 +4388,8 @@
       <c r="G5" s="9" t="s">
         <v>503</v>
       </c>
-      <c r="H5" s="11" t="s">
-        <v>541</v>
+      <c r="H5" s="12" t="s">
+        <v>540</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="42">
@@ -4211,8 +4414,8 @@
       <c r="G6" s="9" t="s">
         <v>503</v>
       </c>
-      <c r="H6" s="11" t="s">
-        <v>541</v>
+      <c r="H6" s="12" t="s">
+        <v>540</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="63">
@@ -4237,8 +4440,8 @@
       <c r="G7" s="9" t="s">
         <v>503</v>
       </c>
-      <c r="H7" s="11" t="s">
-        <v>541</v>
+      <c r="H7" s="12" t="s">
+        <v>540</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="63">
@@ -4263,8 +4466,8 @@
       <c r="G8" s="9" t="s">
         <v>503</v>
       </c>
-      <c r="H8" s="11" t="s">
-        <v>541</v>
+      <c r="H8" s="12" t="s">
+        <v>540</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="63">
@@ -4284,13 +4487,13 @@
         <v>11</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="G9" s="9" t="s">
         <v>503</v>
       </c>
-      <c r="H9" s="11" t="s">
-        <v>541</v>
+      <c r="H9" s="12" t="s">
+        <v>540</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="42">
@@ -4310,13 +4513,13 @@
         <v>183</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="G10" s="9" t="s">
         <v>503</v>
       </c>
-      <c r="H10" s="11" t="s">
-        <v>541</v>
+      <c r="H10" s="12" t="s">
+        <v>540</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="63">
@@ -4336,13 +4539,13 @@
         <v>182</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="G11" s="9" t="s">
         <v>503</v>
       </c>
-      <c r="H11" s="11" t="s">
-        <v>541</v>
+      <c r="H11" s="12" t="s">
+        <v>540</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="42">
@@ -4362,13 +4565,13 @@
         <v>18</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="G12" s="9" t="s">
         <v>503</v>
       </c>
-      <c r="H12" s="11" t="s">
-        <v>541</v>
+      <c r="H12" s="12" t="s">
+        <v>540</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="63">
@@ -4388,13 +4591,13 @@
         <v>21</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="G13" s="9" t="s">
         <v>503</v>
       </c>
-      <c r="H13" s="11" t="s">
-        <v>541</v>
+      <c r="H13" s="12" t="s">
+        <v>540</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="42">
@@ -4414,13 +4617,13 @@
         <v>19</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="G14" s="9" t="s">
         <v>503</v>
       </c>
-      <c r="H14" s="11" t="s">
-        <v>541</v>
+      <c r="H14" s="12" t="s">
+        <v>540</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="63">
@@ -4440,13 +4643,13 @@
         <v>120</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="G15" s="9" t="s">
         <v>503</v>
       </c>
-      <c r="H15" s="11" t="s">
-        <v>541</v>
+      <c r="H15" s="12" t="s">
+        <v>540</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="42">
@@ -4471,8 +4674,8 @@
       <c r="G16" s="9" t="s">
         <v>503</v>
       </c>
-      <c r="H16" s="11" t="s">
-        <v>541</v>
+      <c r="H16" s="12" t="s">
+        <v>540</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="42">
@@ -4497,8 +4700,8 @@
       <c r="G17" s="9" t="s">
         <v>503</v>
       </c>
-      <c r="H17" s="11" t="s">
-        <v>541</v>
+      <c r="H17" s="12" t="s">
+        <v>540</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="63">
@@ -4523,8 +4726,8 @@
       <c r="G18" s="9" t="s">
         <v>503</v>
       </c>
-      <c r="H18" s="11" t="s">
-        <v>541</v>
+      <c r="H18" s="12" t="s">
+        <v>540</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="63">
@@ -4544,13 +4747,13 @@
         <v>127</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="G19" s="9" t="s">
         <v>503</v>
       </c>
-      <c r="H19" s="11" t="s">
-        <v>541</v>
+      <c r="H19" s="12" t="s">
+        <v>540</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="42">
@@ -4575,8 +4778,8 @@
       <c r="G20" s="9" t="s">
         <v>503</v>
       </c>
-      <c r="H20" s="11" t="s">
-        <v>541</v>
+      <c r="H20" s="12" t="s">
+        <v>540</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="63">
@@ -4596,13 +4799,13 @@
         <v>180</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="G21" s="9" t="s">
         <v>503</v>
       </c>
-      <c r="H21" s="11" t="s">
-        <v>541</v>
+      <c r="H21" s="12" t="s">
+        <v>540</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="42">
@@ -4627,8 +4830,8 @@
       <c r="G22" s="9" t="s">
         <v>503</v>
       </c>
-      <c r="H22" s="11" t="s">
-        <v>541</v>
+      <c r="H22" s="12" t="s">
+        <v>540</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="63">
@@ -4648,13 +4851,13 @@
         <v>181</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="G23" s="9" t="s">
         <v>503</v>
       </c>
-      <c r="H23" s="11" t="s">
-        <v>541</v>
+      <c r="H23" s="12" t="s">
+        <v>540</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="42">
@@ -4674,13 +4877,13 @@
         <v>133</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="G24" s="9" t="s">
         <v>503</v>
       </c>
-      <c r="H24" s="11" t="s">
-        <v>541</v>
+      <c r="H24" s="12" t="s">
+        <v>540</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="63">
@@ -4700,13 +4903,13 @@
         <v>134</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="G25" s="9" t="s">
         <v>503</v>
       </c>
-      <c r="H25" s="11" t="s">
-        <v>541</v>
+      <c r="H25" s="12" t="s">
+        <v>540</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="63">
@@ -4726,13 +4929,13 @@
         <v>135</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="G26" s="9" t="s">
         <v>503</v>
       </c>
-      <c r="H26" s="11" t="s">
-        <v>541</v>
+      <c r="H26" s="12" t="s">
+        <v>540</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="42">
@@ -4757,8 +4960,8 @@
       <c r="G27" s="9" t="s">
         <v>503</v>
       </c>
-      <c r="H27" s="11" t="s">
-        <v>541</v>
+      <c r="H27" s="12" t="s">
+        <v>540</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="63">
@@ -4778,13 +4981,13 @@
         <v>138</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="G28" s="9" t="s">
         <v>503</v>
       </c>
-      <c r="H28" s="11" t="s">
-        <v>541</v>
+      <c r="H28" s="12" t="s">
+        <v>540</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="63">
@@ -4801,7 +5004,7 @@
         <v>139</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="F29" s="4" t="s">
         <v>494</v>
@@ -4809,8 +5012,8 @@
       <c r="G29" s="9" t="s">
         <v>503</v>
       </c>
-      <c r="H29" s="11" t="s">
-        <v>541</v>
+      <c r="H29" s="12" t="s">
+        <v>540</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="42">
@@ -4835,8 +5038,8 @@
       <c r="G30" s="9" t="s">
         <v>503</v>
       </c>
-      <c r="H30" s="11" t="s">
-        <v>541</v>
+      <c r="H30" s="12" t="s">
+        <v>540</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="63">
@@ -4856,13 +5059,13 @@
         <v>141</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="G31" s="9" t="s">
         <v>503</v>
       </c>
-      <c r="H31" s="11" t="s">
-        <v>541</v>
+      <c r="H31" s="12" t="s">
+        <v>540</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="63">
@@ -4887,8 +5090,8 @@
       <c r="G32" s="9" t="s">
         <v>503</v>
       </c>
-      <c r="H32" s="11" t="s">
-        <v>541</v>
+      <c r="H32" s="12" t="s">
+        <v>540</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="63">
@@ -4908,13 +5111,13 @@
         <v>144</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="G33" s="9" t="s">
         <v>503</v>
       </c>
-      <c r="H33" s="11" t="s">
-        <v>541</v>
+      <c r="H33" s="12" t="s">
+        <v>540</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="42">
@@ -4934,13 +5137,13 @@
         <v>163</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="G34" s="9" t="s">
         <v>503</v>
       </c>
-      <c r="H34" s="11" t="s">
-        <v>541</v>
+      <c r="H34" s="12" t="s">
+        <v>540</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="84">
@@ -4965,8 +5168,8 @@
       <c r="G35" s="9" t="s">
         <v>503</v>
       </c>
-      <c r="H35" s="11" t="s">
-        <v>541</v>
+      <c r="H35" s="12" t="s">
+        <v>540</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="63">
@@ -4986,13 +5189,13 @@
         <v>169</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="G36" s="9" t="s">
         <v>503</v>
       </c>
-      <c r="H36" s="11" t="s">
-        <v>541</v>
+      <c r="H36" s="12" t="s">
+        <v>540</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="63">
@@ -5017,8 +5220,8 @@
       <c r="G37" s="9" t="s">
         <v>503</v>
       </c>
-      <c r="H37" s="11" t="s">
-        <v>541</v>
+      <c r="H37" s="12" t="s">
+        <v>540</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="63">
@@ -5038,13 +5241,13 @@
         <v>171</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="G38" s="9" t="s">
         <v>503</v>
       </c>
-      <c r="H38" s="11" t="s">
-        <v>541</v>
+      <c r="H38" s="12" t="s">
+        <v>540</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="63">
@@ -5064,13 +5267,13 @@
         <v>172</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="G39" s="9" t="s">
         <v>503</v>
       </c>
-      <c r="H39" s="11" t="s">
-        <v>541</v>
+      <c r="H39" s="12" t="s">
+        <v>540</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="63">
@@ -5090,13 +5293,13 @@
         <v>173</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="G40" s="9" t="s">
         <v>503</v>
       </c>
-      <c r="H40" s="11" t="s">
-        <v>541</v>
+      <c r="H40" s="12" t="s">
+        <v>540</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="63">
@@ -5116,13 +5319,13 @@
         <v>174</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="G41" s="9" t="s">
         <v>503</v>
       </c>
-      <c r="H41" s="11" t="s">
-        <v>541</v>
+      <c r="H41" s="12" t="s">
+        <v>540</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="63">
@@ -5142,13 +5345,13 @@
         <v>176</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="G42" s="9" t="s">
         <v>503</v>
       </c>
-      <c r="H42" s="11" t="s">
-        <v>541</v>
+      <c r="H42" s="12" t="s">
+        <v>540</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="63">
@@ -5168,13 +5371,13 @@
         <v>177</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G43" s="9" t="s">
         <v>503</v>
       </c>
-      <c r="H43" s="11" t="s">
-        <v>541</v>
+      <c r="H43" s="12" t="s">
+        <v>540</v>
       </c>
     </row>
     <row r="44" spans="1:8" ht="63">
@@ -5194,13 +5397,13 @@
         <v>178</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="G44" s="9" t="s">
         <v>503</v>
       </c>
-      <c r="H44" s="11" t="s">
-        <v>541</v>
+      <c r="H44" s="12" t="s">
+        <v>540</v>
       </c>
     </row>
     <row r="45" spans="1:8" ht="42">
@@ -5220,13 +5423,13 @@
         <v>221</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="G45" s="9" t="s">
         <v>503</v>
       </c>
-      <c r="H45" s="11" t="s">
-        <v>541</v>
+      <c r="H45" s="12" t="s">
+        <v>540</v>
       </c>
     </row>
     <row r="46" spans="1:8" ht="63">
@@ -5246,13 +5449,13 @@
         <v>179</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="G46" s="9" t="s">
         <v>503</v>
       </c>
-      <c r="H46" s="11" t="s">
-        <v>541</v>
+      <c r="H46" s="12" t="s">
+        <v>540</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="63">
@@ -5272,13 +5475,13 @@
         <v>184</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="G47" s="9" t="s">
         <v>503</v>
       </c>
-      <c r="H47" s="11" t="s">
-        <v>541</v>
+      <c r="H47" s="12" t="s">
+        <v>540</v>
       </c>
     </row>
     <row r="48" spans="1:8" ht="63">
@@ -5298,13 +5501,13 @@
         <v>185</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="G48" s="9" t="s">
         <v>503</v>
       </c>
-      <c r="H48" s="11" t="s">
-        <v>541</v>
+      <c r="H48" s="12" t="s">
+        <v>540</v>
       </c>
     </row>
     <row r="49" spans="1:8" ht="63">
@@ -5324,13 +5527,13 @@
         <v>186</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="G49" s="9" t="s">
         <v>503</v>
       </c>
-      <c r="H49" s="11" t="s">
-        <v>541</v>
+      <c r="H49" s="12" t="s">
+        <v>540</v>
       </c>
     </row>
     <row r="50" spans="1:8" ht="63">
@@ -5350,13 +5553,13 @@
         <v>187</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="G50" s="9" t="s">
         <v>503</v>
       </c>
-      <c r="H50" s="11" t="s">
-        <v>541</v>
+      <c r="H50" s="12" t="s">
+        <v>540</v>
       </c>
     </row>
     <row r="51" spans="1:8" ht="63">
@@ -5376,13 +5579,13 @@
         <v>188</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="G51" s="9" t="s">
         <v>503</v>
       </c>
-      <c r="H51" s="11" t="s">
-        <v>541</v>
+      <c r="H51" s="12" t="s">
+        <v>540</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="63">
@@ -5402,13 +5605,13 @@
         <v>189</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="G52" s="9" t="s">
         <v>503</v>
       </c>
-      <c r="H52" s="11" t="s">
-        <v>541</v>
+      <c r="H52" s="12" t="s">
+        <v>540</v>
       </c>
     </row>
     <row r="53" spans="1:8" ht="63">
@@ -5433,8 +5636,8 @@
       <c r="G53" s="9" t="s">
         <v>503</v>
       </c>
-      <c r="H53" s="11" t="s">
-        <v>541</v>
+      <c r="H53" s="12" t="s">
+        <v>540</v>
       </c>
     </row>
     <row r="54" spans="1:8" ht="63">
@@ -5459,8 +5662,8 @@
       <c r="G54" s="9" t="s">
         <v>503</v>
       </c>
-      <c r="H54" s="11" t="s">
-        <v>541</v>
+      <c r="H54" s="12" t="s">
+        <v>540</v>
       </c>
     </row>
     <row r="55" spans="1:8" ht="42">
@@ -5480,13 +5683,13 @@
         <v>194</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="G55" s="9" t="s">
         <v>503</v>
       </c>
-      <c r="H55" s="11" t="s">
-        <v>541</v>
+      <c r="H55" s="12" t="s">
+        <v>540</v>
       </c>
     </row>
     <row r="56" spans="1:8" ht="42">
@@ -5511,8 +5714,8 @@
       <c r="G56" s="9" t="s">
         <v>503</v>
       </c>
-      <c r="H56" s="11" t="s">
-        <v>541</v>
+      <c r="H56" s="12" t="s">
+        <v>540</v>
       </c>
     </row>
     <row r="57" spans="1:8" ht="63">
@@ -5532,13 +5735,13 @@
         <v>196</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="G57" s="9" t="s">
         <v>503</v>
       </c>
-      <c r="H57" s="10" t="s">
-        <v>541</v>
+      <c r="H57" s="12" t="s">
+        <v>540</v>
       </c>
     </row>
     <row r="58" spans="1:8" ht="63">
@@ -5558,13 +5761,13 @@
         <v>200</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="G58" s="9" t="s">
         <v>503</v>
       </c>
-      <c r="H58" s="10" t="s">
-        <v>541</v>
+      <c r="H58" s="12" t="s">
+        <v>540</v>
       </c>
     </row>
     <row r="59" spans="1:8" ht="63">
@@ -5589,8 +5792,8 @@
       <c r="G59" s="9" t="s">
         <v>503</v>
       </c>
-      <c r="H59" s="11" t="s">
-        <v>541</v>
+      <c r="H59" s="12" t="s">
+        <v>540</v>
       </c>
     </row>
     <row r="60" spans="1:8" ht="21">
@@ -5610,13 +5813,13 @@
         <v>207</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="G60" s="9" t="s">
         <v>503</v>
       </c>
-      <c r="H60" s="11" t="s">
-        <v>541</v>
+      <c r="H60" s="12" t="s">
+        <v>540</v>
       </c>
     </row>
     <row r="61" spans="1:8" ht="21">
@@ -5641,6 +5844,9 @@
       <c r="G61" s="9" t="s">
         <v>503</v>
       </c>
+      <c r="H61" s="12" t="s">
+        <v>540</v>
+      </c>
     </row>
     <row r="62" spans="1:8" ht="42">
       <c r="A62" s="3" t="s">
@@ -5659,13 +5865,13 @@
         <v>213</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="G62" s="9" t="s">
         <v>503</v>
       </c>
       <c r="H62" s="13" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
     </row>
     <row r="63" spans="1:8" ht="42">
@@ -5685,13 +5891,13 @@
         <v>212</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="G63" s="9" t="s">
         <v>503</v>
       </c>
       <c r="H63" s="13" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
     </row>
     <row r="64" spans="1:8" ht="84">
@@ -5711,13 +5917,13 @@
         <v>218</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G64" s="9" t="s">
         <v>503</v>
       </c>
-      <c r="H64" s="11" t="s">
-        <v>541</v>
+      <c r="H64" s="12" t="s">
+        <v>540</v>
       </c>
     </row>
     <row r="65" spans="1:8" ht="84">
@@ -5737,13 +5943,13 @@
         <v>219</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G65" s="9" t="s">
         <v>503</v>
       </c>
-      <c r="H65" s="11" t="s">
-        <v>541</v>
+      <c r="H65" s="12" t="s">
+        <v>540</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="63">
@@ -5763,13 +5969,13 @@
         <v>220</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="G66" s="9" t="s">
         <v>503</v>
       </c>
-      <c r="H66" s="11" t="s">
-        <v>541</v>
+      <c r="H66" s="12" t="s">
+        <v>540</v>
       </c>
     </row>
     <row r="67" spans="1:8" ht="63">
@@ -5794,7 +6000,9 @@
       <c r="G67" s="9" t="s">
         <v>503</v>
       </c>
-      <c r="H67" s="10"/>
+      <c r="H67" s="12" t="s">
+        <v>540</v>
+      </c>
     </row>
     <row r="68" spans="1:8" ht="42">
       <c r="A68" s="3" t="s">
@@ -5818,7 +6026,9 @@
       <c r="G68" s="9" t="s">
         <v>503</v>
       </c>
-      <c r="H68" s="10"/>
+      <c r="H68" s="12" t="s">
+        <v>540</v>
+      </c>
     </row>
     <row r="69" spans="1:8" ht="42">
       <c r="A69" s="3" t="s">
@@ -5837,13 +6047,13 @@
         <v>229</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="G69" s="9" t="s">
         <v>503</v>
       </c>
-      <c r="H69" s="10" t="s">
-        <v>541</v>
+      <c r="H69" s="12" t="s">
+        <v>540</v>
       </c>
     </row>
     <row r="70" spans="1:8" ht="42">
@@ -5868,8 +6078,8 @@
       <c r="G70" s="9" t="s">
         <v>503</v>
       </c>
-      <c r="H70" s="10" t="s">
-        <v>541</v>
+      <c r="H70" s="12" t="s">
+        <v>540</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="63">
@@ -5889,13 +6099,13 @@
         <v>233</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="G71" s="9" t="s">
         <v>503</v>
       </c>
-      <c r="H71" s="10" t="s">
-        <v>541</v>
+      <c r="H71" s="12" t="s">
+        <v>540</v>
       </c>
     </row>
     <row r="72" spans="1:8" ht="84">
@@ -5914,9 +6124,14 @@
       <c r="E72" s="4" t="s">
         <v>505</v>
       </c>
-      <c r="F72" s="4"/>
-      <c r="G72" s="3" t="s">
-        <v>16</v>
+      <c r="F72" s="4" t="s">
+        <v>643</v>
+      </c>
+      <c r="G72" s="9" t="s">
+        <v>503</v>
+      </c>
+      <c r="H72" s="12" t="s">
+        <v>540</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="84">
@@ -5933,11 +6148,16 @@
         <v>162</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>516</v>
-      </c>
-      <c r="F73" s="4"/>
-      <c r="G73" s="3" t="s">
-        <v>16</v>
+        <v>515</v>
+      </c>
+      <c r="F73" s="4" t="s">
+        <v>644</v>
+      </c>
+      <c r="G73" s="9" t="s">
+        <v>503</v>
+      </c>
+      <c r="H73" s="12" t="s">
+        <v>540</v>
       </c>
     </row>
     <row r="74" spans="1:8" ht="42">
@@ -5956,9 +6176,14 @@
       <c r="E74" s="4" t="s">
         <v>472</v>
       </c>
-      <c r="F74" s="4"/>
-      <c r="G74" s="3" t="s">
-        <v>16</v>
+      <c r="F74" s="4" t="s">
+        <v>645</v>
+      </c>
+      <c r="G74" s="9" t="s">
+        <v>503</v>
+      </c>
+      <c r="H74" s="12" t="s">
+        <v>540</v>
       </c>
     </row>
     <row r="75" spans="1:8" ht="84">
@@ -5975,11 +6200,16 @@
         <v>162</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>517</v>
-      </c>
-      <c r="F75" s="4"/>
-      <c r="G75" s="3" t="s">
-        <v>16</v>
+        <v>516</v>
+      </c>
+      <c r="F75" s="4" t="s">
+        <v>646</v>
+      </c>
+      <c r="G75" s="9" t="s">
+        <v>503</v>
+      </c>
+      <c r="H75" s="12" t="s">
+        <v>540</v>
       </c>
     </row>
     <row r="76" spans="1:8" ht="84">
@@ -5996,11 +6226,16 @@
         <v>475</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>518</v>
-      </c>
-      <c r="F76" s="4"/>
-      <c r="G76" s="3" t="s">
-        <v>16</v>
+        <v>517</v>
+      </c>
+      <c r="F76" s="4" t="s">
+        <v>648</v>
+      </c>
+      <c r="G76" s="9" t="s">
+        <v>503</v>
+      </c>
+      <c r="H76" s="12" t="s">
+        <v>540</v>
       </c>
     </row>
     <row r="77" spans="1:8" ht="84">
@@ -6017,11 +6252,16 @@
         <v>475</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>519</v>
-      </c>
-      <c r="F77" s="4"/>
-      <c r="G77" s="3" t="s">
-        <v>16</v>
+        <v>518</v>
+      </c>
+      <c r="F77" s="4" t="s">
+        <v>649</v>
+      </c>
+      <c r="G77" s="9" t="s">
+        <v>503</v>
+      </c>
+      <c r="H77" s="12" t="s">
+        <v>540</v>
       </c>
     </row>
     <row r="78" spans="1:8" ht="84">
@@ -6038,11 +6278,16 @@
         <v>473</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>512</v>
-      </c>
-      <c r="F78" s="4"/>
-      <c r="G78" s="3" t="s">
-        <v>16</v>
+        <v>511</v>
+      </c>
+      <c r="F78" s="4" t="s">
+        <v>650</v>
+      </c>
+      <c r="G78" s="9" t="s">
+        <v>503</v>
+      </c>
+      <c r="H78" s="12" t="s">
+        <v>540</v>
       </c>
     </row>
     <row r="79" spans="1:8" ht="63">
@@ -6059,11 +6304,16 @@
         <v>473</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>511</v>
-      </c>
-      <c r="F79" s="4"/>
-      <c r="G79" s="3" t="s">
-        <v>16</v>
+        <v>510</v>
+      </c>
+      <c r="F79" s="4" t="s">
+        <v>651</v>
+      </c>
+      <c r="G79" s="9" t="s">
+        <v>503</v>
+      </c>
+      <c r="H79" s="12" t="s">
+        <v>540</v>
       </c>
     </row>
     <row r="80" spans="1:8" ht="63">
@@ -6080,14 +6330,19 @@
         <v>473</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>514</v>
-      </c>
-      <c r="F80" s="4"/>
-      <c r="G80" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7" ht="42">
+        <v>513</v>
+      </c>
+      <c r="F80" s="4" t="s">
+        <v>652</v>
+      </c>
+      <c r="G80" s="9" t="s">
+        <v>503</v>
+      </c>
+      <c r="H80" s="12" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" ht="63">
       <c r="A81" s="3" t="s">
         <v>98</v>
       </c>
@@ -6104,13 +6359,16 @@
         <v>225</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>507</v>
+        <v>653</v>
       </c>
       <c r="G81" s="9" t="s">
         <v>503</v>
       </c>
-    </row>
-    <row r="82" spans="1:7" ht="63">
+      <c r="H81" s="12" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" ht="63">
       <c r="A82" s="3" t="s">
         <v>99</v>
       </c>
@@ -6124,14 +6382,19 @@
         <v>20</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>508</v>
-      </c>
-      <c r="F82" s="4"/>
-      <c r="G82" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7" ht="84">
+        <v>507</v>
+      </c>
+      <c r="F82" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="G82" s="9" t="s">
+        <v>503</v>
+      </c>
+      <c r="H82" s="12" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" ht="84">
       <c r="A83" s="3" t="s">
         <v>100</v>
       </c>
@@ -6145,14 +6408,19 @@
         <v>473</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>520</v>
-      </c>
-      <c r="F83" s="4"/>
-      <c r="G83" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7" ht="63">
+        <v>519</v>
+      </c>
+      <c r="F83" s="4" t="s">
+        <v>655</v>
+      </c>
+      <c r="G83" s="9" t="s">
+        <v>503</v>
+      </c>
+      <c r="H83" s="12" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" ht="63">
       <c r="A84" s="3" t="s">
         <v>101</v>
       </c>
@@ -6166,14 +6434,19 @@
         <v>473</v>
       </c>
       <c r="E84" s="4" t="s">
-        <v>510</v>
-      </c>
-      <c r="F84" s="4"/>
-      <c r="G84" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="85" spans="1:7" ht="84">
+        <v>509</v>
+      </c>
+      <c r="F84" s="4" t="s">
+        <v>656</v>
+      </c>
+      <c r="G84" s="9" t="s">
+        <v>503</v>
+      </c>
+      <c r="H84" s="12" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" ht="84">
       <c r="A85" s="3" t="s">
         <v>102</v>
       </c>
@@ -6187,14 +6460,19 @@
         <v>473</v>
       </c>
       <c r="E85" s="4" t="s">
-        <v>509</v>
-      </c>
-      <c r="F85" s="4"/>
-      <c r="G85" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="86" spans="1:7" ht="84">
+        <v>508</v>
+      </c>
+      <c r="F85" s="4" t="s">
+        <v>657</v>
+      </c>
+      <c r="G85" s="9" t="s">
+        <v>503</v>
+      </c>
+      <c r="H85" s="12" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" ht="84">
       <c r="A86" s="3" t="s">
         <v>103</v>
       </c>
@@ -6208,14 +6486,19 @@
         <v>473</v>
       </c>
       <c r="E86" s="4" t="s">
-        <v>515</v>
-      </c>
-      <c r="F86" s="4"/>
-      <c r="G86" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7" ht="105">
+        <v>514</v>
+      </c>
+      <c r="F86" s="4" t="s">
+        <v>658</v>
+      </c>
+      <c r="G86" s="9" t="s">
+        <v>503</v>
+      </c>
+      <c r="H86" s="12" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" ht="105">
       <c r="A87" s="3" t="s">
         <v>104</v>
       </c>
@@ -6229,14 +6512,19 @@
         <v>128</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>613</v>
-      </c>
-      <c r="F87" s="4"/>
-      <c r="G87" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="88" spans="1:7" ht="105">
+        <v>612</v>
+      </c>
+      <c r="F87" s="4" t="s">
+        <v>659</v>
+      </c>
+      <c r="G87" s="9" t="s">
+        <v>503</v>
+      </c>
+      <c r="H87" s="12" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" ht="105">
       <c r="A88" s="3" t="s">
         <v>105</v>
       </c>
@@ -6250,16 +6538,21 @@
         <v>130</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>513</v>
-      </c>
-      <c r="F88" s="4"/>
-      <c r="G88" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="89" spans="1:7" ht="42">
+        <v>512</v>
+      </c>
+      <c r="F88" s="4" t="s">
+        <v>660</v>
+      </c>
+      <c r="G88" s="9" t="s">
+        <v>503</v>
+      </c>
+      <c r="H88" s="12" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" ht="63">
       <c r="A89" s="3" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="B89" s="4" t="s">
         <v>222</v>
@@ -6273,12 +6566,17 @@
       <c r="E89" s="4" t="s">
         <v>477</v>
       </c>
-      <c r="F89" s="4"/>
-      <c r="G89" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7" ht="84">
+      <c r="F89" s="4" t="s">
+        <v>661</v>
+      </c>
+      <c r="G89" s="9" t="s">
+        <v>503</v>
+      </c>
+      <c r="H89" s="12" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" ht="105">
       <c r="A90" s="3" t="s">
         <v>106</v>
       </c>
@@ -6292,14 +6590,19 @@
         <v>136</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>521</v>
-      </c>
-      <c r="F90" s="4"/>
-      <c r="G90" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7" ht="84">
+        <v>520</v>
+      </c>
+      <c r="F90" s="4" t="s">
+        <v>662</v>
+      </c>
+      <c r="G90" s="9" t="s">
+        <v>503</v>
+      </c>
+      <c r="H90" s="12" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" ht="84">
       <c r="A91" s="3" t="s">
         <v>107</v>
       </c>
@@ -6307,20 +6610,25 @@
         <v>504</v>
       </c>
       <c r="C91" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="D91" s="4" t="s">
         <v>522</v>
       </c>
-      <c r="D91" s="4" t="s">
-        <v>523</v>
-      </c>
       <c r="E91" s="4" t="s">
-        <v>539</v>
-      </c>
-      <c r="F91" s="4"/>
-      <c r="G91" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="92" spans="1:7" ht="21">
+        <v>538</v>
+      </c>
+      <c r="F91" s="4" t="s">
+        <v>663</v>
+      </c>
+      <c r="G91" s="9" t="s">
+        <v>503</v>
+      </c>
+      <c r="H91" s="12" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" ht="84">
       <c r="A92" s="3" t="s">
         <v>108</v>
       </c>
@@ -6336,12 +6644,17 @@
       <c r="E92" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="F92" s="4"/>
-      <c r="G92" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="93" spans="1:7" ht="105">
+      <c r="F92" s="4" t="s">
+        <v>647</v>
+      </c>
+      <c r="G92" s="9" t="s">
+        <v>503</v>
+      </c>
+      <c r="H92" s="13" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" ht="105">
       <c r="A93" s="3" t="s">
         <v>109</v>
       </c>
@@ -6355,14 +6668,19 @@
         <v>238</v>
       </c>
       <c r="E93" s="4" t="s">
-        <v>596</v>
-      </c>
-      <c r="F93" s="4"/>
-      <c r="G93" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="94" spans="1:7" ht="84">
+        <v>595</v>
+      </c>
+      <c r="F93" s="4" t="s">
+        <v>664</v>
+      </c>
+      <c r="G93" s="9" t="s">
+        <v>503</v>
+      </c>
+      <c r="H93" s="13" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" ht="84">
       <c r="A94" s="3" t="s">
         <v>110</v>
       </c>
@@ -6376,14 +6694,19 @@
         <v>238</v>
       </c>
       <c r="E94" s="4" t="s">
-        <v>597</v>
-      </c>
-      <c r="F94" s="4"/>
-      <c r="G94" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="95" spans="1:7" ht="84">
+        <v>596</v>
+      </c>
+      <c r="F94" s="4" t="s">
+        <v>665</v>
+      </c>
+      <c r="G94" s="9" t="s">
+        <v>503</v>
+      </c>
+      <c r="H94" s="13" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" ht="84">
       <c r="A95" s="3" t="s">
         <v>111</v>
       </c>
@@ -6397,14 +6720,19 @@
         <v>238</v>
       </c>
       <c r="E95" s="4" t="s">
-        <v>598</v>
-      </c>
-      <c r="F95" s="4"/>
-      <c r="G95" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="96" spans="1:7" ht="63">
+        <v>597</v>
+      </c>
+      <c r="F95" s="4" t="s">
+        <v>666</v>
+      </c>
+      <c r="G95" s="9" t="s">
+        <v>503</v>
+      </c>
+      <c r="H95" s="13" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" ht="63">
       <c r="A96" s="3" t="s">
         <v>112</v>
       </c>
@@ -6418,14 +6746,19 @@
         <v>238</v>
       </c>
       <c r="E96" s="4" t="s">
-        <v>599</v>
-      </c>
-      <c r="F96" s="4"/>
-      <c r="G96" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="97" spans="1:7" ht="105">
+        <v>598</v>
+      </c>
+      <c r="F96" s="4" t="s">
+        <v>667</v>
+      </c>
+      <c r="G96" s="9" t="s">
+        <v>503</v>
+      </c>
+      <c r="H96" s="11" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" ht="105">
       <c r="A97" s="3" t="s">
         <v>113</v>
       </c>
@@ -6439,14 +6772,19 @@
         <v>481</v>
       </c>
       <c r="E97" s="4" t="s">
-        <v>600</v>
-      </c>
-      <c r="F97" s="4"/>
-      <c r="G97" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="98" spans="1:7" ht="84">
+        <v>599</v>
+      </c>
+      <c r="F97" s="4" t="s">
+        <v>668</v>
+      </c>
+      <c r="G97" s="9" t="s">
+        <v>503</v>
+      </c>
+      <c r="H97" s="11" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" ht="84">
       <c r="A98" s="3" t="s">
         <v>114</v>
       </c>
@@ -6460,14 +6798,19 @@
         <v>481</v>
       </c>
       <c r="E98" s="4" t="s">
-        <v>601</v>
-      </c>
-      <c r="F98" s="4"/>
-      <c r="G98" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="99" spans="1:7" ht="63">
+        <v>600</v>
+      </c>
+      <c r="F98" s="4" t="s">
+        <v>669</v>
+      </c>
+      <c r="G98" s="9" t="s">
+        <v>503</v>
+      </c>
+      <c r="H98" s="11" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" ht="63">
       <c r="A99" s="3" t="s">
         <v>115</v>
       </c>
@@ -6481,14 +6824,19 @@
         <v>481</v>
       </c>
       <c r="E99" s="4" t="s">
-        <v>602</v>
-      </c>
-      <c r="F99" s="4"/>
-      <c r="G99" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="100" spans="1:7" ht="84">
+        <v>601</v>
+      </c>
+      <c r="F99" s="4" t="s">
+        <v>670</v>
+      </c>
+      <c r="G99" s="9" t="s">
+        <v>503</v>
+      </c>
+      <c r="H99" s="11" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" ht="84">
       <c r="A100" s="3" t="s">
         <v>116</v>
       </c>
@@ -6502,14 +6850,19 @@
         <v>479</v>
       </c>
       <c r="E100" s="4" t="s">
-        <v>603</v>
-      </c>
-      <c r="F100" s="4"/>
-      <c r="G100" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="101" spans="1:7" ht="84">
+        <v>602</v>
+      </c>
+      <c r="F100" s="4" t="s">
+        <v>671</v>
+      </c>
+      <c r="G100" s="9" t="s">
+        <v>503</v>
+      </c>
+      <c r="H100" s="11" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" ht="84">
       <c r="A101" s="3" t="s">
         <v>117</v>
       </c>
@@ -6523,14 +6876,19 @@
         <v>214</v>
       </c>
       <c r="E101" s="4" t="s">
-        <v>604</v>
-      </c>
-      <c r="F101" s="4"/>
-      <c r="G101" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="102" spans="1:7" ht="84">
+        <v>603</v>
+      </c>
+      <c r="F101" s="4" t="s">
+        <v>672</v>
+      </c>
+      <c r="G101" s="9" t="s">
+        <v>503</v>
+      </c>
+      <c r="H101" s="11" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" ht="84">
       <c r="A102" s="3" t="s">
         <v>118</v>
       </c>
@@ -6544,14 +6902,19 @@
         <v>481</v>
       </c>
       <c r="E102" s="4" t="s">
-        <v>520</v>
-      </c>
-      <c r="F102" s="4"/>
-      <c r="G102" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="103" spans="1:7" ht="63">
+        <v>519</v>
+      </c>
+      <c r="F102" s="4" t="s">
+        <v>673</v>
+      </c>
+      <c r="G102" s="9" t="s">
+        <v>503</v>
+      </c>
+      <c r="H102" s="11" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" ht="63">
       <c r="A103" s="3" t="s">
         <v>240</v>
       </c>
@@ -6565,14 +6928,19 @@
         <v>481</v>
       </c>
       <c r="E103" s="4" t="s">
-        <v>605</v>
-      </c>
-      <c r="F103" s="4"/>
-      <c r="G103" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="104" spans="1:7" ht="84">
+        <v>604</v>
+      </c>
+      <c r="F103" s="4" t="s">
+        <v>674</v>
+      </c>
+      <c r="G103" s="9" t="s">
+        <v>503</v>
+      </c>
+      <c r="H103" s="11" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" ht="84">
       <c r="A104" s="3" t="s">
         <v>241</v>
       </c>
@@ -6586,14 +6954,19 @@
         <v>481</v>
       </c>
       <c r="E104" s="4" t="s">
-        <v>606</v>
-      </c>
-      <c r="F104" s="4"/>
-      <c r="G104" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="105" spans="1:7" ht="84">
+        <v>605</v>
+      </c>
+      <c r="F104" s="4" t="s">
+        <v>675</v>
+      </c>
+      <c r="G104" s="9" t="s">
+        <v>503</v>
+      </c>
+      <c r="H104" s="11" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" ht="84">
       <c r="A105" s="3" t="s">
         <v>242</v>
       </c>
@@ -6607,14 +6980,19 @@
         <v>481</v>
       </c>
       <c r="E105" s="4" t="s">
-        <v>607</v>
-      </c>
-      <c r="F105" s="4"/>
-      <c r="G105" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="106" spans="1:7" ht="84">
+        <v>606</v>
+      </c>
+      <c r="F105" s="4" t="s">
+        <v>676</v>
+      </c>
+      <c r="G105" s="9" t="s">
+        <v>503</v>
+      </c>
+      <c r="H105" s="11" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" ht="84">
       <c r="A106" s="3" t="s">
         <v>243</v>
       </c>
@@ -6625,17 +7003,22 @@
         <v>145</v>
       </c>
       <c r="D106" s="4" t="s">
+        <v>531</v>
+      </c>
+      <c r="E106" s="4" t="s">
         <v>532</v>
       </c>
-      <c r="E106" s="4" t="s">
-        <v>533</v>
-      </c>
-      <c r="F106" s="4"/>
-      <c r="G106" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="107" spans="1:7" ht="63">
+      <c r="F106" s="4" t="s">
+        <v>677</v>
+      </c>
+      <c r="G106" s="9" t="s">
+        <v>503</v>
+      </c>
+      <c r="H106" s="11" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" ht="63">
       <c r="A107" s="3" t="s">
         <v>244</v>
       </c>
@@ -6646,17 +7029,22 @@
         <v>145</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="E107" s="4" t="s">
-        <v>534</v>
-      </c>
-      <c r="F107" s="4"/>
-      <c r="G107" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="108" spans="1:7" ht="84">
+        <v>533</v>
+      </c>
+      <c r="F107" s="4" t="s">
+        <v>678</v>
+      </c>
+      <c r="G107" s="9" t="s">
+        <v>503</v>
+      </c>
+      <c r="H107" s="11" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" ht="84">
       <c r="A108" s="3" t="s">
         <v>245</v>
       </c>
@@ -6667,17 +7055,22 @@
         <v>146</v>
       </c>
       <c r="D108" s="4" t="s">
+        <v>534</v>
+      </c>
+      <c r="E108" s="4" t="s">
         <v>535</v>
       </c>
-      <c r="E108" s="4" t="s">
-        <v>536</v>
-      </c>
-      <c r="F108" s="4"/>
-      <c r="G108" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="109" spans="1:7" ht="126">
+      <c r="F108" s="4" t="s">
+        <v>679</v>
+      </c>
+      <c r="G108" s="9" t="s">
+        <v>503</v>
+      </c>
+      <c r="H108" s="11" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" ht="126">
       <c r="A109" s="3" t="s">
         <v>246</v>
       </c>
@@ -6688,17 +7081,22 @@
         <v>146</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="E109" s="4" t="s">
-        <v>537</v>
-      </c>
-      <c r="F109" s="4"/>
-      <c r="G109" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="110" spans="1:7" ht="105">
+        <v>536</v>
+      </c>
+      <c r="F109" s="4" t="s">
+        <v>680</v>
+      </c>
+      <c r="G109" s="9" t="s">
+        <v>503</v>
+      </c>
+      <c r="H109" s="11" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" ht="105">
       <c r="A110" s="3" t="s">
         <v>247</v>
       </c>
@@ -6709,54 +7107,63 @@
         <v>146</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="E110" s="4" t="s">
-        <v>538</v>
-      </c>
-      <c r="F110" s="4"/>
-      <c r="G110" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="111" spans="1:7" ht="42">
+        <v>537</v>
+      </c>
+      <c r="F110" s="4" t="s">
+        <v>681</v>
+      </c>
+      <c r="G110" s="9" t="s">
+        <v>503</v>
+      </c>
+      <c r="H110" s="11" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" ht="42">
       <c r="A111" s="3" t="s">
         <v>248</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="C111" s="4" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="D111" s="4" t="s">
         <v>205</v>
       </c>
       <c r="E111" s="4" t="s">
-        <v>588</v>
-      </c>
-      <c r="F111" s="4"/>
+        <v>587</v>
+      </c>
+      <c r="F111" s="4" t="s">
+        <v>623</v>
+      </c>
       <c r="G111" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="112" spans="1:7" ht="63">
+    <row r="112" spans="1:8" ht="84">
       <c r="A112" s="3" t="s">
         <v>249</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="C112" s="4" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="D112" s="4" t="s">
         <v>205</v>
       </c>
       <c r="E112" s="4" t="s">
-        <v>593</v>
-      </c>
-      <c r="F112" s="4"/>
+        <v>592</v>
+      </c>
+      <c r="F112" s="4" t="s">
+        <v>624</v>
+      </c>
       <c r="G112" s="3" t="s">
         <v>16</v>
       </c>
@@ -6766,49 +7173,53 @@
         <v>250</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="C113" s="4" t="s">
         <v>209</v>
       </c>
       <c r="D113" s="4" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E113" s="4" t="s">
-        <v>589</v>
-      </c>
-      <c r="F113" s="4"/>
+        <v>588</v>
+      </c>
+      <c r="F113" s="4" t="s">
+        <v>625</v>
+      </c>
       <c r="G113" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="114" spans="1:7" ht="42">
+    <row r="114" spans="1:7" ht="84">
       <c r="A114" s="3" t="s">
         <v>251</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="C114" s="4" t="s">
         <v>209</v>
       </c>
       <c r="D114" s="4" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E114" s="4" t="s">
-        <v>592</v>
-      </c>
-      <c r="F114" s="4"/>
+        <v>591</v>
+      </c>
+      <c r="F114" s="4" t="s">
+        <v>626</v>
+      </c>
       <c r="G114" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="115" spans="1:7" ht="42">
+    <row r="115" spans="1:7" ht="84">
       <c r="A115" s="3" t="s">
         <v>252</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="C115" s="4" t="s">
         <v>478</v>
@@ -6817,9 +7228,11 @@
         <v>479</v>
       </c>
       <c r="E115" s="4" t="s">
-        <v>591</v>
-      </c>
-      <c r="F115" s="4"/>
+        <v>590</v>
+      </c>
+      <c r="F115" s="4" t="s">
+        <v>627</v>
+      </c>
       <c r="G115" s="3" t="s">
         <v>16</v>
       </c>
@@ -6829,7 +7242,7 @@
         <v>253</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="C116" s="4" t="s">
         <v>478</v>
@@ -6838,9 +7251,11 @@
         <v>479</v>
       </c>
       <c r="E116" s="4" t="s">
-        <v>594</v>
-      </c>
-      <c r="F116" s="4"/>
+        <v>593</v>
+      </c>
+      <c r="F116" s="4" t="s">
+        <v>628</v>
+      </c>
       <c r="G116" s="3" t="s">
         <v>16</v>
       </c>
@@ -6850,7 +7265,7 @@
         <v>254</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="C117" s="4" t="s">
         <v>215</v>
@@ -6859,19 +7274,21 @@
         <v>214</v>
       </c>
       <c r="E117" s="4" t="s">
-        <v>595</v>
-      </c>
-      <c r="F117" s="4"/>
+        <v>594</v>
+      </c>
+      <c r="F117" s="4" t="s">
+        <v>629</v>
+      </c>
       <c r="G117" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="118" spans="1:7" ht="42">
+    <row r="118" spans="1:7" ht="84">
       <c r="A118" s="3" t="s">
         <v>255</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="C118" s="4" t="s">
         <v>215</v>
@@ -6880,9 +7297,11 @@
         <v>214</v>
       </c>
       <c r="E118" s="4" t="s">
-        <v>591</v>
-      </c>
-      <c r="F118" s="4"/>
+        <v>590</v>
+      </c>
+      <c r="F118" s="4" t="s">
+        <v>630</v>
+      </c>
       <c r="G118" s="3" t="s">
         <v>16</v>
       </c>
@@ -6892,7 +7311,7 @@
         <v>256</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="C119" s="4" t="s">
         <v>215</v>
@@ -6901,9 +7320,11 @@
         <v>214</v>
       </c>
       <c r="E119" s="4" t="s">
-        <v>589</v>
-      </c>
-      <c r="F119" s="4"/>
+        <v>588</v>
+      </c>
+      <c r="F119" s="4" t="s">
+        <v>625</v>
+      </c>
       <c r="G119" s="3" t="s">
         <v>16</v>
       </c>
@@ -6913,7 +7334,7 @@
         <v>257</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="C120" s="4" t="s">
         <v>215</v>
@@ -6922,9 +7343,11 @@
         <v>214</v>
       </c>
       <c r="E120" s="4" t="s">
-        <v>594</v>
-      </c>
-      <c r="F120" s="4"/>
+        <v>593</v>
+      </c>
+      <c r="F120" s="4" t="s">
+        <v>631</v>
+      </c>
       <c r="G120" s="3" t="s">
         <v>16</v>
       </c>
@@ -6934,7 +7357,7 @@
         <v>258</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="C121" s="4" t="s">
         <v>215</v>
@@ -6943,9 +7366,11 @@
         <v>214</v>
       </c>
       <c r="E121" s="4" t="s">
-        <v>612</v>
-      </c>
-      <c r="F121" s="4"/>
+        <v>611</v>
+      </c>
+      <c r="F121" s="4" t="s">
+        <v>632</v>
+      </c>
       <c r="G121" s="3" t="s">
         <v>16</v>
       </c>
@@ -6955,18 +7380,20 @@
         <v>259</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="C122" s="4" t="s">
         <v>217</v>
       </c>
       <c r="D122" s="4" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="E122" s="4" t="s">
-        <v>608</v>
-      </c>
-      <c r="F122" s="4"/>
+        <v>607</v>
+      </c>
+      <c r="F122" s="4" t="s">
+        <v>633</v>
+      </c>
       <c r="G122" s="3" t="s">
         <v>16</v>
       </c>
@@ -6976,18 +7403,20 @@
         <v>260</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="C123" s="4" t="s">
         <v>217</v>
       </c>
       <c r="D123" s="4" t="s">
+        <v>608</v>
+      </c>
+      <c r="E123" s="4" t="s">
         <v>609</v>
       </c>
-      <c r="E123" s="4" t="s">
-        <v>610</v>
-      </c>
-      <c r="F123" s="4"/>
+      <c r="F123" s="4" t="s">
+        <v>634</v>
+      </c>
       <c r="G123" s="3" t="s">
         <v>16</v>
       </c>
@@ -6997,18 +7426,20 @@
         <v>261</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="C124" s="4" t="s">
         <v>217</v>
       </c>
       <c r="D124" s="4" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="E124" s="4" t="s">
-        <v>589</v>
-      </c>
-      <c r="F124" s="4"/>
+        <v>588</v>
+      </c>
+      <c r="F124" s="4" t="s">
+        <v>625</v>
+      </c>
       <c r="G124" s="3" t="s">
         <v>16</v>
       </c>
@@ -7018,18 +7449,20 @@
         <v>262</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="C125" s="4" t="s">
         <v>217</v>
       </c>
       <c r="D125" s="4" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="E125" s="4" t="s">
-        <v>594</v>
-      </c>
-      <c r="F125" s="4"/>
+        <v>593</v>
+      </c>
+      <c r="F125" s="4" t="s">
+        <v>631</v>
+      </c>
       <c r="G125" s="3" t="s">
         <v>16</v>
       </c>
@@ -7039,39 +7472,43 @@
         <v>263</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="C126" s="4" t="s">
         <v>217</v>
       </c>
       <c r="D126" s="4" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="E126" s="4" t="s">
-        <v>611</v>
-      </c>
-      <c r="F126" s="4"/>
+        <v>610</v>
+      </c>
+      <c r="F126" s="4" t="s">
+        <v>635</v>
+      </c>
       <c r="G126" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="127" spans="1:7" ht="42">
+    <row r="127" spans="1:7" ht="84">
       <c r="A127" s="3" t="s">
         <v>264</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C127" s="4" t="s">
         <v>160</v>
       </c>
       <c r="D127" s="4" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="E127" s="4" t="s">
-        <v>615</v>
-      </c>
-      <c r="F127" s="4"/>
+        <v>614</v>
+      </c>
+      <c r="F127" s="4" t="s">
+        <v>636</v>
+      </c>
       <c r="G127" s="3" t="s">
         <v>16</v>
       </c>
@@ -7081,102 +7518,112 @@
         <v>265</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C128" s="4" t="s">
         <v>160</v>
       </c>
       <c r="D128" s="4" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="E128" s="4" t="s">
-        <v>618</v>
-      </c>
-      <c r="F128" s="4"/>
+        <v>617</v>
+      </c>
+      <c r="F128" s="4" t="s">
+        <v>637</v>
+      </c>
       <c r="G128" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="129" spans="1:7" ht="63">
+    <row r="129" spans="1:7" ht="84">
       <c r="A129" s="3" t="s">
         <v>266</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C129" s="4" t="s">
         <v>160</v>
       </c>
       <c r="D129" s="4" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="E129" s="4" t="s">
-        <v>621</v>
-      </c>
-      <c r="F129" s="4"/>
+        <v>620</v>
+      </c>
+      <c r="F129" s="4" t="s">
+        <v>638</v>
+      </c>
       <c r="G129" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="130" spans="1:7" ht="42">
+    <row r="130" spans="1:7" ht="63">
       <c r="A130" s="3" t="s">
         <v>267</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C130" s="4" t="s">
         <v>160</v>
       </c>
       <c r="D130" s="4" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="E130" s="4" t="s">
-        <v>622</v>
-      </c>
-      <c r="F130" s="4"/>
+        <v>621</v>
+      </c>
+      <c r="F130" s="4" t="s">
+        <v>639</v>
+      </c>
       <c r="G130" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="131" spans="1:7" ht="42">
+    <row r="131" spans="1:7" ht="84">
       <c r="A131" s="3" t="s">
         <v>268</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C131" s="4" t="s">
         <v>160</v>
       </c>
       <c r="D131" s="4" t="s">
+        <v>615</v>
+      </c>
+      <c r="E131" s="4" t="s">
         <v>616</v>
       </c>
-      <c r="E131" s="4" t="s">
-        <v>617</v>
-      </c>
-      <c r="F131" s="4"/>
+      <c r="F131" s="4" t="s">
+        <v>640</v>
+      </c>
       <c r="G131" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="132" spans="1:7" ht="42">
+    <row r="132" spans="1:7" ht="63">
       <c r="A132" s="3" t="s">
         <v>269</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C132" s="4" t="s">
         <v>160</v>
       </c>
       <c r="D132" s="4" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="E132" s="4" t="s">
-        <v>619</v>
-      </c>
-      <c r="F132" s="4"/>
+        <v>618</v>
+      </c>
+      <c r="F132" s="4" t="s">
+        <v>641</v>
+      </c>
       <c r="G132" s="3" t="s">
         <v>16</v>
       </c>
@@ -7186,18 +7633,20 @@
         <v>270</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C133" s="4" t="s">
         <v>160</v>
       </c>
       <c r="D133" s="4" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="E133" s="4" t="s">
-        <v>623</v>
-      </c>
-      <c r="F133" s="4"/>
+        <v>622</v>
+      </c>
+      <c r="F133" s="4" t="s">
+        <v>642</v>
+      </c>
       <c r="G133" s="3" t="s">
         <v>16</v>
       </c>
@@ -9415,7 +9864,7 @@
     </row>
     <row r="335" spans="1:7">
       <c r="A335" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B335" s="4"/>
       <c r="C335" s="4"/>
@@ -9426,7 +9875,7 @@
     </row>
     <row r="336" spans="1:7">
       <c r="A336" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B336" s="4"/>
       <c r="C336" s="4"/>
@@ -9437,7 +9886,7 @@
     </row>
     <row r="337" spans="1:7">
       <c r="A337" s="3" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B337" s="4"/>
       <c r="C337" s="4"/>
@@ -9448,7 +9897,7 @@
     </row>
     <row r="338" spans="1:7">
       <c r="A338" s="3" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B338" s="4"/>
       <c r="C338" s="4"/>
@@ -9459,7 +9908,7 @@
     </row>
     <row r="339" spans="1:7">
       <c r="A339" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B339" s="4"/>
       <c r="C339" s="4"/>
@@ -9470,7 +9919,7 @@
     </row>
     <row r="340" spans="1:7">
       <c r="A340" s="3" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B340" s="4"/>
       <c r="C340" s="4"/>
@@ -9481,7 +9930,7 @@
     </row>
     <row r="341" spans="1:7">
       <c r="A341" s="3" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B341" s="4"/>
       <c r="C341" s="4"/>
@@ -9492,7 +9941,7 @@
     </row>
     <row r="342" spans="1:7">
       <c r="A342" s="3" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B342" s="4"/>
       <c r="C342" s="4"/>
@@ -9504,7 +9953,7 @@
   </sheetData>
   <autoFilter ref="A2:H342" xr:uid="{833B9C12-88F9-F440-902B-BDAD178A24F6}"/>
   <phoneticPr fontId="1"/>
-  <conditionalFormatting sqref="H62:H63 A3:G342">
+  <conditionalFormatting sqref="H62:H63 G92:H92 A3:G342 H93:H110">
     <cfRule type="expression" dxfId="0" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
